--- a/docs/cruce_hojas_tanda2.xlsx
+++ b/docs/cruce_hojas_tanda2.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conceptos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce'!$A$1:$U$287</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce'!$A$1:$V$287</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conceptos'!$A$1:$H$1075</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U287"/>
+  <dimension ref="A1:V287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -477,9 +477,10 @@
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="45" customWidth="1" min="17" max="17"/>
     <col width="50" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
-    <col width="30" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="21" max="21"/>
+    <col width="30" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -575,15 +576,20 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>Generada por (Excel, solo cotejo)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>Código HE</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Opp</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>TU DECISIÓN</t>
         </is>
@@ -662,13 +668,14 @@
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="4" t="inlineStr"/>
+      <c r="U2" s="2" t="inlineStr"/>
+      <c r="V2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -750,13 +757,14 @@
           <t>Título dice ascensor y plataforma pero la descripción habla de 'dos ascensores'; 'Marcellino' mal escrito</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr"/>
-      <c r="U3" s="4" t="inlineStr"/>
+      <c r="U3" s="2" t="inlineStr"/>
+      <c r="V3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -832,13 +840,14 @@
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr"/>
-      <c r="U4" s="4" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -924,13 +933,14 @@
           <t>Subida de una parada de ascensor existente y modificación de maquinaria; precio conjunto 1.800; los pagos del 50% dicen 950 + IVA (no cuadra con 1.800); hoja casi idéntica a la de la escalera D</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="n"/>
+      <c r="T5" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr"/>
-      <c r="U5" s="4" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1016,13 +1026,14 @@
           <t>Subida de una parada de ascensor existente y modificación de maquinaria; precio conjunto 1.800; los pagos del 50% dicen 950 + IVA (no cuadra con 1.800); hoja casi idéntica a la de la escalera E</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="n"/>
+      <c r="T6" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr"/>
-      <c r="U6" s="4" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1102,13 +1113,14 @@
           <t>Factura a CEGA ESTRUCTURAS PREFABRICADAS (pagador empresa), no a la comunidad</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="n"/>
+      <c r="T7" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T7" s="2" t="inlineStr"/>
-      <c r="U7" s="4" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1188,13 +1200,14 @@
           <t>Factura a CEGA ESTRUCTURAS PREFABRICADAS (pagador empresa), no a la comunidad</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="n"/>
+      <c r="T8" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr"/>
-      <c r="U8" s="4" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1287,13 +1300,14 @@
           <t>Dos hojas en un fichero (proyecto conjunto + subvenciones a éxito 3,7%); total 14.670 con 12% de descuento por proyecto conjunto = 12.909,60 (total_base con descuento; importes de línea sin descontar); 'Mejora de envolvente térmica' sin decir si es SATE; línea de 740 'Memoria y Proyecto conjunto y visado' SIN CASAR</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="n"/>
+      <c r="T9" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T9" s="2" t="inlineStr"/>
-      <c r="U9" s="4" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1376,13 +1390,14 @@
           <t>Proyecto valorado en 17.620 + iva pero gratuito a cambio de cesión de CAES; total = cesión de ahorros + 3% subvención</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="n"/>
+      <c r="T10" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T10" s="2" t="inlineStr"/>
-      <c r="U10" s="4" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1468,13 +1483,14 @@
           <t>Título dice proyecto de rehabilitación de cubierta con desamiantado pero el contenido es tramitación de subvenciones; precio conjunto 1.980; Otra Documentación Técnica sin bloque</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="n"/>
+      <c r="T11" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr"/>
-      <c r="U11" s="4" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1556,13 +1572,14 @@
           <t>Precio conjunto 1.800 sin desglose</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="n"/>
+      <c r="T12" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T12" s="2" t="inlineStr"/>
-      <c r="U12" s="4" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1642,13 +1659,14 @@
           <t>Subvención para la comunidad de Marquesa de Silvela 11 pero los datos de facturación rellenos son de CEGA ESTRUCTURAS PREFABRICADAS, S.L. (B13835616); pago en 4 mensualidades</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="n"/>
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T13" s="2" t="inlineStr"/>
-      <c r="U13" s="4" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1728,13 +1746,14 @@
           <t>Factura a CEGA ESTRUCTURAS PREFABRICADAS (pagador empresa), no a la comunidad</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr"/>
-      <c r="U14" s="4" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1812,13 +1831,14 @@
         </is>
       </c>
       <c r="R15" s="2" t="n"/>
-      <c r="S15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="n"/>
+      <c r="T15" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T15" s="2" t="inlineStr"/>
-      <c r="U15" s="4" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1897,13 +1917,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="n"/>
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr"/>
-      <c r="U16" s="4" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr"/>
+      <c r="V16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1956,13 +1977,14 @@
           <t>Importes en la firmada: Proyecto rampa o plataforma (PBE, DR/licencia, DF, CSS) 2.600; pago 50% entrega proyecto, 25% licencia, 25% fin de obra</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="n"/>
+      <c r="T17" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr"/>
-      <c r="U17" s="4" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2037,13 +2059,14 @@
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="n"/>
+      <c r="T18" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr"/>
-      <c r="U18" s="4" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr"/>
+      <c r="V18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2122,13 +2145,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="n"/>
+      <c r="T19" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T19" s="2" t="inlineStr"/>
-      <c r="U19" s="4" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2208,13 +2232,14 @@
           <t>Forma de pago 'a la entrega de Proyecto' en una hoja solo de subvención; no dice de qué tipo de subvención</t>
         </is>
       </c>
-      <c r="S20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="n"/>
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T20" s="2" t="inlineStr"/>
-      <c r="U20" s="4" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr"/>
+      <c r="V20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2289,13 +2314,14 @@
         </is>
       </c>
       <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="n"/>
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr"/>
-      <c r="U21" s="4" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr"/>
+      <c r="V21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2370,13 +2396,14 @@
         </is>
       </c>
       <c r="R22" s="2" t="n"/>
-      <c r="S22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="n"/>
+      <c r="T22" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T22" s="2" t="inlineStr"/>
-      <c r="U22" s="4" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2457,13 +2484,14 @@
           <t>Pagador Schindler con orden de compra; forma de pago contradictoria (100% a la contratación vs confirming 60 días); precio conjunto 2.000</t>
         </is>
       </c>
-      <c r="S23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T23" s="2" t="inlineStr"/>
-      <c r="U23" s="4" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -2539,13 +2567,14 @@
         </is>
       </c>
       <c r="R24" s="2" t="n"/>
-      <c r="S24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T24" s="2" t="inlineStr"/>
-      <c r="U24" s="4" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -2620,13 +2649,14 @@
         </is>
       </c>
       <c r="R25" s="2" t="n"/>
-      <c r="S25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="n"/>
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T25" s="2" t="inlineStr"/>
-      <c r="U25" s="4" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2708,13 +2738,14 @@
           <t>Pagador FAIN; precio conjunto 3.500</t>
         </is>
       </c>
-      <c r="S26" s="2" t="inlineStr">
+      <c r="S26" s="2" t="n"/>
+      <c r="T26" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T26" s="2" t="inlineStr"/>
-      <c r="U26" s="4" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -2790,13 +2821,14 @@
         </is>
       </c>
       <c r="R27" s="2" t="n"/>
-      <c r="S27" s="2" t="inlineStr">
+      <c r="S27" s="2" t="n"/>
+      <c r="T27" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T27" s="2" t="inlineStr"/>
-      <c r="U27" s="4" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -2871,13 +2903,14 @@
         </is>
       </c>
       <c r="R28" s="2" t="n"/>
-      <c r="S28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="n"/>
+      <c r="T28" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T28" s="2" t="inlineStr"/>
-      <c r="U28" s="4" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -2930,13 +2963,14 @@
           <t>Importes en la firmada: Renovacion subvenciones 1.690</t>
         </is>
       </c>
-      <c r="S29" s="2" t="inlineStr">
+      <c r="S29" s="2" t="n"/>
+      <c r="T29" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T29" s="2" t="inlineStr"/>
-      <c r="U29" s="4" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -3015,13 +3049,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="n"/>
+      <c r="T30" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="4" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -3100,13 +3135,14 @@
           <t>Conforme 'el cliente' con campo Nº pedido: el pagador podría ser una empresa, no la comunidad</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="n"/>
+      <c r="T31" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr"/>
-      <c r="U31" s="4" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -3186,13 +3222,14 @@
           <t>Membrete con dirección Guzmán el Bueno 56 (otra plantilla)</t>
         </is>
       </c>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="n"/>
+      <c r="T32" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr"/>
-      <c r="U32" s="4" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3237,13 +3274,14 @@
         </is>
       </c>
       <c r="R33" s="2" t="n"/>
-      <c r="S33" s="2" t="inlineStr">
+      <c r="S33" s="2" t="n"/>
+      <c r="T33" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T33" s="2" t="inlineStr"/>
-      <c r="U33" s="4" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -3322,13 +3360,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="n"/>
+      <c r="T34" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr"/>
-      <c r="U34" s="4" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -3373,13 +3412,14 @@
         </is>
       </c>
       <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="inlineStr">
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T35" s="2" t="inlineStr"/>
-      <c r="U35" s="4" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -3424,13 +3464,14 @@
         </is>
       </c>
       <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="S36" s="2" t="n"/>
+      <c r="T36" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="4" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -3475,13 +3516,14 @@
         </is>
       </c>
       <c r="R37" s="2" t="n"/>
-      <c r="S37" s="2" t="inlineStr">
+      <c r="S37" s="2" t="n"/>
+      <c r="T37" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T37" s="2" t="inlineStr"/>
-      <c r="U37" s="4" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -3560,13 +3602,14 @@
         </is>
       </c>
       <c r="R38" s="2" t="n"/>
-      <c r="S38" s="2" t="inlineStr">
+      <c r="S38" s="2" t="n"/>
+      <c r="T38" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T38" s="2" t="inlineStr"/>
-      <c r="U38" s="4" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3648,13 +3691,14 @@
           <t>Precio único 5.900 que incluye toma de datos, proyecto, licencia y dirección de obra</t>
         </is>
       </c>
-      <c r="S39" s="2" t="inlineStr">
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T39" s="2" t="inlineStr"/>
-      <c r="U39" s="4" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -3729,13 +3773,14 @@
         </is>
       </c>
       <c r="R40" s="2" t="n"/>
-      <c r="S40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="n"/>
+      <c r="T40" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T40" s="2" t="inlineStr"/>
-      <c r="U40" s="4" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -3808,13 +3853,14 @@
         </is>
       </c>
       <c r="R41" s="2" t="n"/>
-      <c r="S41" s="2" t="inlineStr">
+      <c r="S41" s="2" t="n"/>
+      <c r="T41" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T41" s="2" t="inlineStr"/>
-      <c r="U41" s="4" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -3897,13 +3943,14 @@
           <t>6 ascensores en una hoja: importes por ascensor (6.500 c/u, 39.000 los 6); total 34.320 con 12% de descuento por volumen solo si se contratan los 6; los 4.760 cubren toma de datos, proyecto y DF</t>
         </is>
       </c>
-      <c r="S42" s="2" t="inlineStr">
+      <c r="S42" s="2" t="n"/>
+      <c r="T42" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T42" s="2" t="inlineStr"/>
-      <c r="U42" s="4" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3986,13 +4033,14 @@
           <t>Precio conjunto 3000 para todo; pagador ASCENSORES CEGA</t>
         </is>
       </c>
-      <c r="S43" s="2" t="inlineStr">
+      <c r="S43" s="2" t="n"/>
+      <c r="T43" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="4" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -4075,13 +4123,14 @@
           <t>Precio conjunto 3000 para todo; pagador ASCENSORES CEGA</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
+      <c r="S44" s="2" t="n"/>
+      <c r="T44" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T44" s="2" t="inlineStr"/>
-      <c r="U44" s="4" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -4161,13 +4210,14 @@
           <t>Plataforma vertical con rampa en la entrada del portal y abrepuertas; pagador Schindler; forma de pago contradictoria; precio conjunto 1.800</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S45" s="2" t="n"/>
+      <c r="T45" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T45" s="2" t="inlineStr"/>
-      <c r="U45" s="4" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -4254,13 +4304,14 @@
           <t>Proyecto de solución de humedades en sótanos y trasteros (obra sin TIPO propio); 'Conforme el cliente' sin decir comunidad; precio conjunto 1.800; 'Inspección de deficiencias' SIN CASAR (¿informe técnico?)</t>
         </is>
       </c>
-      <c r="S46" s="2" t="inlineStr">
+      <c r="S46" s="2" t="n"/>
+      <c r="T46" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="4" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -4349,13 +4400,14 @@
           <t>Dos hojas en un fichero (proyecto ascensor 5.900 + subvenciones 1.980); los 4.160 cubren en una línea toma de datos, proyecto y DF</t>
         </is>
       </c>
-      <c r="S47" s="2" t="inlineStr">
+      <c r="S47" s="2" t="n"/>
+      <c r="T47" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T47" s="2" t="inlineStr"/>
-      <c r="U47" s="4" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -4438,13 +4490,14 @@
           <t>Precio conjunto 5000 para todo; pagador ASCENSORES CEGA</t>
         </is>
       </c>
-      <c r="S48" s="2" t="inlineStr">
+      <c r="S48" s="2" t="n"/>
+      <c r="T48" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T48" s="2" t="inlineStr"/>
-      <c r="U48" s="4" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -4533,13 +4586,14 @@
           <t>Dos hojas en un fichero (proyecto ascensor 5.900 + subvenciones 1.980); los 4.160 cubren en una línea toma de datos, proyecto y DF</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="S49" s="2" t="n"/>
+      <c r="T49" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T49" s="2" t="inlineStr"/>
-      <c r="U49" s="4" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -4619,13 +4673,14 @@
           <t>Transformación de dos ascensores de 12 paradas (Modificación asc. por ser cambio del existente); pagador Schindler con orden de compra; forma de pago contradictoria (cargo en cuenta vs confirming 60 días); precio conjunto 4.000</t>
         </is>
       </c>
-      <c r="S50" s="2" t="inlineStr">
+      <c r="S50" s="2" t="n"/>
+      <c r="T50" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T50" s="2" t="inlineStr"/>
-      <c r="U50" s="4" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -4711,13 +4766,14 @@
           <t>Dos hojas en un fichero: proyecto modificación completa de 2 ascensores con precio conjunto 14.000 + subvención 1.980; total_base es la suma. Formas de pago distintas por hoja</t>
         </is>
       </c>
-      <c r="S51" s="2" t="inlineStr">
+      <c r="S51" s="2" t="n"/>
+      <c r="T51" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T51" s="2" t="inlineStr"/>
-      <c r="U51" s="4" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -4800,13 +4856,14 @@
           <t>Los 3.760 cubren en una sola línea toma de datos, proyecto y dirección de obra</t>
         </is>
       </c>
-      <c r="S52" s="2" t="inlineStr">
+      <c r="S52" s="2" t="n"/>
+      <c r="T52" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T52" s="2" t="inlineStr"/>
-      <c r="U52" s="4" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -4888,13 +4945,14 @@
           <t>Los 2.310 cubren en una línea toma de datos, proyecto y DF</t>
         </is>
       </c>
-      <c r="S53" s="2" t="inlineStr">
+      <c r="S53" s="2" t="n"/>
+      <c r="T53" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T53" s="2" t="inlineStr"/>
-      <c r="U53" s="4" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -4980,13 +5038,14 @@
           <t>Título dice proyecto de rehabilitación de cubierta con desamiantado pero el contenido es tramitación de subvenciones; precio conjunto 1.980; Otra Documentación Técnica sin bloque</t>
         </is>
       </c>
-      <c r="S54" s="2" t="inlineStr">
+      <c r="S54" s="2" t="n"/>
+      <c r="T54" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T54" s="2" t="inlineStr"/>
-      <c r="U54" s="4" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -5062,13 +5121,14 @@
         </is>
       </c>
       <c r="R55" s="2" t="n"/>
-      <c r="S55" s="2" t="inlineStr">
+      <c r="S55" s="2" t="n"/>
+      <c r="T55" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T55" s="2" t="inlineStr"/>
-      <c r="U55" s="4" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -5154,13 +5214,14 @@
           <t>Precio conjunto 6.500 + IVA para todo; pago 100% al encargo (poco habitual). El cliente no se nombra (se supone comunidad); el formulario trae casilla 'Pedido nº'</t>
         </is>
       </c>
-      <c r="S56" s="2" t="inlineStr">
+      <c r="S56" s="2" t="n"/>
+      <c r="T56" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T56" s="2" t="inlineStr"/>
-      <c r="U56" s="4" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -5236,13 +5297,14 @@
         </is>
       </c>
       <c r="R57" s="2" t="n"/>
-      <c r="S57" s="2" t="inlineStr">
+      <c r="S57" s="2" t="n"/>
+      <c r="T57" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T57" s="2" t="inlineStr"/>
-      <c r="U57" s="4" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -5336,13 +5398,14 @@
           <t>Precio conjunto 12.950 para todo; subvenciones a éxito según documento adjunto no incluido (pct desconocido)</t>
         </is>
       </c>
-      <c r="S58" s="2" t="inlineStr">
+      <c r="S58" s="2" t="n"/>
+      <c r="T58" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T58" s="2" t="inlineStr"/>
-      <c r="U58" s="4" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -5395,13 +5458,14 @@
           <t>Importes en la firmada: Tramitacion subvenciones accesibilidad y eficiencia (IEE, libro, CEE incluidos) 4% a exito</t>
         </is>
       </c>
-      <c r="S59" s="2" t="inlineStr">
+      <c r="S59" s="2" t="n"/>
+      <c r="T59" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T59" s="2" t="inlineStr"/>
-      <c r="U59" s="4" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -5484,13 +5548,14 @@
           <t>Los 3.760 cubren en una línea toma de datos, proyecto y DF</t>
         </is>
       </c>
-      <c r="S60" s="2" t="inlineStr">
+      <c r="S60" s="2" t="n"/>
+      <c r="T60" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T60" s="2" t="inlineStr"/>
-      <c r="U60" s="4" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -5569,13 +5634,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S61" s="2" t="inlineStr">
+      <c r="S61" s="2" t="n"/>
+      <c r="T61" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T61" s="2" t="inlineStr"/>
-      <c r="U61" s="4" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -5655,13 +5721,14 @@
           <t>Factura a CEGA ESTRUCTURAS PREFABRICADAS (pagador empresa), no a la comunidad</t>
         </is>
       </c>
-      <c r="S62" s="2" t="inlineStr">
+      <c r="S62" s="2" t="n"/>
+      <c r="T62" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T62" s="2" t="inlineStr"/>
-      <c r="U62" s="4" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -5741,13 +5808,14 @@
           <t>Factura a CEGA ESTRUCTURAS PREFABRICADAS (pagador empresa), no a la comunidad</t>
         </is>
       </c>
-      <c r="S63" s="2" t="inlineStr">
+      <c r="S63" s="2" t="n"/>
+      <c r="T63" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T63" s="2" t="inlineStr"/>
-      <c r="U63" s="4" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -5829,13 +5897,14 @@
           <t>Los 2.360 cubren en una línea toma de datos y proyecto; 'proyecto de Accesibilidad (Rampa)'</t>
         </is>
       </c>
-      <c r="S64" s="2" t="inlineStr">
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T64" s="2" t="inlineStr"/>
-      <c r="U64" s="4" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="4" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -5914,13 +5983,14 @@
           <t>Conforme SCHINDLER con Nº pedido</t>
         </is>
       </c>
-      <c r="S65" s="2" t="inlineStr">
+      <c r="S65" s="2" t="n"/>
+      <c r="T65" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T65" s="2" t="inlineStr"/>
-      <c r="U65" s="4" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -6003,13 +6073,14 @@
           <t>Proyecto+licencia+DO+CFO con precio conjunto 3.500; CSS 500 aparte. Datos de facturación de ROSERSESE SERVICIOS INTEGRALES SL (Valencia), CIF relleno con el nombre</t>
         </is>
       </c>
-      <c r="S66" s="2" t="inlineStr">
+      <c r="S66" s="2" t="n"/>
+      <c r="T66" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T66" s="2" t="inlineStr"/>
-      <c r="U66" s="4" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="4" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -6099,13 +6170,14 @@
           <t>Dos hojas en un fichero (proyecto ascensor 4.500 + subvenciones 1.980); los 2.260 cubren en una línea toma de datos, proyecto y DF</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr">
+      <c r="S67" s="2" t="n"/>
+      <c r="T67" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T67" s="2" t="inlineStr"/>
-      <c r="U67" s="4" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="4" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -6188,13 +6260,14 @@
           <t>Proyecto valorado en 17.620 + iva pero gratuito a cambio de cesión de CAES; total = cesión de ahorros + 3% subvención</t>
         </is>
       </c>
-      <c r="S68" s="2" t="inlineStr">
+      <c r="S68" s="2" t="n"/>
+      <c r="T68" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T68" s="2" t="inlineStr"/>
-      <c r="U68" s="4" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="4" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -6273,13 +6346,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S69" s="2" t="inlineStr">
+      <c r="S69" s="2" t="n"/>
+      <c r="T69" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T69" s="2" t="inlineStr"/>
-      <c r="U69" s="4" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="4" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -6362,13 +6436,14 @@
           <t>Los 4.760 cubren en una línea toma de datos, proyecto y DF</t>
         </is>
       </c>
-      <c r="S70" s="2" t="inlineStr">
+      <c r="S70" s="2" t="n"/>
+      <c r="T70" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T70" s="2" t="inlineStr"/>
-      <c r="U70" s="4" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -6444,13 +6519,14 @@
         </is>
       </c>
       <c r="R71" s="2" t="n"/>
-      <c r="S71" s="2" t="inlineStr">
+      <c r="S71" s="2" t="n"/>
+      <c r="T71" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T71" s="2" t="inlineStr"/>
-      <c r="U71" s="4" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="4" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -6531,13 +6607,14 @@
           <t>Precio conjunto 2.200 sin desglose</t>
         </is>
       </c>
-      <c r="S72" s="2" t="inlineStr">
+      <c r="S72" s="2" t="n"/>
+      <c r="T72" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T72" s="2" t="inlineStr"/>
-      <c r="U72" s="4" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -6619,13 +6696,14 @@
           <t>Otra Documentación Técnica sin bloque concreto; incluye monetización de ahorros energéticos</t>
         </is>
       </c>
-      <c r="S73" s="2" t="inlineStr">
+      <c r="S73" s="2" t="n"/>
+      <c r="T73" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T73" s="2" t="inlineStr"/>
-      <c r="U73" s="4" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="4" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -6700,13 +6778,14 @@
         </is>
       </c>
       <c r="R74" s="2" t="n"/>
-      <c r="S74" s="2" t="inlineStr">
+      <c r="S74" s="2" t="n"/>
+      <c r="T74" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T74" s="2" t="inlineStr"/>
-      <c r="U74" s="4" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -6785,13 +6864,14 @@
         </is>
       </c>
       <c r="R75" s="2" t="n"/>
-      <c r="S75" s="2" t="inlineStr">
+      <c r="S75" s="2" t="n"/>
+      <c r="T75" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T75" s="2" t="inlineStr"/>
-      <c r="U75" s="4" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -6875,13 +6955,14 @@
           <t>Los importes no cuadran: 6.970 + 490 = 7.460, pero TOTAL HONORARIOS 8.850. La línea de 6.970 junta toma de datos y proyecto. Hay otra hoja (E175) para la misma dirección con oferta CAES</t>
         </is>
       </c>
-      <c r="S76" s="2" t="inlineStr">
+      <c r="S76" s="2" t="n"/>
+      <c r="T76" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T76" s="2" t="inlineStr"/>
-      <c r="U76" s="4" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="4" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -6966,13 +7047,14 @@
           <t>Honorarios RD 25.530 rebajados a 8.500 con cesión de CAES; la forma de pago dice 2 x 4.500 (= 9.000), no cuadra con 8.500. Misma dirección que E174</t>
         </is>
       </c>
-      <c r="S77" s="2" t="inlineStr">
+      <c r="S77" s="2" t="n"/>
+      <c r="T77" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T77" s="2" t="inlineStr"/>
-      <c r="U77" s="4" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -7055,13 +7137,14 @@
           <t>Proyecto valorado en 17.620 + iva pero gratuito a cambio de cesión de CAES; total = cesión de ahorros + 3% subvención</t>
         </is>
       </c>
-      <c r="S78" s="2" t="inlineStr">
+      <c r="S78" s="2" t="n"/>
+      <c r="T78" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T78" s="2" t="inlineStr"/>
-      <c r="U78" s="4" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="4" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -7154,13 +7237,14 @@
           <t>Dos hojas en un fichero (proyecto conjunto + subvenciones a éxito 3,7%); total 14.670 con 12% de descuento por proyecto conjunto = 12.909,60 (total_base con descuento; importes de línea sin descontar); 'Mejora de envolvente térmica' sin decir si es SATE; línea de 740 'Memoria y Proyecto conjunto y visado' SIN CASAR</t>
         </is>
       </c>
-      <c r="S79" s="2" t="inlineStr">
+      <c r="S79" s="2" t="n"/>
+      <c r="T79" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T79" s="2" t="inlineStr"/>
-      <c r="U79" s="4" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="4" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -7236,13 +7320,14 @@
         </is>
       </c>
       <c r="R80" s="2" t="n"/>
-      <c r="S80" s="2" t="inlineStr">
+      <c r="S80" s="2" t="n"/>
+      <c r="T80" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T80" s="2" t="inlineStr"/>
-      <c r="U80" s="4" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="4" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -7326,13 +7411,14 @@
           <t>Total sin descuento 22.830 menos 16.830 CAES = 6.000; desglose de lista marcado incluido. Sin membrete</t>
         </is>
       </c>
-      <c r="S81" s="2" t="inlineStr">
+      <c r="S81" s="2" t="n"/>
+      <c r="T81" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T81" s="2" t="inlineStr"/>
-      <c r="U81" s="4" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="4" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -7385,13 +7471,14 @@
           <t>Importes en la firmada: Tramitación subvención accesibilidad 1.980; proyecto 2 ascensores y plataforma elevadora (escaneado, PBE, licencia, DO) 11.500</t>
         </is>
       </c>
-      <c r="S82" s="2" t="inlineStr">
+      <c r="S82" s="2" t="n"/>
+      <c r="T82" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T82" s="2" t="inlineStr"/>
-      <c r="U82" s="4" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="4" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -7474,13 +7561,14 @@
           <t>Precio conjunto 3.936 para instalación de elevador</t>
         </is>
       </c>
-      <c r="S83" s="2" t="inlineStr">
+      <c r="S83" s="2" t="n"/>
+      <c r="T83" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T83" s="2" t="inlineStr"/>
-      <c r="U83" s="4" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -7560,13 +7648,14 @@
           <t>Precio conjunto 4.800 (sin indicar IVA). Conforme Schindler. Sin forma de pago</t>
         </is>
       </c>
-      <c r="S84" s="2" t="inlineStr">
+      <c r="S84" s="2" t="n"/>
+      <c r="T84" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T84" s="2" t="inlineStr"/>
-      <c r="U84" s="4" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -7648,13 +7737,14 @@
           <t>Precio conjunto 4.800. Proyecto global de accesibilidad (peldaño de portal, desnivel 1,05 m, peldaño entreplanta) con aprobación de Patrimonio</t>
         </is>
       </c>
-      <c r="S85" s="2" t="inlineStr">
+      <c r="S85" s="2" t="n"/>
+      <c r="T85" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T85" s="2" t="inlineStr"/>
-      <c r="U85" s="4" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -7699,13 +7789,14 @@
         </is>
       </c>
       <c r="R86" s="2" t="n"/>
-      <c r="S86" s="2" t="inlineStr">
+      <c r="S86" s="2" t="n"/>
+      <c r="T86" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T86" s="2" t="inlineStr"/>
-      <c r="U86" s="4" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -7795,13 +7886,14 @@
           <t>Dos hojas en un fichero (proyecto ascensor 4.500 precio conjunto sin desglose + subvenciones 1.980)</t>
         </is>
       </c>
-      <c r="S87" s="2" t="inlineStr">
+      <c r="S87" s="2" t="n"/>
+      <c r="T87" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T87" s="2" t="inlineStr"/>
-      <c r="U87" s="4" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -7881,13 +7973,14 @@
           <t>Modificación completa de un proyecto de ascensor ya existente</t>
         </is>
       </c>
-      <c r="S88" s="2" t="inlineStr">
+      <c r="S88" s="2" t="n"/>
+      <c r="T88" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T88" s="2" t="inlineStr"/>
-      <c r="U88" s="4" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -7940,13 +8033,14 @@
           <t>Importes en la firmada: Tramitacion subvencion accesibilidad (con IEE si falta) 1.980</t>
         </is>
       </c>
-      <c r="S89" s="2" t="inlineStr">
+      <c r="S89" s="2" t="n"/>
+      <c r="T89" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T89" s="2" t="inlineStr"/>
-      <c r="U89" s="4" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -7999,13 +8093,14 @@
           <t>Importes en la firmada: Proyecto accesibilidad 3 ascensores con bajada a sótano (proyecto, licencia/DR, CFO): 2.800 x 3 ascensores = 8.400 + IVA</t>
         </is>
       </c>
-      <c r="S90" s="2" t="inlineStr">
+      <c r="S90" s="2" t="n"/>
+      <c r="T90" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T90" s="2" t="inlineStr"/>
-      <c r="U90" s="4" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="4" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -8081,13 +8176,14 @@
         </is>
       </c>
       <c r="R91" s="2" t="n"/>
-      <c r="S91" s="2" t="inlineStr">
+      <c r="S91" s="2" t="n"/>
+      <c r="T91" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T91" s="2" t="inlineStr"/>
-      <c r="U91" s="4" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="4" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -8180,13 +8276,14 @@
           <t>Dos hojas en un fichero (proyecto conjunto + subvenciones a éxito 3,7%); total 14.670 con 12% de descuento por proyecto conjunto = 12.909,60 (total_base con descuento; importes de línea sin descontar); 'Mejora de envolvente térmica' sin decir si es SATE; línea de 740 'Memoria y Proyecto conjunto y visado' SIN CASAR</t>
         </is>
       </c>
-      <c r="S92" s="2" t="inlineStr">
+      <c r="S92" s="2" t="n"/>
+      <c r="T92" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T92" s="2" t="inlineStr"/>
-      <c r="U92" s="4" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="4" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -8265,13 +8362,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S93" s="2" t="inlineStr">
+      <c r="S93" s="2" t="n"/>
+      <c r="T93" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T93" s="2" t="inlineStr"/>
-      <c r="U93" s="4" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="4" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -8357,13 +8455,14 @@
           <t>Precio conjunto 5.500 sin desglose. La hoja fecha 8-oct-2024 pero el título del fichero dice 18/03/2025 (modificado 31-mar-2025). Va con E246 (subvención, misma dirección)</t>
         </is>
       </c>
-      <c r="S94" s="2" t="inlineStr">
+      <c r="S94" s="2" t="n"/>
+      <c r="T94" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T94" s="2" t="inlineStr"/>
-      <c r="U94" s="4" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="4" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -8447,13 +8546,14 @@
           <t>Solo tramo fijo, sin porcentaje a éxito. IEE incluido solo si no hay previo válido. La hoja fecha 8-oct-2024 pero el título dice 18/03/2025. Va con E245 (proyecto, misma dirección)</t>
         </is>
       </c>
-      <c r="S95" s="2" t="inlineStr">
+      <c r="S95" s="2" t="n"/>
+      <c r="T95" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T95" s="2" t="inlineStr"/>
-      <c r="U95" s="4" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="4" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -8538,13 +8638,14 @@
           <t>Total sin descuento 28.690 menos 10.508,18 CAES = 18.181,82; desglose de lista marcado incluido. Hay otra hoja (E160) para la misma dirección, solo envolvente, de 17-feb-2025. Sin membrete</t>
         </is>
       </c>
-      <c r="S96" s="2" t="inlineStr">
+      <c r="S96" s="2" t="n"/>
+      <c r="T96" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T96" s="2" t="inlineStr"/>
-      <c r="U96" s="4" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="4" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -8632,13 +8733,14 @@
           <t>Sin descuento: proyecto 18.000 + LEE 1.900 + IEE 950 = 20.850. La tabla pone 'TOTAL 9.930 + 21% iva = 11.910', que no cuadra; 11.910 = 9.930 + 1.980 sin IVA. Misma dirección que E159 (18-feb-2025, con ascensor)</t>
         </is>
       </c>
-      <c r="S97" s="2" t="inlineStr">
+      <c r="S97" s="2" t="n"/>
+      <c r="T97" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T97" s="2" t="inlineStr"/>
-      <c r="U97" s="4" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="4" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -8713,13 +8815,14 @@
         </is>
       </c>
       <c r="R98" s="2" t="n"/>
-      <c r="S98" s="2" t="inlineStr">
+      <c r="S98" s="2" t="n"/>
+      <c r="T98" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T98" s="2" t="inlineStr"/>
-      <c r="U98" s="4" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="4" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -8795,13 +8898,14 @@
         </is>
       </c>
       <c r="R99" s="2" t="n"/>
-      <c r="S99" s="2" t="inlineStr">
+      <c r="S99" s="2" t="n"/>
+      <c r="T99" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T99" s="2" t="inlineStr"/>
-      <c r="U99" s="4" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="4" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -8876,13 +8980,14 @@
         </is>
       </c>
       <c r="R100" s="2" t="n"/>
-      <c r="S100" s="2" t="inlineStr">
+      <c r="S100" s="2" t="n"/>
+      <c r="T100" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T100" s="2" t="inlineStr"/>
-      <c r="U100" s="4" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -8958,13 +9063,14 @@
         </is>
       </c>
       <c r="R101" s="2" t="n"/>
-      <c r="S101" s="2" t="inlineStr">
+      <c r="S101" s="2" t="n"/>
+      <c r="T101" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T101" s="2" t="inlineStr"/>
-      <c r="U101" s="4" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="4" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -9048,13 +9154,14 @@
           <t>El importe 4.050,79 cubre a la vez toma de datos, modelado 3D, proyecto básico y de ejecución y visado COAM (casado como REDACCION PROYECTO, revisar). Hoja gemela de PLAZA DEL PAULAR 2 (E249)</t>
         </is>
       </c>
-      <c r="S102" s="2" t="inlineStr">
+      <c r="S102" s="2" t="n"/>
+      <c r="T102" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T102" s="2" t="inlineStr"/>
-      <c r="U102" s="4" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="4" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -9138,13 +9245,14 @@
           <t>El importe 4.050,79 cubre a la vez toma de datos, modelado 3D, proyecto básico y de ejecución y visado COAM (casado como REDACCION PROYECTO, revisar). Pago 50% a la entrega de proyecto pero mantiene la cláusula de devolución si se deniega la licencia. Hoja gemela de PLAZA DEL PAULAR 1 (E248)</t>
         </is>
       </c>
-      <c r="S103" s="2" t="inlineStr">
+      <c r="S103" s="2" t="n"/>
+      <c r="T103" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T103" s="2" t="inlineStr"/>
-      <c r="U103" s="4" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="4" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -9223,13 +9331,14 @@
           <t>Otra Documentación Técnica sin bloque concreto (documentación requerida por cada convocatoria)</t>
         </is>
       </c>
-      <c r="S104" s="2" t="inlineStr">
+      <c r="S104" s="2" t="n"/>
+      <c r="T104" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T104" s="2" t="inlineStr"/>
-      <c r="U104" s="4" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="4" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -9309,13 +9418,14 @@
           <t>Precio conjunto 3.000 para DF y CSS</t>
         </is>
       </c>
-      <c r="S105" s="2" t="inlineStr">
+      <c r="S105" s="2" t="n"/>
+      <c r="T105" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T105" s="2" t="inlineStr"/>
-      <c r="U105" s="4" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr"/>
+      <c r="V105" s="4" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -9397,13 +9507,14 @@
           <t>Precio conjunto 2.571,40 para instalación de elevador vertical</t>
         </is>
       </c>
-      <c r="S106" s="2" t="inlineStr">
+      <c r="S106" s="2" t="n"/>
+      <c r="T106" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T106" s="2" t="inlineStr"/>
-      <c r="U106" s="4" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr"/>
+      <c r="V106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -9483,13 +9594,14 @@
           <t>Firma 'Conforme el cliente' sin decir comunidad; el texto dice Comunidad de Propietarios</t>
         </is>
       </c>
-      <c r="S107" s="2" t="inlineStr">
+      <c r="S107" s="2" t="n"/>
+      <c r="T107" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T107" s="2" t="inlineStr"/>
-      <c r="U107" s="4" t="inlineStr"/>
+      <c r="U107" s="2" t="inlineStr"/>
+      <c r="V107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -9574,13 +9686,14 @@
           <t>Precio conjunto 5.500 sin desglose</t>
         </is>
       </c>
-      <c r="S108" s="2" t="inlineStr">
+      <c r="S108" s="2" t="n"/>
+      <c r="T108" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T108" s="2" t="inlineStr"/>
-      <c r="U108" s="4" t="inlineStr"/>
+      <c r="U108" s="2" t="inlineStr"/>
+      <c r="V108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -9656,13 +9769,14 @@
         </is>
       </c>
       <c r="R109" s="2" t="n"/>
-      <c r="S109" s="2" t="inlineStr">
+      <c r="S109" s="2" t="n"/>
+      <c r="T109" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T109" s="2" t="inlineStr"/>
-      <c r="U109" s="4" t="inlineStr"/>
+      <c r="U109" s="2" t="inlineStr"/>
+      <c r="V109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -9748,13 +9862,14 @@
           <t>Precio conjunto 6.900 sin desglose. Título del fichero con '(3) (1)': posible copia/versión</t>
         </is>
       </c>
-      <c r="S110" s="2" t="inlineStr">
+      <c r="S110" s="2" t="n"/>
+      <c r="T110" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T110" s="2" t="inlineStr"/>
-      <c r="U110" s="4" t="inlineStr"/>
+      <c r="U110" s="2" t="inlineStr"/>
+      <c r="V110" s="4" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -9833,13 +9948,14 @@
           <t>Renovación consecutiva de subvención (oferta especial)</t>
         </is>
       </c>
-      <c r="S111" s="2" t="inlineStr">
+      <c r="S111" s="2" t="n"/>
+      <c r="T111" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T111" s="2" t="inlineStr"/>
-      <c r="U111" s="4" t="inlineStr"/>
+      <c r="U111" s="2" t="inlineStr"/>
+      <c r="V111" s="4" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -9892,13 +10008,14 @@
           <t>Importes en la firmada: Proyecto rehabilitación envolvente térmica con cesión de CAES: 8.900 total con descuento (sin descuento 22.830: proyecto 18.000, LE 1.900, IEE 950, subvenciones 1.980; descuento -13.930)</t>
         </is>
       </c>
-      <c r="S112" s="2" t="inlineStr">
+      <c r="S112" s="2" t="n"/>
+      <c r="T112" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T112" s="2" t="inlineStr"/>
-      <c r="U112" s="4" t="inlineStr"/>
+      <c r="U112" s="2" t="inlineStr"/>
+      <c r="V112" s="4" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -9943,13 +10060,14 @@
         </is>
       </c>
       <c r="R113" s="2" t="n"/>
-      <c r="S113" s="2" t="inlineStr">
+      <c r="S113" s="2" t="n"/>
+      <c r="T113" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T113" s="2" t="inlineStr"/>
-      <c r="U113" s="4" t="inlineStr"/>
+      <c r="U113" s="2" t="inlineStr"/>
+      <c r="V113" s="4" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -10036,13 +10154,14 @@
           <t>Proyecto 33.600 sin descuento; descuento CAES -26.680 aplicado al proyecto (6.920). Total sin descuento 41.550</t>
         </is>
       </c>
-      <c r="S114" s="2" t="inlineStr">
+      <c r="S114" s="2" t="n"/>
+      <c r="T114" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T114" s="2" t="inlineStr"/>
-      <c r="U114" s="4" t="inlineStr"/>
+      <c r="U114" s="2" t="inlineStr"/>
+      <c r="V114" s="4" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -10087,13 +10206,14 @@
         </is>
       </c>
       <c r="R115" s="2" t="n"/>
-      <c r="S115" s="2" t="inlineStr">
+      <c r="S115" s="2" t="n"/>
+      <c r="T115" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T115" s="2" t="inlineStr"/>
-      <c r="U115" s="4" t="inlineStr"/>
+      <c r="U115" s="2" t="inlineStr"/>
+      <c r="V115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -10169,13 +10289,14 @@
         </is>
       </c>
       <c r="R116" s="2" t="n"/>
-      <c r="S116" s="2" t="inlineStr">
+      <c r="S116" s="2" t="n"/>
+      <c r="T116" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T116" s="2" t="inlineStr"/>
-      <c r="U116" s="4" t="inlineStr"/>
+      <c r="U116" s="2" t="inlineStr"/>
+      <c r="V116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -10228,13 +10349,14 @@
           <t>Importes en la firmada: Elaboracion IEE (con CEE) 950</t>
         </is>
       </c>
-      <c r="S117" s="2" t="inlineStr">
+      <c r="S117" s="2" t="n"/>
+      <c r="T117" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T117" s="2" t="inlineStr"/>
-      <c r="U117" s="4" t="inlineStr"/>
+      <c r="U117" s="2" t="inlineStr"/>
+      <c r="V117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -10319,13 +10441,14 @@
           <t>Precio conjunto 14.600 sin desglose</t>
         </is>
       </c>
-      <c r="S118" s="2" t="inlineStr">
+      <c r="S118" s="2" t="n"/>
+      <c r="T118" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T118" s="2" t="inlineStr"/>
-      <c r="U118" s="4" t="inlineStr"/>
+      <c r="U118" s="2" t="inlineStr"/>
+      <c r="V118" s="4" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -10409,13 +10532,14 @@
           <t>Formato antiguo; sin tramo a éxito</t>
         </is>
       </c>
-      <c r="S119" s="2" t="inlineStr">
+      <c r="S119" s="2" t="n"/>
+      <c r="T119" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T119" s="2" t="inlineStr"/>
-      <c r="U119" s="4" t="inlineStr"/>
+      <c r="U119" s="2" t="inlineStr"/>
+      <c r="V119" s="4" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -10496,13 +10620,14 @@
           <t>Eliminación de barreras: bajada a cota cero de ascensor y modificación del primer tramo de escalera y del portal</t>
         </is>
       </c>
-      <c r="S120" s="2" t="inlineStr">
+      <c r="S120" s="2" t="n"/>
+      <c r="T120" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T120" s="2" t="inlineStr"/>
-      <c r="U120" s="4" t="inlineStr"/>
+      <c r="U120" s="2" t="inlineStr"/>
+      <c r="V120" s="4" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -10586,13 +10711,14 @@
           <t>IEE solo si no hay uno previo válido</t>
         </is>
       </c>
-      <c r="S121" s="2" t="inlineStr">
+      <c r="S121" s="2" t="n"/>
+      <c r="T121" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T121" s="2" t="inlineStr"/>
-      <c r="U121" s="4" t="inlineStr"/>
+      <c r="U121" s="2" t="inlineStr"/>
+      <c r="V121" s="4" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -10671,13 +10797,14 @@
           <t>No dice de qué obra es la CSS</t>
         </is>
       </c>
-      <c r="S122" s="2" t="inlineStr">
+      <c r="S122" s="2" t="n"/>
+      <c r="T122" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T122" s="2" t="inlineStr"/>
-      <c r="U122" s="4" t="inlineStr"/>
+      <c r="U122" s="2" t="inlineStr"/>
+      <c r="V122" s="4" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -10753,13 +10880,14 @@
         </is>
       </c>
       <c r="R123" s="2" t="n"/>
-      <c r="S123" s="2" t="inlineStr">
+      <c r="S123" s="2" t="n"/>
+      <c r="T123" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T123" s="2" t="inlineStr"/>
-      <c r="U123" s="4" t="inlineStr"/>
+      <c r="U123" s="2" t="inlineStr"/>
+      <c r="V123" s="4" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -10834,13 +10962,14 @@
         </is>
       </c>
       <c r="R124" s="2" t="n"/>
-      <c r="S124" s="2" t="inlineStr">
+      <c r="S124" s="2" t="n"/>
+      <c r="T124" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T124" s="2" t="inlineStr"/>
-      <c r="U124" s="4" t="inlineStr"/>
+      <c r="U124" s="2" t="inlineStr"/>
+      <c r="V124" s="4" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -10885,13 +11014,14 @@
         </is>
       </c>
       <c r="R125" s="2" t="n"/>
-      <c r="S125" s="2" t="inlineStr">
+      <c r="S125" s="2" t="n"/>
+      <c r="T125" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T125" s="2" t="inlineStr"/>
-      <c r="U125" s="4" t="inlineStr"/>
+      <c r="U125" s="2" t="inlineStr"/>
+      <c r="V125" s="4" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -10969,13 +11099,14 @@
           <t>Importe = 1,5% del precio de la contrata (no es importe fijo ni % a éxito). Obra de 'Plataforma o Rampa', sin concretar</t>
         </is>
       </c>
-      <c r="S126" s="2" t="inlineStr">
+      <c r="S126" s="2" t="n"/>
+      <c r="T126" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T126" s="2" t="inlineStr"/>
-      <c r="U126" s="4" t="inlineStr"/>
+      <c r="U126" s="2" t="inlineStr"/>
+      <c r="V126" s="4" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -11062,13 +11193,14 @@
           <t>Precio conjunto 3.175 sin desglose</t>
         </is>
       </c>
-      <c r="S127" s="2" t="inlineStr">
+      <c r="S127" s="2" t="n"/>
+      <c r="T127" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T127" s="2" t="inlineStr"/>
-      <c r="U127" s="4" t="inlineStr"/>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="4" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -11147,13 +11279,14 @@
           <t>Misma dirección y fecha que E095 (proyecto de accesibilidad portal)</t>
         </is>
       </c>
-      <c r="S128" s="2" t="inlineStr">
+      <c r="S128" s="2" t="n"/>
+      <c r="T128" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T128" s="2" t="inlineStr"/>
-      <c r="U128" s="4" t="inlineStr"/>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="4" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -11229,13 +11362,14 @@
         </is>
       </c>
       <c r="R129" s="2" t="n"/>
-      <c r="S129" s="2" t="inlineStr">
+      <c r="S129" s="2" t="n"/>
+      <c r="T129" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T129" s="2" t="inlineStr"/>
-      <c r="U129" s="4" t="inlineStr"/>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="4" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -11310,13 +11444,14 @@
         </is>
       </c>
       <c r="R130" s="2" t="n"/>
-      <c r="S130" s="2" t="inlineStr">
+      <c r="S130" s="2" t="n"/>
+      <c r="T130" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T130" s="2" t="inlineStr"/>
-      <c r="U130" s="4" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="4" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -11399,13 +11534,14 @@
           <t>Oferta especial de renovación consecutiva (1.690)</t>
         </is>
       </c>
-      <c r="S131" s="2" t="inlineStr">
+      <c r="S131" s="2" t="n"/>
+      <c r="T131" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T131" s="2" t="inlineStr"/>
-      <c r="U131" s="4" t="inlineStr"/>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="4" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -11488,13 +11624,14 @@
           <t>Precio conjunto 7500 sin desglose por concepto; la lista salta al punto '5. Coordinación de Seguridad y Salud'</t>
         </is>
       </c>
-      <c r="S132" s="2" t="inlineStr">
+      <c r="S132" s="2" t="n"/>
+      <c r="T132" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T132" s="2" t="inlineStr"/>
-      <c r="U132" s="4" t="inlineStr"/>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="4" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -11578,13 +11715,14 @@
           <t>Formato antiguo 'Propuesta de Honorarios'; IEE incluido solo si no hay uno previo válido; sin tramo variable</t>
         </is>
       </c>
-      <c r="S133" s="2" t="inlineStr">
+      <c r="S133" s="2" t="n"/>
+      <c r="T133" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T133" s="2" t="inlineStr"/>
-      <c r="U133" s="4" t="inlineStr"/>
+      <c r="U133" s="2" t="inlineStr"/>
+      <c r="V133" s="4" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -11629,13 +11767,14 @@
         </is>
       </c>
       <c r="R134" s="2" t="n"/>
-      <c r="S134" s="2" t="inlineStr">
+      <c r="S134" s="2" t="n"/>
+      <c r="T134" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T134" s="2" t="inlineStr"/>
-      <c r="U134" s="4" t="inlineStr"/>
+      <c r="U134" s="2" t="inlineStr"/>
+      <c r="V134" s="4" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -11718,13 +11857,14 @@
           <t>La hoja no pone municipio (el título dice Madrid); tramo fijo 2.225 €, distinto del habitual 1.980 €</t>
         </is>
       </c>
-      <c r="S135" s="2" t="inlineStr">
+      <c r="S135" s="2" t="n"/>
+      <c r="T135" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T135" s="2" t="inlineStr"/>
-      <c r="U135" s="4" t="inlineStr"/>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="4" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -11807,13 +11947,14 @@
           <t>La dirección no lleva municipio en el cuerpo (título: MADRID)</t>
         </is>
       </c>
-      <c r="S136" s="2" t="inlineStr">
+      <c r="S136" s="2" t="n"/>
+      <c r="T136" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T136" s="2" t="inlineStr"/>
-      <c r="U136" s="4" t="inlineStr"/>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="4" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -11906,13 +12047,14 @@
           <t>Honorarios de proyecto 7.950 en precio conjunto (sin desglose) + subvención 1.980 fijo; total_base = 7.950 + 1.980</t>
         </is>
       </c>
-      <c r="S137" s="2" t="inlineStr">
+      <c r="S137" s="2" t="n"/>
+      <c r="T137" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T137" s="2" t="inlineStr"/>
-      <c r="U137" s="4" t="inlineStr"/>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="4" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -11994,13 +12136,14 @@
           <t>Ascensor por patio; 'Conforme el cliente' sin nombre: no se sabe si es comunidad o empresa; precio conjunto 6.900; firma digital de 20-06-2025 posterior a la fecha de la hoja</t>
         </is>
       </c>
-      <c r="S138" s="2" t="inlineStr">
+      <c r="S138" s="2" t="n"/>
+      <c r="T138" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T138" s="2" t="inlineStr"/>
-      <c r="U138" s="4" t="inlineStr"/>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="4" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -12080,13 +12223,14 @@
           <t>Firma 'Conforme el cliente' sin decir comunidad (va con el proyecto E219); firma digital de 20-06-2025 posterior a la fecha de la hoja</t>
         </is>
       </c>
-      <c r="S139" s="2" t="inlineStr">
+      <c r="S139" s="2" t="n"/>
+      <c r="T139" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T139" s="2" t="inlineStr"/>
-      <c r="U139" s="4" t="inlineStr"/>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="4" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -12178,13 +12322,14 @@
           <t>Presupuesto modificado (según título); precio conjunto de proyecto 4.500 sin desglose; IEE, LEE y CEE sin precio, no se sabe si van en proyecto o en subvención</t>
         </is>
       </c>
-      <c r="S140" s="2" t="inlineStr">
+      <c r="S140" s="2" t="n"/>
+      <c r="T140" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T140" s="2" t="inlineStr"/>
-      <c r="U140" s="4" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="4" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -12260,13 +12405,14 @@
         </is>
       </c>
       <c r="R141" s="2" t="n"/>
-      <c r="S141" s="2" t="inlineStr">
+      <c r="S141" s="2" t="n"/>
+      <c r="T141" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T141" s="2" t="inlineStr"/>
-      <c r="U141" s="4" t="inlineStr"/>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="4" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -12357,13 +12503,14 @@
           <t>Tramitación de CAES (632) cobrada aparte, no es descuento por cesión: SIN CASAR. Fase 2 (subvenciones, IEE, LEEx) solo informativa, a contratar después; no incluida</t>
         </is>
       </c>
-      <c r="S142" s="2" t="inlineStr">
+      <c r="S142" s="2" t="n"/>
+      <c r="T142" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T142" s="2" t="inlineStr"/>
-      <c r="U142" s="4" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="4" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -12450,13 +12597,14 @@
           <t>Gestión de CAES (408) cobrada aparte, no es descuento por cesión: SIN CASAR. Fase 2 (subvenciones, IEE, LEEx) solo informativa, a contratar después; no incluida</t>
         </is>
       </c>
-      <c r="S143" s="2" t="inlineStr">
+      <c r="S143" s="2" t="n"/>
+      <c r="T143" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T143" s="2" t="inlineStr"/>
-      <c r="U143" s="4" t="inlineStr"/>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="4" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -12548,13 +12696,14 @@
           <t>Modificación de condiciones (título). Contrato supeditado a consulta previa sin coste de viabilidad del ascensor interior: si es negativa, se cancela. Proyecto 5.900 € conjunto + subvención 1.980 €; total_base sumado</t>
         </is>
       </c>
-      <c r="S144" s="2" t="inlineStr">
+      <c r="S144" s="2" t="n"/>
+      <c r="T144" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T144" s="2" t="inlineStr"/>
-      <c r="U144" s="4" t="inlineStr"/>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="4" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -12599,13 +12748,14 @@
         </is>
       </c>
       <c r="R145" s="2" t="n"/>
-      <c r="S145" s="2" t="inlineStr">
+      <c r="S145" s="2" t="n"/>
+      <c r="T145" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T145" s="2" t="inlineStr"/>
-      <c r="U145" s="4" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="4" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -12699,13 +12849,14 @@
           <t>Texto empieza cortado: sin dirección, sin fecha ni cabecera; tipo de SATE no especificado; servicios descritos sin precio propio se marcan incluidos</t>
         </is>
       </c>
-      <c r="S146" s="2" t="inlineStr">
+      <c r="S146" s="2" t="n"/>
+      <c r="T146" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T146" s="2" t="inlineStr"/>
-      <c r="U146" s="4" t="inlineStr"/>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="4" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -12788,13 +12939,14 @@
           <t>Modificación de un proyecto existente, no dice de qué obra; sin tipo en el catálogo</t>
         </is>
       </c>
-      <c r="S147" s="2" t="inlineStr">
+      <c r="S147" s="2" t="n"/>
+      <c r="T147" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T147" s="2" t="inlineStr"/>
-      <c r="U147" s="4" t="inlineStr"/>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="4" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -12877,13 +13029,14 @@
           <t>Conforme FAIN: el pagador es FAIN (ascensorista)</t>
         </is>
       </c>
-      <c r="S148" s="2" t="inlineStr">
+      <c r="S148" s="2" t="n"/>
+      <c r="T148" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T148" s="2" t="inlineStr"/>
-      <c r="U148" s="4" t="inlineStr"/>
+      <c r="U148" s="2" t="inlineStr"/>
+      <c r="V148" s="4" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -12976,13 +13129,14 @@
           <t>Total 11.300 + IVA TACHADO; con cesión de CAES queda sin coste (descuento estimado -11.300), solo 3,5% de subvenciones nuevas (excluido lo ya concedido Next Generation). La obra no se nombra como SATE (dice 'proyecto de eficiencia energética ejecutado'); bloque SATE CON CESION DE CAES por el descuento CAES, revisar</t>
         </is>
       </c>
-      <c r="S149" s="2" t="inlineStr">
+      <c r="S149" s="2" t="n"/>
+      <c r="T149" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T149" s="2" t="inlineStr"/>
-      <c r="U149" s="4" t="inlineStr"/>
+      <c r="U149" s="2" t="inlineStr"/>
+      <c r="V149" s="4" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -13062,13 +13216,14 @@
         </is>
       </c>
       <c r="R150" s="2" t="n"/>
-      <c r="S150" s="2" t="inlineStr">
+      <c r="S150" s="2" t="n"/>
+      <c r="T150" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T150" s="2" t="inlineStr"/>
-      <c r="U150" s="4" t="inlineStr"/>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="4" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -13152,13 +13307,14 @@
           <t>Precio conjunto 850 para IEE + CEE</t>
         </is>
       </c>
-      <c r="S151" s="2" t="inlineStr">
+      <c r="S151" s="2" t="n"/>
+      <c r="T151" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T151" s="2" t="inlineStr"/>
-      <c r="U151" s="4" t="inlineStr"/>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="4" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -13246,13 +13402,14 @@
           <t>Precio conjunto 2.100 sin desglose</t>
         </is>
       </c>
-      <c r="S152" s="2" t="inlineStr">
+      <c r="S152" s="2" t="n"/>
+      <c r="T152" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T152" s="2" t="inlineStr"/>
-      <c r="U152" s="4" t="inlineStr"/>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="4" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -13339,13 +13496,14 @@
           <t>Precio conjunto 'Proyecto' 3.500 para proyecto, licencia, fin de obra y DF (sin desglose); sin toma de datos</t>
         </is>
       </c>
-      <c r="S153" s="2" t="inlineStr">
+      <c r="S153" s="2" t="n"/>
+      <c r="T153" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T153" s="2" t="inlineStr"/>
-      <c r="U153" s="4" t="inlineStr"/>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="4" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -13433,13 +13591,14 @@
           <t>Precio conjunto 4.000 sin desglose. El título del fichero dice 'PRY ACCESIBILIDAD', el texto dice instalación de ascensor</t>
         </is>
       </c>
-      <c r="S154" s="2" t="inlineStr">
+      <c r="S154" s="2" t="n"/>
+      <c r="T154" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T154" s="2" t="inlineStr"/>
-      <c r="U154" s="4" t="inlineStr"/>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="4" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -13484,13 +13643,14 @@
         </is>
       </c>
       <c r="R155" s="2" t="n"/>
-      <c r="S155" s="2" t="inlineStr">
+      <c r="S155" s="2" t="n"/>
+      <c r="T155" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T155" s="2" t="inlineStr"/>
-      <c r="U155" s="4" t="inlineStr"/>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="4" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -13573,13 +13733,14 @@
           <t>Es RENOVACIÓN de subvenciones (una presentación ante CAM y otra ante Ayuntamiento); sin tramo a éxito</t>
         </is>
       </c>
-      <c r="S156" s="2" t="inlineStr">
+      <c r="S156" s="2" t="n"/>
+      <c r="T156" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T156" s="2" t="inlineStr"/>
-      <c r="U156" s="4" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="4" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -13668,13 +13829,14 @@
           <t>Precio conjunto de proyecto 5.500 (1ª parte 3.300: proyecto, licencia, IEE; 2ª parte 2.200: fin de obra, CSS, DF) + subvención 1.980; sin toma de datos</t>
         </is>
       </c>
-      <c r="S157" s="2" t="inlineStr">
+      <c r="S157" s="2" t="n"/>
+      <c r="T157" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T157" s="2" t="inlineStr"/>
-      <c r="U157" s="4" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="4" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -13759,13 +13921,14 @@
           <t>IEE y LEE en el desglose sin precio propio: puestos como incluidos en el tramo fijo</t>
         </is>
       </c>
-      <c r="S158" s="2" t="inlineStr">
+      <c r="S158" s="2" t="n"/>
+      <c r="T158" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T158" s="2" t="inlineStr"/>
-      <c r="U158" s="4" t="inlineStr"/>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="4" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -13853,13 +14016,14 @@
           <t>Precio conjunto 5.700 sin desglose. Consulta vinculante: si se deniega el encargo no tiene coste; si con informe favorable no se hace el proyecto, cuesta 1.200 + IVA</t>
         </is>
       </c>
-      <c r="S159" s="2" t="inlineStr">
+      <c r="S159" s="2" t="n"/>
+      <c r="T159" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T159" s="2" t="inlineStr"/>
-      <c r="U159" s="4" t="inlineStr"/>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="4" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -13904,13 +14068,14 @@
         </is>
       </c>
       <c r="R160" s="2" t="n"/>
-      <c r="S160" s="2" t="inlineStr">
+      <c r="S160" s="2" t="n"/>
+      <c r="T160" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T160" s="2" t="inlineStr"/>
-      <c r="U160" s="4" t="inlineStr"/>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="4" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -14004,13 +14169,14 @@
           <t>Total dado IVA INCLUIDO: 10.000 €; base calculada 10.000/1,21 = 8.264,46. Precio conjunto para todo, sin repartir; sin tramo a éxito de subvención</t>
         </is>
       </c>
-      <c r="S161" s="2" t="inlineStr">
+      <c r="S161" s="2" t="n"/>
+      <c r="T161" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T161" s="2" t="inlineStr"/>
-      <c r="U161" s="4" t="inlineStr"/>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="4" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -14110,13 +14276,14 @@
           <t>Precio único con descuento 8.265 € + 1.735,65 IVA, pero dice 10.000 € IVA incluido (no cuadra por 0,65 €); la cesión de CAEs solo sale en el título; 'envolvente térmica' casada como SATE envolvente completa; sin tramo variable de subvención</t>
         </is>
       </c>
-      <c r="S162" s="2" t="inlineStr">
+      <c r="S162" s="2" t="n"/>
+      <c r="T162" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T162" s="2" t="inlineStr"/>
-      <c r="U162" s="4" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="4" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -14195,13 +14362,14 @@
           <t>El título del fichero dice 'CSS FAIN' (posible pagador FAIN, ascensorista) pero la hoja no nombra pagador; sin forma de pago clara</t>
         </is>
       </c>
-      <c r="S163" s="2" t="inlineStr">
+      <c r="S163" s="2" t="n"/>
+      <c r="T163" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T163" s="2" t="inlineStr"/>
-      <c r="U163" s="4" t="inlineStr"/>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="4" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -14280,13 +14448,14 @@
         </is>
       </c>
       <c r="R164" s="2" t="n"/>
-      <c r="S164" s="2" t="inlineStr">
+      <c r="S164" s="2" t="n"/>
+      <c r="T164" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T164" s="2" t="inlineStr"/>
-      <c r="U164" s="4" t="inlineStr"/>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="4" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -14331,13 +14500,14 @@
         </is>
       </c>
       <c r="R165" s="2" t="n"/>
-      <c r="S165" s="2" t="inlineStr">
+      <c r="S165" s="2" t="n"/>
+      <c r="T165" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T165" s="2" t="inlineStr"/>
-      <c r="U165" s="4" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="4" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -14429,13 +14599,14 @@
           <t>'Sustitución de ascensor y bajada a cota cero': casado como Modificación asc. + Cota cero; precio conjunto 6.500 con subvención incluida sin tramo variable</t>
         </is>
       </c>
-      <c r="S166" s="2" t="inlineStr">
+      <c r="S166" s="2" t="n"/>
+      <c r="T166" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T166" s="2" t="inlineStr"/>
-      <c r="U166" s="4" t="inlineStr"/>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="4" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -14514,13 +14685,14 @@
         </is>
       </c>
       <c r="R167" s="2" t="n"/>
-      <c r="S167" s="2" t="inlineStr">
+      <c r="S167" s="2" t="n"/>
+      <c r="T167" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T167" s="2" t="inlineStr"/>
-      <c r="U167" s="4" t="inlineStr"/>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="4" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -14599,13 +14771,14 @@
         </is>
       </c>
       <c r="R168" s="2" t="n"/>
-      <c r="S168" s="2" t="inlineStr">
+      <c r="S168" s="2" t="n"/>
+      <c r="T168" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T168" s="2" t="inlineStr"/>
-      <c r="U168" s="4" t="inlineStr"/>
+      <c r="U168" s="2" t="inlineStr"/>
+      <c r="V168" s="4" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -14687,13 +14860,14 @@
           <t>Conforme FAIN con códigos de pedido: el pagador es FAIN (ascensorista)</t>
         </is>
       </c>
-      <c r="S169" s="2" t="inlineStr">
+      <c r="S169" s="2" t="n"/>
+      <c r="T169" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T169" s="2" t="inlineStr"/>
-      <c r="U169" s="4" t="inlineStr"/>
+      <c r="U169" s="2" t="inlineStr"/>
+      <c r="V169" s="4" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -14787,13 +14961,14 @@
           <t>Proyecto 2.500 € precio conjunto + CSS 800 € + subvención 1.980 € = 5.280 + IVA; subvención sin tramo variable (una presentación por entidad)</t>
         </is>
       </c>
-      <c r="S170" s="2" t="inlineStr">
+      <c r="S170" s="2" t="n"/>
+      <c r="T170" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T170" s="2" t="inlineStr"/>
-      <c r="U170" s="4" t="inlineStr"/>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="4" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -14887,13 +15062,14 @@
           <t>Proyecto 2.500 € precio conjunto + CSS 800 € + subvención 1.980 € = 5.280 + IVA; subvención sin tramo variable (una presentación por entidad)</t>
         </is>
       </c>
-      <c r="S171" s="2" t="inlineStr">
+      <c r="S171" s="2" t="n"/>
+      <c r="T171" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T171" s="2" t="inlineStr"/>
-      <c r="U171" s="4" t="inlineStr"/>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="4" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -14976,13 +15152,14 @@
           <t>Subvenciones de accesibilidad; sin tramo a éxito</t>
         </is>
       </c>
-      <c r="S172" s="2" t="inlineStr">
+      <c r="S172" s="2" t="n"/>
+      <c r="T172" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T172" s="2" t="inlineStr"/>
-      <c r="U172" s="4" t="inlineStr"/>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="4" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -15027,13 +15204,14 @@
         </is>
       </c>
       <c r="R173" s="2" t="n"/>
-      <c r="S173" s="2" t="inlineStr">
+      <c r="S173" s="2" t="n"/>
+      <c r="T173" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T173" s="2" t="inlineStr"/>
-      <c r="U173" s="4" t="inlineStr"/>
+      <c r="U173" s="2" t="inlineStr"/>
+      <c r="V173" s="4" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -15112,13 +15290,14 @@
         </is>
       </c>
       <c r="R174" s="2" t="n"/>
-      <c r="S174" s="2" t="inlineStr">
+      <c r="S174" s="2" t="n"/>
+      <c r="T174" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T174" s="2" t="inlineStr"/>
-      <c r="U174" s="4" t="inlineStr"/>
+      <c r="U174" s="2" t="inlineStr"/>
+      <c r="V174" s="4" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
@@ -15205,13 +15384,14 @@
           <t>Proyecto y DF a 0 € (parece reencargo de una obra ya contratada). Los 650 mezclan visado, seguro RC y nueva DR: SIN CASAR (¿TRAMITACION LICENCIAS?)</t>
         </is>
       </c>
-      <c r="S175" s="2" t="inlineStr">
+      <c r="S175" s="2" t="n"/>
+      <c r="T175" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T175" s="2" t="inlineStr"/>
-      <c r="U175" s="4" t="inlineStr"/>
+      <c r="U175" s="2" t="inlineStr"/>
+      <c r="V175" s="4" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -15298,13 +15478,14 @@
           <t>Sustitución de 2 ascensores casada como Modificación asc. (revisar); precio conjunto 3.500; el título del fichero menciona FAIN pero la hoja no nombra pagador</t>
         </is>
       </c>
-      <c r="S176" s="2" t="inlineStr">
+      <c r="S176" s="2" t="n"/>
+      <c r="T176" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T176" s="2" t="inlineStr"/>
-      <c r="U176" s="4" t="inlineStr"/>
+      <c r="U176" s="2" t="inlineStr"/>
+      <c r="V176" s="4" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -15387,13 +15568,14 @@
           <t>Solo tramo fijo, sin porcentaje a éxito. IEE NO incluido: la comunidad tiene uno previo</t>
         </is>
       </c>
-      <c r="S177" s="2" t="inlineStr">
+      <c r="S177" s="2" t="n"/>
+      <c r="T177" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T177" s="2" t="inlineStr"/>
-      <c r="U177" s="4" t="inlineStr"/>
+      <c r="U177" s="2" t="inlineStr"/>
+      <c r="V177" s="4" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -15438,13 +15620,14 @@
         </is>
       </c>
       <c r="R178" s="2" t="n"/>
-      <c r="S178" s="2" t="inlineStr">
+      <c r="S178" s="2" t="n"/>
+      <c r="T178" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T178" s="2" t="inlineStr"/>
-      <c r="U178" s="4" t="inlineStr"/>
+      <c r="U178" s="2" t="inlineStr"/>
+      <c r="V178" s="4" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -15523,13 +15706,14 @@
         </is>
       </c>
       <c r="R179" s="2" t="n"/>
-      <c r="S179" s="2" t="inlineStr">
+      <c r="S179" s="2" t="n"/>
+      <c r="T179" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T179" s="2" t="inlineStr"/>
-      <c r="U179" s="4" t="inlineStr"/>
+      <c r="U179" s="2" t="inlineStr"/>
+      <c r="V179" s="4" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -15609,13 +15793,14 @@
           <t>Bajada a cota cero añadiendo parada en sótano; pagador Schindler; membrete con otra dirección (Guzmán el Bueno 56); forma de pago contradictoria; precio conjunto 2.900</t>
         </is>
       </c>
-      <c r="S180" s="2" t="inlineStr">
+      <c r="S180" s="2" t="n"/>
+      <c r="T180" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T180" s="2" t="inlineStr"/>
-      <c r="U180" s="4" t="inlineStr"/>
+      <c r="U180" s="2" t="inlineStr"/>
+      <c r="V180" s="4" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -15705,13 +15890,14 @@
           <t>Arquitectura 8.500 € precio conjunto + subvención 1.980 € = 10.480 + IVA; 'envolvente térmica con cubierta' casada como SATE envolvente completa</t>
         </is>
       </c>
-      <c r="S181" s="2" t="inlineStr">
+      <c r="S181" s="2" t="n"/>
+      <c r="T181" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T181" s="2" t="inlineStr"/>
-      <c r="U181" s="4" t="inlineStr"/>
+      <c r="U181" s="2" t="inlineStr"/>
+      <c r="V181" s="4" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -15798,11 +15984,16 @@
       </c>
       <c r="S182" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T182" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T182" s="2" t="inlineStr"/>
-      <c r="U182" s="4" t="inlineStr"/>
+      <c r="U182" s="2" t="inlineStr"/>
+      <c r="V182" s="4" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -15883,11 +16074,16 @@
       <c r="R183" s="2" t="n"/>
       <c r="S183" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T183" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T183" s="2" t="inlineStr"/>
-      <c r="U183" s="4" t="inlineStr"/>
+      <c r="U183" s="2" t="inlineStr"/>
+      <c r="V183" s="4" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -15970,13 +16166,14 @@
           <t>Precio conjunto 5000 sin desglose por concepto; la lista salta al punto '5. Coordinación de Seguridad y Salud'</t>
         </is>
       </c>
-      <c r="S184" s="2" t="inlineStr">
+      <c r="S184" s="2" t="n"/>
+      <c r="T184" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T184" s="2" t="inlineStr"/>
-      <c r="U184" s="4" t="inlineStr"/>
+      <c r="U184" s="2" t="inlineStr"/>
+      <c r="V184" s="4" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -16063,11 +16260,16 @@
       </c>
       <c r="S185" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T185" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T185" s="2" t="inlineStr"/>
-      <c r="U185" s="4" t="inlineStr"/>
+      <c r="U185" s="2" t="inlineStr"/>
+      <c r="V185" s="4" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -16148,11 +16350,16 @@
       <c r="R186" s="2" t="n"/>
       <c r="S186" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T186" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T186" s="2" t="inlineStr"/>
-      <c r="U186" s="4" t="inlineStr"/>
+      <c r="U186" s="2" t="inlineStr"/>
+      <c r="V186" s="4" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -16231,13 +16438,14 @@
         </is>
       </c>
       <c r="R187" s="2" t="n"/>
-      <c r="S187" s="2" t="inlineStr">
+      <c r="S187" s="2" t="n"/>
+      <c r="T187" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T187" s="2" t="inlineStr"/>
-      <c r="U187" s="4" t="inlineStr"/>
+      <c r="U187" s="2" t="inlineStr"/>
+      <c r="V187" s="4" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -16325,13 +16533,14 @@
           <t>Precio conjunto 6.900</t>
         </is>
       </c>
-      <c r="S188" s="2" t="inlineStr">
+      <c r="S188" s="2" t="n"/>
+      <c r="T188" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T188" s="2" t="inlineStr"/>
-      <c r="U188" s="4" t="inlineStr"/>
+      <c r="U188" s="2" t="inlineStr"/>
+      <c r="V188" s="4" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -16416,13 +16625,14 @@
           <t>Precio único 1.980 para subvención + IEE + CEE; IEE y CEE marcados incluidos</t>
         </is>
       </c>
-      <c r="S189" s="2" t="inlineStr">
+      <c r="S189" s="2" t="n"/>
+      <c r="T189" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T189" s="2" t="inlineStr"/>
-      <c r="U189" s="4" t="inlineStr"/>
+      <c r="U189" s="2" t="inlineStr"/>
+      <c r="V189" s="4" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -16506,13 +16716,14 @@
           <t>Proyecto Básico y de Ejecución 5.500 como precio conjunto de toma de datos, proyecto, licencia y CFO; total_base = 5.500 + 500 + 1.980 (la hoja no da total). Forma de pago solo para el proyecto</t>
         </is>
       </c>
-      <c r="S190" s="2" t="inlineStr">
+      <c r="S190" s="2" t="n"/>
+      <c r="T190" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T190" s="2" t="inlineStr"/>
-      <c r="U190" s="4" t="inlineStr"/>
+      <c r="U190" s="2" t="inlineStr"/>
+      <c r="V190" s="4" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -16588,13 +16799,14 @@
         </is>
       </c>
       <c r="R191" s="2" t="n"/>
-      <c r="S191" s="2" t="inlineStr">
+      <c r="S191" s="2" t="n"/>
+      <c r="T191" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T191" s="2" t="inlineStr"/>
-      <c r="U191" s="4" t="inlineStr"/>
+      <c r="U191" s="2" t="inlineStr"/>
+      <c r="V191" s="4" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -16688,13 +16900,14 @@
           <t>REV2; título fechado 29/09/2025 pero la hoja dice 25/11/2025. 'Rehabilitación parcial' no casa con TIPOS. Precio conjunto 4.000 sin repartir</t>
         </is>
       </c>
-      <c r="S192" s="2" t="inlineStr">
+      <c r="S192" s="2" t="n"/>
+      <c r="T192" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T192" s="2" t="inlineStr"/>
-      <c r="U192" s="4" t="inlineStr"/>
+      <c r="U192" s="2" t="inlineStr"/>
+      <c r="V192" s="4" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -16787,13 +17000,14 @@
           <t>Honorarios de proyecto 7.000 en precio conjunto + subvención 1.980 fijo; total_base = 7.000 + 1.980. Devolución si no se concede licencia</t>
         </is>
       </c>
-      <c r="S193" s="2" t="inlineStr">
+      <c r="S193" s="2" t="n"/>
+      <c r="T193" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T193" s="2" t="inlineStr"/>
-      <c r="U193" s="4" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr"/>
+      <c r="V193" s="4" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -16874,11 +17088,16 @@
       <c r="R194" s="2" t="n"/>
       <c r="S194" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T194" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T194" s="2" t="inlineStr"/>
-      <c r="U194" s="4" t="inlineStr"/>
+      <c r="U194" s="2" t="inlineStr"/>
+      <c r="V194" s="4" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -16970,13 +17189,14 @@
           <t>Fecha escrita '04/07/0225' (errata; se toma 2025-07-04: el título dice 04/04/0225 y el fichero se modificó el 2025-07-04); sin CSS; precio conjunto 6.900</t>
         </is>
       </c>
-      <c r="S195" s="2" t="inlineStr">
+      <c r="S195" s="2" t="n"/>
+      <c r="T195" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T195" s="2" t="inlineStr"/>
-      <c r="U195" s="4" t="inlineStr"/>
+      <c r="U195" s="2" t="inlineStr"/>
+      <c r="V195" s="4" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -17067,13 +17287,14 @@
           <t>Proyecto 7.900 € precio conjunto + subvención 1.980 € fijo; total_base sumado (la hoja no da total); CEE sin precio propio</t>
         </is>
       </c>
-      <c r="S196" s="2" t="inlineStr">
+      <c r="S196" s="2" t="n"/>
+      <c r="T196" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="4" t="inlineStr"/>
+      <c r="U196" s="2" t="inlineStr"/>
+      <c r="V196" s="4" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -17162,13 +17383,14 @@
           <t>Dos ascensores: honorarios de proyecto 6.000 POR ASCENSOR (no dice total); subvenciones 1.980 precio único para los dos; dos hojas en un fichero</t>
         </is>
       </c>
-      <c r="S197" s="2" t="inlineStr">
+      <c r="S197" s="2" t="n"/>
+      <c r="T197" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T197" s="2" t="inlineStr"/>
-      <c r="U197" s="4" t="inlineStr"/>
+      <c r="U197" s="2" t="inlineStr"/>
+      <c r="V197" s="4" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -17257,13 +17479,14 @@
           <t>La consulta urbanística (800) ya se pagó antes y se descuenta (-800); las celdas 1.160 y 800 vienen pegadas en la tabla; la suma cuadra con 5.100</t>
         </is>
       </c>
-      <c r="S198" s="2" t="inlineStr">
+      <c r="S198" s="2" t="n"/>
+      <c r="T198" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T198" s="2" t="inlineStr"/>
-      <c r="U198" s="4" t="inlineStr"/>
+      <c r="U198" s="2" t="inlineStr"/>
+      <c r="V198" s="4" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -17347,13 +17570,14 @@
           <t>Solo tramo fijo, sin porcentaje a éxito. IEE incluido solo si no hay previo válido</t>
         </is>
       </c>
-      <c r="S199" s="2" t="inlineStr">
+      <c r="S199" s="2" t="n"/>
+      <c r="T199" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T199" s="2" t="inlineStr"/>
-      <c r="U199" s="4" t="inlineStr"/>
+      <c r="U199" s="2" t="inlineStr"/>
+      <c r="V199" s="4" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -17443,11 +17667,16 @@
       </c>
       <c r="S200" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T200" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T200" s="2" t="inlineStr"/>
-      <c r="U200" s="4" t="inlineStr"/>
+      <c r="U200" s="2" t="inlineStr"/>
+      <c r="V200" s="4" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -17542,11 +17771,16 @@
       </c>
       <c r="S201" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T201" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T201" s="2" t="inlineStr"/>
-      <c r="U201" s="4" t="inlineStr"/>
+      <c r="U201" s="2" t="inlineStr"/>
+      <c r="V201" s="4" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -17629,11 +17863,16 @@
       </c>
       <c r="S202" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T202" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T202" s="2" t="inlineStr"/>
-      <c r="U202" s="4" t="inlineStr"/>
+      <c r="U202" s="2" t="inlineStr"/>
+      <c r="V202" s="4" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -17716,13 +17955,14 @@
           <t>Proyecto conjunto 6.500 (bajada a cota cero de dos ascensores con sustitución) + subvención 1.980; total_base es la suma. Se titula 'Propuesta'. Menciona alternativa con Iberdrola (SATE, aerotermia, fotovoltaica) sin precio</t>
         </is>
       </c>
-      <c r="S203" s="2" t="inlineStr">
+      <c r="S203" s="2" t="n"/>
+      <c r="T203" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T203" s="2" t="inlineStr"/>
-      <c r="U203" s="4" t="inlineStr"/>
+      <c r="U203" s="2" t="inlineStr"/>
+      <c r="V203" s="4" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -17811,13 +18051,14 @@
           <t>Total sin descuento 30.750 menos 22.250 por cesión de CAES = 8.500; desglose marcado incluido. Exige firmar Contrato de Cesión de CAES (Anexo I). 'Envolvente térmica' casada como SATE envolvente completa (revisar). Oferta válida 30 días</t>
         </is>
       </c>
-      <c r="S204" s="2" t="inlineStr">
+      <c r="S204" s="2" t="n"/>
+      <c r="T204" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T204" s="2" t="inlineStr"/>
-      <c r="U204" s="4" t="inlineStr"/>
+      <c r="U204" s="2" t="inlineStr"/>
+      <c r="V204" s="4" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -17907,13 +18148,14 @@
           <t>'Rehabilitación parcial DR' no casa con TIPOS. Precio conjunto 3.500 sin repartir</t>
         </is>
       </c>
-      <c r="S205" s="2" t="inlineStr">
+      <c r="S205" s="2" t="n"/>
+      <c r="T205" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T205" s="2" t="inlineStr"/>
-      <c r="U205" s="4" t="inlineStr"/>
+      <c r="U205" s="2" t="inlineStr"/>
+      <c r="V205" s="4" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -17998,11 +18240,16 @@
       </c>
       <c r="S206" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T206" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T206" s="2" t="inlineStr"/>
-      <c r="U206" s="4" t="inlineStr"/>
+      <c r="U206" s="2" t="inlineStr"/>
+      <c r="V206" s="4" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -18087,11 +18334,16 @@
       </c>
       <c r="S207" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T207" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T207" s="2" t="inlineStr"/>
-      <c r="U207" s="4" t="inlineStr"/>
+      <c r="U207" s="2" t="inlineStr"/>
+      <c r="V207" s="4" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -18174,11 +18426,16 @@
       <c r="R208" s="2" t="n"/>
       <c r="S208" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T208" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T208" s="2" t="inlineStr"/>
-      <c r="U208" s="4" t="inlineStr"/>
+      <c r="U208" s="2" t="inlineStr"/>
+      <c r="V208" s="4" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -18259,11 +18516,16 @@
       <c r="R209" s="2" t="n"/>
       <c r="S209" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T209" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T209" s="2" t="inlineStr"/>
-      <c r="U209" s="4" t="inlineStr"/>
+      <c r="U209" s="2" t="inlineStr"/>
+      <c r="V209" s="4" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -18347,13 +18609,14 @@
           <t>Precio conjunto 1.800 para CSS y DF</t>
         </is>
       </c>
-      <c r="S210" s="2" t="inlineStr">
+      <c r="S210" s="2" t="n"/>
+      <c r="T210" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T210" s="2" t="inlineStr"/>
-      <c r="U210" s="4" t="inlineStr"/>
+      <c r="U210" s="2" t="inlineStr"/>
+      <c r="V210" s="4" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -18441,13 +18704,14 @@
           <t>Precio conjunto 5.700</t>
         </is>
       </c>
-      <c r="S211" s="2" t="inlineStr">
+      <c r="S211" s="2" t="n"/>
+      <c r="T211" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T211" s="2" t="inlineStr"/>
-      <c r="U211" s="4" t="inlineStr"/>
+      <c r="U211" s="2" t="inlineStr"/>
+      <c r="V211" s="4" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -18528,11 +18792,16 @@
       <c r="R212" s="2" t="n"/>
       <c r="S212" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T212" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T212" s="2" t="inlineStr"/>
-      <c r="U212" s="4" t="inlineStr"/>
+      <c r="U212" s="2" t="inlineStr"/>
+      <c r="V212" s="4" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -18629,11 +18898,16 @@
       </c>
       <c r="S213" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T213" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T213" s="2" t="inlineStr"/>
-      <c r="U213" s="4" t="inlineStr"/>
+      <c r="U213" s="2" t="inlineStr"/>
+      <c r="V213" s="4" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -18719,11 +18993,16 @@
       </c>
       <c r="S214" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T214" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T214" s="2" t="inlineStr"/>
-      <c r="U214" s="4" t="inlineStr"/>
+      <c r="U214" s="2" t="inlineStr"/>
+      <c r="V214" s="4" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -18810,11 +19089,16 @@
       <c r="R215" s="2" t="n"/>
       <c r="S215" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T215" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T215" s="2" t="inlineStr"/>
-      <c r="U215" s="4" t="inlineStr"/>
+      <c r="U215" s="2" t="inlineStr"/>
+      <c r="V215" s="4" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -18898,13 +19182,14 @@
           <t>Tres portales (133, 135, 137) en una hoja. Precio conjunto 1.650 para DF + informe/certificado de idoneidad, sin repartir</t>
         </is>
       </c>
-      <c r="S216" s="2" t="inlineStr">
+      <c r="S216" s="2" t="n"/>
+      <c r="T216" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T216" s="2" t="inlineStr"/>
-      <c r="U216" s="4" t="inlineStr"/>
+      <c r="U216" s="2" t="inlineStr"/>
+      <c r="V216" s="4" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -18993,11 +19278,16 @@
       </c>
       <c r="S217" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T217" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T217" s="2" t="inlineStr"/>
-      <c r="U217" s="4" t="inlineStr"/>
+      <c r="U217" s="2" t="inlineStr"/>
+      <c r="V217" s="4" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -19088,11 +19378,16 @@
       </c>
       <c r="S218" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T218" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T218" s="2" t="inlineStr"/>
-      <c r="U218" s="4" t="inlineStr"/>
+      <c r="U218" s="2" t="inlineStr"/>
+      <c r="V218" s="4" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -19173,11 +19468,16 @@
       <c r="R219" s="2" t="n"/>
       <c r="S219" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T219" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T219" s="2" t="inlineStr"/>
-      <c r="U219" s="4" t="inlineStr"/>
+      <c r="U219" s="2" t="inlineStr"/>
+      <c r="V219" s="4" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -19258,11 +19558,16 @@
       <c r="R220" s="2" t="n"/>
       <c r="S220" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T220" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T220" s="2" t="inlineStr"/>
-      <c r="U220" s="4" t="inlineStr"/>
+      <c r="U220" s="2" t="inlineStr"/>
+      <c r="V220" s="4" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -19355,13 +19660,14 @@
           <t>La hoja dice 'ENVOLVENTE TÉRMICA' (título: SATE SIN CAES ROEN), casado como SATE envolvente completa; precio conjunto 11.518 sin desglose, subvención incluida sin tramo variable</t>
         </is>
       </c>
-      <c r="S221" s="2" t="inlineStr">
+      <c r="S221" s="2" t="n"/>
+      <c r="T221" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T221" s="2" t="inlineStr"/>
-      <c r="U221" s="4" t="inlineStr"/>
+      <c r="U221" s="2" t="inlineStr"/>
+      <c r="V221" s="4" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -19446,11 +19752,16 @@
       </c>
       <c r="S222" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T222" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T222" s="2" t="inlineStr"/>
-      <c r="U222" s="4" t="inlineStr"/>
+      <c r="U222" s="2" t="inlineStr"/>
+      <c r="V222" s="4" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -19540,11 +19851,16 @@
       </c>
       <c r="S223" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T223" s="2" t="inlineStr"/>
-      <c r="U223" s="4" t="inlineStr"/>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="4" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -19649,11 +19965,16 @@
       </c>
       <c r="S224" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T224" s="2" t="inlineStr"/>
-      <c r="U224" s="4" t="inlineStr"/>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="4" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -19744,11 +20065,16 @@
       </c>
       <c r="S225" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T225" s="2" t="inlineStr"/>
-      <c r="U225" s="4" t="inlineStr"/>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="4" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -19834,11 +20160,16 @@
       </c>
       <c r="S226" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T226" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T226" s="2" t="inlineStr"/>
-      <c r="U226" s="4" t="inlineStr"/>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="4" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -19929,11 +20260,16 @@
       </c>
       <c r="S227" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T227" s="2" t="inlineStr"/>
-      <c r="U227" s="4" t="inlineStr"/>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="4" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -20024,11 +20360,16 @@
       </c>
       <c r="S228" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T228" s="2" t="inlineStr"/>
-      <c r="U228" s="4" t="inlineStr"/>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="4" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -20115,11 +20456,16 @@
       </c>
       <c r="S229" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T229" s="2" t="inlineStr"/>
-      <c r="U229" s="4" t="inlineStr"/>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="4" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -20204,11 +20550,16 @@
       </c>
       <c r="S230" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T230" s="2" t="inlineStr"/>
-      <c r="U230" s="4" t="inlineStr"/>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="4" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -20289,11 +20640,16 @@
       <c r="R231" s="2" t="n"/>
       <c r="S231" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T231" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T231" s="2" t="inlineStr"/>
-      <c r="U231" s="4" t="inlineStr"/>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="4" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -20382,11 +20738,16 @@
       </c>
       <c r="S232" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T232" s="2" t="inlineStr"/>
-      <c r="U232" s="4" t="inlineStr"/>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="4" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -20473,11 +20834,16 @@
       </c>
       <c r="S233" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T233" s="2" t="inlineStr"/>
-      <c r="U233" s="4" t="inlineStr"/>
+      <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="4" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
@@ -20562,11 +20928,16 @@
       </c>
       <c r="S234" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T234" s="2" t="inlineStr"/>
-      <c r="U234" s="4" t="inlineStr"/>
+      <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="4" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
@@ -20652,11 +21023,16 @@
       </c>
       <c r="S235" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T235" s="2" t="inlineStr"/>
-      <c r="U235" s="4" t="inlineStr"/>
+      <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="4" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
@@ -20743,11 +21119,16 @@
       <c r="R236" s="2" t="n"/>
       <c r="S236" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T236" s="2" t="inlineStr"/>
-      <c r="U236" s="4" t="inlineStr"/>
+      <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="4" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -20843,11 +21224,16 @@
       </c>
       <c r="S237" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T237" s="2" t="inlineStr"/>
-      <c r="U237" s="4" t="inlineStr"/>
+      <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="4" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
@@ -20935,11 +21321,16 @@
       </c>
       <c r="S238" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T238" s="2" t="inlineStr"/>
-      <c r="U238" s="4" t="inlineStr"/>
+      <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="4" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -21029,11 +21420,16 @@
       </c>
       <c r="S239" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T239" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T239" s="2" t="inlineStr"/>
-      <c r="U239" s="4" t="inlineStr"/>
+      <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="4" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -21117,11 +21513,16 @@
       </c>
       <c r="S240" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T240" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T240" s="2" t="inlineStr"/>
-      <c r="U240" s="4" t="inlineStr"/>
+      <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="4" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
@@ -21224,11 +21625,16 @@
       </c>
       <c r="S241" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T241" s="2" t="inlineStr"/>
-      <c r="U241" s="4" t="inlineStr"/>
+      <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="4" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -21318,11 +21724,16 @@
       </c>
       <c r="S242" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T242" s="2" t="inlineStr"/>
-      <c r="U242" s="4" t="inlineStr"/>
+      <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="4" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
@@ -21406,11 +21817,16 @@
       </c>
       <c r="S243" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T243" s="2" t="inlineStr"/>
-      <c r="U243" s="4" t="inlineStr"/>
+      <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="4" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -21501,11 +21917,16 @@
       </c>
       <c r="S244" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T244" s="2" t="inlineStr"/>
-      <c r="U244" s="4" t="inlineStr"/>
+      <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="4" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -21596,11 +22017,16 @@
       </c>
       <c r="S245" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T245" s="2" t="inlineStr"/>
-      <c r="U245" s="4" t="inlineStr"/>
+      <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="4" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
@@ -21690,11 +22116,16 @@
       </c>
       <c r="S246" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T246" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T246" s="2" t="inlineStr"/>
-      <c r="U246" s="4" t="inlineStr"/>
+      <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="4" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -21785,11 +22216,16 @@
       </c>
       <c r="S247" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T247" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T247" s="2" t="inlineStr"/>
-      <c r="U247" s="4" t="inlineStr"/>
+      <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="4" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
@@ -21884,11 +22320,16 @@
       </c>
       <c r="S248" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T248" s="2" t="inlineStr"/>
-      <c r="U248" s="4" t="inlineStr"/>
+      <c r="U248" s="2" t="inlineStr"/>
+      <c r="V248" s="4" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -21980,11 +22421,16 @@
       </c>
       <c r="S249" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T249" s="2" t="inlineStr"/>
-      <c r="U249" s="4" t="inlineStr"/>
+      <c r="U249" s="2" t="inlineStr"/>
+      <c r="V249" s="4" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
@@ -22068,11 +22514,16 @@
       </c>
       <c r="S250" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T250" s="2" t="inlineStr"/>
-      <c r="U250" s="4" t="inlineStr"/>
+      <c r="U250" s="2" t="inlineStr"/>
+      <c r="V250" s="4" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -22125,13 +22576,14 @@
           <t>Importes en la firmada: Dirección facultativa y CSS 2.500 + IVA</t>
         </is>
       </c>
-      <c r="S251" s="2" t="inlineStr">
+      <c r="S251" s="2" t="n"/>
+      <c r="T251" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T251" s="2" t="inlineStr"/>
-      <c r="U251" s="4" t="inlineStr"/>
+      <c r="U251" s="2" t="inlineStr"/>
+      <c r="V251" s="4" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
@@ -22217,11 +22669,16 @@
       </c>
       <c r="S252" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T252" s="2" t="inlineStr"/>
-      <c r="U252" s="4" t="inlineStr"/>
+      <c r="U252" s="2" t="inlineStr"/>
+      <c r="V252" s="4" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
@@ -22274,13 +22731,14 @@
           <t>Importes en la firmada: DF y CSS 2.500</t>
         </is>
       </c>
-      <c r="S253" s="2" t="inlineStr">
+      <c r="S253" s="2" t="n"/>
+      <c r="T253" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T253" s="2" t="inlineStr"/>
-      <c r="U253" s="4" t="inlineStr"/>
+      <c r="U253" s="2" t="inlineStr"/>
+      <c r="V253" s="4" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -22377,11 +22835,16 @@
       </c>
       <c r="S254" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T254" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T254" s="2" t="inlineStr"/>
-      <c r="U254" s="4" t="inlineStr"/>
+      <c r="U254" s="2" t="inlineStr"/>
+      <c r="V254" s="4" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
@@ -22472,11 +22935,16 @@
       </c>
       <c r="S255" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T255" s="2" t="inlineStr"/>
-      <c r="U255" s="4" t="inlineStr"/>
+      <c r="U255" s="2" t="inlineStr"/>
+      <c r="V255" s="4" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -22561,11 +23029,16 @@
       </c>
       <c r="S256" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T256" s="2" t="inlineStr"/>
-      <c r="U256" s="4" t="inlineStr"/>
+      <c r="U256" s="2" t="inlineStr"/>
+      <c r="V256" s="4" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -22656,11 +23129,16 @@
       </c>
       <c r="S257" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T257" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T257" s="2" t="inlineStr"/>
-      <c r="U257" s="4" t="inlineStr"/>
+      <c r="U257" s="2" t="inlineStr"/>
+      <c r="V257" s="4" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
@@ -22745,11 +23223,16 @@
       </c>
       <c r="S258" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T258" s="2" t="inlineStr"/>
-      <c r="U258" s="4" t="inlineStr"/>
+      <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="4" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
@@ -22833,11 +23316,16 @@
       </c>
       <c r="S259" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T259" s="2" t="inlineStr"/>
-      <c r="U259" s="4" t="inlineStr"/>
+      <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="4" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
@@ -22925,11 +23413,16 @@
       </c>
       <c r="S260" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T260" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T260" s="2" t="inlineStr"/>
-      <c r="U260" s="4" t="inlineStr"/>
+      <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="4" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
@@ -23014,11 +23507,16 @@
       </c>
       <c r="S261" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T261" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T261" s="2" t="inlineStr"/>
-      <c r="U261" s="4" t="inlineStr"/>
+      <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="4" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
@@ -23108,11 +23606,16 @@
       </c>
       <c r="S262" s="2" t="inlineStr">
         <is>
+          <t>CG/ por alejandra</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T262" s="2" t="inlineStr"/>
-      <c r="U262" s="4" t="inlineStr"/>
+      <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="4" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
@@ -23205,11 +23708,16 @@
       </c>
       <c r="S263" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T263" s="2" t="inlineStr"/>
-      <c r="U263" s="4" t="inlineStr"/>
+      <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="4" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
@@ -23288,11 +23796,16 @@
       <c r="R264" s="2" t="n"/>
       <c r="S264" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T264" s="2" t="inlineStr"/>
-      <c r="U264" s="4" t="inlineStr"/>
+      <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="4" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
@@ -23386,11 +23899,16 @@
       </c>
       <c r="S265" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T265" s="2" t="inlineStr"/>
-      <c r="U265" s="4" t="inlineStr"/>
+      <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="4" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
@@ -23477,11 +23995,16 @@
       </c>
       <c r="S266" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T266" s="2" t="inlineStr"/>
-      <c r="U266" s="4" t="inlineStr"/>
+      <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="4" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -23569,11 +24092,16 @@
       </c>
       <c r="S267" s="2" t="inlineStr">
         <is>
+          <t>CG/ por alejandra</t>
+        </is>
+      </c>
+      <c r="T267" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T267" s="2" t="inlineStr"/>
-      <c r="U267" s="4" t="inlineStr"/>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="4" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -23664,11 +24192,16 @@
       </c>
       <c r="S268" s="2" t="inlineStr">
         <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T268" s="2" t="inlineStr"/>
-      <c r="U268" s="4" t="inlineStr"/>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="4" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
@@ -23757,11 +24290,16 @@
       </c>
       <c r="S269" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T269" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T269" s="2" t="inlineStr"/>
-      <c r="U269" s="4" t="inlineStr"/>
+      <c r="U269" s="2" t="inlineStr"/>
+      <c r="V269" s="4" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
@@ -23845,11 +24383,16 @@
       </c>
       <c r="S270" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T270" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T270" s="2" t="inlineStr"/>
-      <c r="U270" s="4" t="inlineStr"/>
+      <c r="U270" s="2" t="inlineStr"/>
+      <c r="V270" s="4" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
@@ -23940,11 +24483,16 @@
       </c>
       <c r="S271" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T271" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T271" s="2" t="inlineStr"/>
-      <c r="U271" s="4" t="inlineStr"/>
+      <c r="U271" s="2" t="inlineStr"/>
+      <c r="V271" s="4" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
@@ -24029,11 +24577,16 @@
       </c>
       <c r="S272" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T272" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T272" s="2" t="inlineStr"/>
-      <c r="U272" s="4" t="inlineStr"/>
+      <c r="U272" s="2" t="inlineStr"/>
+      <c r="V272" s="4" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
@@ -24122,11 +24675,16 @@
       </c>
       <c r="S273" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T273" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T273" s="2" t="inlineStr"/>
-      <c r="U273" s="4" t="inlineStr"/>
+      <c r="U273" s="2" t="inlineStr"/>
+      <c r="V273" s="4" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
@@ -24207,11 +24765,16 @@
       <c r="R274" s="2" t="n"/>
       <c r="S274" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T274" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T274" s="2" t="inlineStr"/>
-      <c r="U274" s="4" t="inlineStr"/>
+      <c r="U274" s="2" t="inlineStr"/>
+      <c r="V274" s="4" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
@@ -24301,11 +24864,16 @@
       </c>
       <c r="S275" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T275" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T275" s="2" t="inlineStr"/>
-      <c r="U275" s="4" t="inlineStr"/>
+      <c r="U275" s="2" t="inlineStr"/>
+      <c r="V275" s="4" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
@@ -24395,11 +24963,16 @@
       </c>
       <c r="S276" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T276" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T276" s="2" t="inlineStr"/>
-      <c r="U276" s="4" t="inlineStr"/>
+      <c r="U276" s="2" t="inlineStr"/>
+      <c r="V276" s="4" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
@@ -24490,11 +25063,16 @@
       </c>
       <c r="S277" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T277" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T277" s="2" t="inlineStr"/>
-      <c r="U277" s="4" t="inlineStr"/>
+      <c r="U277" s="2" t="inlineStr"/>
+      <c r="V277" s="4" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -24573,13 +25151,14 @@
         </is>
       </c>
       <c r="R278" s="2" t="n"/>
-      <c r="S278" s="2" t="inlineStr">
+      <c r="S278" s="2" t="n"/>
+      <c r="T278" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T278" s="2" t="inlineStr"/>
-      <c r="U278" s="4" t="inlineStr"/>
+      <c r="U278" s="2" t="inlineStr"/>
+      <c r="V278" s="4" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -24670,11 +25249,16 @@
       </c>
       <c r="S279" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T279" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T279" s="2" t="inlineStr"/>
-      <c r="U279" s="4" t="inlineStr"/>
+      <c r="U279" s="2" t="inlineStr"/>
+      <c r="V279" s="4" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
@@ -24759,11 +25343,16 @@
       <c r="R280" s="2" t="n"/>
       <c r="S280" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T280" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T280" s="2" t="inlineStr"/>
-      <c r="U280" s="4" t="inlineStr"/>
+      <c r="U280" s="2" t="inlineStr"/>
+      <c r="V280" s="4" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
@@ -24854,11 +25443,16 @@
       </c>
       <c r="S281" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T281" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T281" s="2" t="inlineStr"/>
-      <c r="U281" s="4" t="inlineStr"/>
+      <c r="U281" s="2" t="inlineStr"/>
+      <c r="V281" s="4" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
@@ -24942,13 +25536,14 @@
           <t>Precio conjunto 1.800 para CSS y DF; forma de pago habla de 'entrega del Proyecto' aunque no hay proyecto</t>
         </is>
       </c>
-      <c r="S282" s="2" t="inlineStr">
+      <c r="S282" s="2" t="n"/>
+      <c r="T282" s="2" t="inlineStr">
         <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T282" s="2" t="inlineStr"/>
-      <c r="U282" s="4" t="inlineStr"/>
+      <c r="U282" s="2" t="inlineStr"/>
+      <c r="V282" s="4" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
@@ -25036,11 +25631,16 @@
       </c>
       <c r="S283" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T283" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T283" s="2" t="inlineStr"/>
-      <c r="U283" s="4" t="inlineStr"/>
+      <c r="U283" s="2" t="inlineStr"/>
+      <c r="V283" s="4" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
@@ -25131,11 +25731,16 @@
       </c>
       <c r="S284" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T284" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T284" s="2" t="inlineStr"/>
-      <c r="U284" s="4" t="inlineStr"/>
+      <c r="U284" s="2" t="inlineStr"/>
+      <c r="V284" s="4" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
@@ -25219,11 +25824,16 @@
       </c>
       <c r="S285" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T285" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T285" s="2" t="inlineStr"/>
-      <c r="U285" s="4" t="inlineStr"/>
+      <c r="U285" s="2" t="inlineStr"/>
+      <c r="V285" s="4" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -25304,11 +25914,16 @@
       <c r="R286" s="2" t="n"/>
       <c r="S286" s="2" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="T286" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T286" s="2" t="inlineStr"/>
-      <c r="U286" s="4" t="inlineStr"/>
+      <c r="U286" s="2" t="inlineStr"/>
+      <c r="V286" s="4" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -25396,14 +26011,19 @@
       </c>
       <c r="S287" s="2" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="T287" s="2" t="inlineStr">
+        <is>
           <t>se asigna al final, con todas</t>
         </is>
       </c>
-      <c r="T287" s="2" t="inlineStr"/>
-      <c r="U287" s="4" t="inlineStr"/>
+      <c r="U287" s="2" t="inlineStr"/>
+      <c r="V287" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U287"/>
+  <autoFilter ref="A1:V287"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/cruce_hojas_tanda2.xlsx
+++ b/docs/cruce_hojas_tanda2.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cruce'!$A$1:$V$287</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conceptos'!$A$1:$H$1074</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conceptos'!$A$1:$H$1078</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22543,7 +22543,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr"/>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>RESUELTO LEYENDO: Datos de la propia firmada (sin enviada en la carpeta): DF y CSS 2.500 + IVA, 23-03-2026, paga URVIAL SL.</t>
+        </is>
+      </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
@@ -22560,10 +22564,21 @@
           <t>contrata: URVIAL SL</t>
         </is>
       </c>
-      <c r="H251" s="2" t="inlineStr"/>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>DF, CSS</t>
+        </is>
+      </c>
       <c r="I251" s="2" t="inlineStr"/>
-      <c r="J251" s="2" t="inlineStr"/>
-      <c r="K251" s="2" t="n"/>
+      <c r="J251" s="2" t="inlineStr">
+        <is>
+          <t>DF: sin precio propio
+CSS: incluido</t>
+        </is>
+      </c>
+      <c r="K251" s="2" t="n">
+        <v>2500</v>
+      </c>
       <c r="L251" s="2" t="n"/>
       <c r="M251" s="2" t="inlineStr">
         <is>
@@ -22698,7 +22713,11 @@
           <t>OK</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr"/>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>RESUELTO LEYENDO: Datos de la propia firmada (sin enviada en la carpeta): DF y CSS 2.500 + IVA, 23-03-2026, paga URVAU SL.</t>
+        </is>
+      </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
           <t>2026-06-03</t>
@@ -22715,10 +22734,21 @@
           <t>contrata: URVAU SL</t>
         </is>
       </c>
-      <c r="H253" s="2" t="inlineStr"/>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>DF, CSS</t>
+        </is>
+      </c>
       <c r="I253" s="2" t="inlineStr"/>
-      <c r="J253" s="2" t="inlineStr"/>
-      <c r="K253" s="2" t="n"/>
+      <c r="J253" s="2" t="inlineStr">
+        <is>
+          <t>DF: sin precio propio
+CSS: incluido</t>
+        </is>
+      </c>
+      <c r="K253" s="2" t="n">
+        <v>2500</v>
+      </c>
       <c r="L253" s="2" t="n"/>
       <c r="M253" s="2" t="inlineStr">
         <is>
@@ -26041,7 +26071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1074"/>
+  <dimension ref="A1:H1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -52095,22 +52125,18 @@
     <row r="915">
       <c r="A915" s="2" t="inlineStr">
         <is>
-          <t>F234</t>
-        </is>
-      </c>
-      <c r="B915" s="2" t="inlineStr">
-        <is>
-          <t>IGLESIA 22 ALCORCÓN</t>
-        </is>
-      </c>
+          <t>F233</t>
+        </is>
+      </c>
+      <c r="B915" s="2" t="n"/>
       <c r="C915" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>Dirección facultativa</t>
         </is>
       </c>
       <c r="D915" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E915" s="2" t="n"/>
@@ -52121,149 +52147,121 @@
     <row r="916">
       <c r="A916" s="2" t="inlineStr">
         <is>
-          <t>F234</t>
-        </is>
-      </c>
-      <c r="B916" s="2" t="inlineStr">
-        <is>
-          <t>IGLESIA 22 ALCORCÓN</t>
-        </is>
-      </c>
+          <t>F233</t>
+        </is>
+      </c>
+      <c r="B916" s="2" t="n"/>
       <c r="C916" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>Coordinación de seguridad y salud</t>
         </is>
       </c>
       <c r="D916" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="E916" s="2" t="n"/>
       <c r="F916" s="2" t="n"/>
-      <c r="G916" s="2" t="inlineStr"/>
+      <c r="G916" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H916" s="2" t="n"/>
     </row>
     <row r="917">
       <c r="A917" s="2" t="inlineStr">
         <is>
-          <t>F236</t>
+          <t>F234</t>
         </is>
       </c>
       <c r="B917" s="2" t="inlineStr">
         <is>
-          <t>ALTAMIRANO 32 MADRID</t>
+          <t>IGLESIA 22 ALCORCÓN</t>
         </is>
       </c>
       <c r="C917" s="2" t="inlineStr">
         <is>
-          <t>Proyecto de Rehabilitación de la Envolvente Térmica</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D917" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
-        </is>
-      </c>
-      <c r="E917" s="2" t="n">
-        <v>19200</v>
-      </c>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="n"/>
       <c r="F917" s="2" t="n"/>
-      <c r="G917" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G917" s="2" t="inlineStr"/>
       <c r="H917" s="2" t="n"/>
     </row>
     <row r="918">
       <c r="A918" s="2" t="inlineStr">
         <is>
-          <t>F236</t>
+          <t>F234</t>
         </is>
       </c>
       <c r="B918" s="2" t="inlineStr">
         <is>
-          <t>ALTAMIRANO 32 MADRID</t>
+          <t>IGLESIA 22 ALCORCÓN</t>
         </is>
       </c>
       <c r="C918" s="2" t="inlineStr">
         <is>
-          <t>Libro del Edificio (LE)</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D918" s="2" t="inlineStr">
         <is>
-          <t>LEE</t>
-        </is>
-      </c>
-      <c r="E918" s="2" t="n">
-        <v>2060</v>
-      </c>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E918" s="2" t="n"/>
       <c r="F918" s="2" t="n"/>
-      <c r="G918" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G918" s="2" t="inlineStr"/>
       <c r="H918" s="2" t="n"/>
     </row>
     <row r="919">
       <c r="A919" s="2" t="inlineStr">
         <is>
-          <t>F236</t>
-        </is>
-      </c>
-      <c r="B919" s="2" t="inlineStr">
-        <is>
-          <t>ALTAMIRANO 32 MADRID</t>
-        </is>
-      </c>
+          <t>F235</t>
+        </is>
+      </c>
+      <c r="B919" s="2" t="n"/>
       <c r="C919" s="2" t="inlineStr">
         <is>
-          <t>Informe de Evaluación del Edificio (IEE)</t>
+          <t>Dirección facultativa</t>
         </is>
       </c>
       <c r="D919" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
-        </is>
-      </c>
-      <c r="E919" s="2" t="n">
-        <v>1030</v>
-      </c>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="n"/>
       <c r="F919" s="2" t="n"/>
-      <c r="G919" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G919" s="2" t="inlineStr"/>
       <c r="H919" s="2" t="n"/>
     </row>
     <row r="920">
       <c r="A920" s="2" t="inlineStr">
         <is>
-          <t>F236</t>
-        </is>
-      </c>
-      <c r="B920" s="2" t="inlineStr">
-        <is>
-          <t>ALTAMIRANO 32 MADRID</t>
-        </is>
-      </c>
+          <t>F235</t>
+        </is>
+      </c>
+      <c r="B920" s="2" t="n"/>
       <c r="C920" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Subvenciones de Eficiencia Energética</t>
+          <t>Coordinación de seguridad y salud</t>
         </is>
       </c>
       <c r="D920" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E920" s="2" t="n">
-        <v>1980</v>
-      </c>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E920" s="2" t="n"/>
       <c r="F920" s="2" t="n"/>
       <c r="G920" s="2" t="inlineStr">
         <is>
@@ -52285,24 +52283,24 @@
       </c>
       <c r="C921" s="2" t="inlineStr">
         <is>
-          <t>Total Honorarios con Descuento por Cesión de CAES</t>
+          <t>Proyecto de Rehabilitación de la Envolvente Térmica</t>
         </is>
       </c>
       <c r="D921" s="2" t="inlineStr">
         <is>
-          <t>SATE CON CESION DE CAES</t>
+          <t>REDACCION PROYECTO</t>
         </is>
       </c>
       <c r="E921" s="2" t="n">
-        <v>10400</v>
+        <v>19200</v>
       </c>
       <c r="F921" s="2" t="n"/>
-      <c r="G921" s="2" t="inlineStr"/>
-      <c r="H921" s="2" t="inlineStr">
-        <is>
-          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
-        </is>
-      </c>
+      <c r="G921" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="n"/>
     </row>
     <row r="922">
       <c r="A922" s="2" t="inlineStr">
@@ -52317,15 +52315,17 @@
       </c>
       <c r="C922" s="2" t="inlineStr">
         <is>
-          <t>Toma de datos y modelado 3D</t>
+          <t>Libro del Edificio (LE)</t>
         </is>
       </c>
       <c r="D922" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
-        </is>
-      </c>
-      <c r="E922" s="2" t="n"/>
+          <t>LEE</t>
+        </is>
+      </c>
+      <c r="E922" s="2" t="n">
+        <v>2060</v>
+      </c>
       <c r="F922" s="2" t="n"/>
       <c r="G922" s="2" t="inlineStr">
         <is>
@@ -52347,15 +52347,17 @@
       </c>
       <c r="C923" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Licencias y Permisos</t>
+          <t>Informe de Evaluación del Edificio (IEE)</t>
         </is>
       </c>
       <c r="D923" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
-        </is>
-      </c>
-      <c r="E923" s="2" t="n"/>
+          <t>IEE</t>
+        </is>
+      </c>
+      <c r="E923" s="2" t="n">
+        <v>1030</v>
+      </c>
       <c r="F923" s="2" t="n"/>
       <c r="G923" s="2" t="inlineStr">
         <is>
@@ -52377,15 +52379,17 @@
       </c>
       <c r="C924" s="2" t="inlineStr">
         <is>
-          <t>Solicitud y análisis de presupuestos</t>
+          <t>Tramitación de Subvenciones de Eficiencia Energética</t>
         </is>
       </c>
       <c r="D924" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
-        </is>
-      </c>
-      <c r="E924" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E924" s="2" t="n">
+        <v>1980</v>
+      </c>
       <c r="F924" s="2" t="n"/>
       <c r="G924" s="2" t="inlineStr">
         <is>
@@ -52407,22 +52411,24 @@
       </c>
       <c r="C925" s="2" t="inlineStr">
         <is>
-          <t>Fin de obra</t>
+          <t>Total Honorarios con Descuento por Cesión de CAES</t>
         </is>
       </c>
       <c r="D925" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
-        </is>
-      </c>
-      <c r="E925" s="2" t="n"/>
+          <t>SATE CON CESION DE CAES</t>
+        </is>
+      </c>
+      <c r="E925" s="2" t="n">
+        <v>10400</v>
+      </c>
       <c r="F925" s="2" t="n"/>
-      <c r="G925" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H925" s="2" t="n"/>
+      <c r="G925" s="2" t="inlineStr"/>
+      <c r="H925" s="2" t="inlineStr">
+        <is>
+          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
+        </is>
+      </c>
     </row>
     <row r="926">
       <c r="A926" s="2" t="inlineStr">
@@ -52437,12 +52443,12 @@
       </c>
       <c r="C926" s="2" t="inlineStr">
         <is>
-          <t>Coordinación de Seguridad y Salud</t>
+          <t>Toma de datos y modelado 3D</t>
         </is>
       </c>
       <c r="D926" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E926" s="2" t="n"/>
@@ -52467,12 +52473,12 @@
       </c>
       <c r="C927" s="2" t="inlineStr">
         <is>
-          <t>Certificado de Eficiencia Energética</t>
+          <t>Tramitación de Licencias y Permisos</t>
         </is>
       </c>
       <c r="D927" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>TRAMITACION LICENCIAS</t>
         </is>
       </c>
       <c r="E927" s="2" t="n"/>
@@ -52497,12 +52503,12 @@
       </c>
       <c r="C928" s="2" t="inlineStr">
         <is>
-          <t>Dirección Facultativa</t>
+          <t>Solicitud y análisis de presupuestos</t>
         </is>
       </c>
       <c r="D928" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E928" s="2" t="n"/>
@@ -52527,12 +52533,12 @@
       </c>
       <c r="C929" s="2" t="inlineStr">
         <is>
-          <t>CAES (no se cobran aparte)</t>
+          <t>Fin de obra</t>
         </is>
       </c>
       <c r="D929" s="2" t="inlineStr">
         <is>
-          <t>GESTION DE CAES</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E929" s="2" t="n"/>
@@ -52547,7 +52553,7 @@
     <row r="930">
       <c r="A930" s="2" t="inlineStr">
         <is>
-          <t>F237</t>
+          <t>F236</t>
         </is>
       </c>
       <c r="B930" s="2" t="inlineStr">
@@ -52557,23 +52563,27 @@
       </c>
       <c r="C930" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>Coordinación de Seguridad y Salud</t>
         </is>
       </c>
       <c r="D930" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="E930" s="2" t="n"/>
       <c r="F930" s="2" t="n"/>
-      <c r="G930" s="2" t="inlineStr"/>
+      <c r="G930" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H930" s="2" t="n"/>
     </row>
     <row r="931">
       <c r="A931" s="2" t="inlineStr">
         <is>
-          <t>F237</t>
+          <t>F236</t>
         </is>
       </c>
       <c r="B931" s="2" t="inlineStr">
@@ -52583,23 +52593,27 @@
       </c>
       <c r="C931" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>Certificado de Eficiencia Energética</t>
         </is>
       </c>
       <c r="D931" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E931" s="2" t="n"/>
       <c r="F931" s="2" t="n"/>
-      <c r="G931" s="2" t="inlineStr"/>
+      <c r="G931" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H931" s="2" t="n"/>
     </row>
     <row r="932">
       <c r="A932" s="2" t="inlineStr">
         <is>
-          <t>F237</t>
+          <t>F236</t>
         </is>
       </c>
       <c r="B932" s="2" t="inlineStr">
@@ -52609,23 +52623,27 @@
       </c>
       <c r="C932" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>Dirección Facultativa</t>
         </is>
       </c>
       <c r="D932" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E932" s="2" t="n"/>
       <c r="F932" s="2" t="n"/>
-      <c r="G932" s="2" t="inlineStr"/>
+      <c r="G932" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H932" s="2" t="n"/>
     </row>
     <row r="933">
       <c r="A933" s="2" t="inlineStr">
         <is>
-          <t>F237</t>
+          <t>F236</t>
         </is>
       </c>
       <c r="B933" s="2" t="inlineStr">
@@ -52635,17 +52653,21 @@
       </c>
       <c r="C933" s="2" t="inlineStr">
         <is>
-          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
+          <t>CAES (no se cobran aparte)</t>
         </is>
       </c>
       <c r="D933" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>GESTION DE CAES</t>
         </is>
       </c>
       <c r="E933" s="2" t="n"/>
       <c r="F933" s="2" t="n"/>
-      <c r="G933" s="2" t="inlineStr"/>
+      <c r="G933" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H933" s="2" t="n"/>
     </row>
     <row r="934">
@@ -52661,12 +52683,12 @@
       </c>
       <c r="C934" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D934" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E934" s="2" t="n"/>
@@ -52687,12 +52709,12 @@
       </c>
       <c r="C935" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D935" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>REDACCION PROYECTO</t>
         </is>
       </c>
       <c r="E935" s="2" t="n"/>
@@ -52713,12 +52735,12 @@
       </c>
       <c r="C936" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D936" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>TRAMITACION LICENCIAS</t>
         </is>
       </c>
       <c r="E936" s="2" t="n"/>
@@ -52729,27 +52751,25 @@
     <row r="937">
       <c r="A937" s="2" t="inlineStr">
         <is>
-          <t>F238</t>
+          <t>F237</t>
         </is>
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>BRUNETE 3. FUENLABRADA</t>
+          <t>ALTAMIRANO 32 MADRID</t>
         </is>
       </c>
       <c r="C937" s="2" t="inlineStr">
         <is>
-          <t>Modificación de proyecto: división del proyecto</t>
+          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
         </is>
       </c>
       <c r="D937" s="2" t="inlineStr">
         <is>
-          <t>MODIFICACION DE PROYECTO</t>
-        </is>
-      </c>
-      <c r="E937" s="2" t="n">
-        <v>1500</v>
-      </c>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
+        </is>
+      </c>
+      <c r="E937" s="2" t="n"/>
       <c r="F937" s="2" t="n"/>
       <c r="G937" s="2" t="inlineStr"/>
       <c r="H937" s="2" t="n"/>
@@ -52757,22 +52777,22 @@
     <row r="938">
       <c r="A938" s="2" t="inlineStr">
         <is>
-          <t>F239</t>
+          <t>F237</t>
         </is>
       </c>
       <c r="B938" s="2" t="inlineStr">
         <is>
-          <t>BRAVO MURILLO 177 MADRID</t>
+          <t>ALTAMIRANO 32 MADRID</t>
         </is>
       </c>
       <c r="C938" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D938" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E938" s="2" t="n"/>
@@ -52783,22 +52803,22 @@
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
         <is>
-          <t>F239</t>
+          <t>F237</t>
         </is>
       </c>
       <c r="B939" s="2" t="inlineStr">
         <is>
-          <t>BRAVO MURILLO 177 MADRID</t>
+          <t>ALTAMIRANO 32 MADRID</t>
         </is>
       </c>
       <c r="C939" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D939" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="E939" s="2" t="n"/>
@@ -52809,22 +52829,22 @@
     <row r="940">
       <c r="A940" s="2" t="inlineStr">
         <is>
-          <t>F239</t>
+          <t>F237</t>
         </is>
       </c>
       <c r="B940" s="2" t="inlineStr">
         <is>
-          <t>BRAVO MURILLO 177 MADRID</t>
+          <t>ALTAMIRANO 32 MADRID</t>
         </is>
       </c>
       <c r="C940" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D940" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E940" s="2" t="n"/>
@@ -52835,25 +52855,27 @@
     <row r="941">
       <c r="A941" s="2" t="inlineStr">
         <is>
-          <t>F239</t>
+          <t>F238</t>
         </is>
       </c>
       <c r="B941" s="2" t="inlineStr">
         <is>
-          <t>BRAVO MURILLO 177 MADRID</t>
+          <t>BRUNETE 3. FUENLABRADA</t>
         </is>
       </c>
       <c r="C941" s="2" t="inlineStr">
         <is>
-          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
+          <t>Modificación de proyecto: división del proyecto</t>
         </is>
       </c>
       <c r="D941" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
-        </is>
-      </c>
-      <c r="E941" s="2" t="n"/>
+          <t>MODIFICACION DE PROYECTO</t>
+        </is>
+      </c>
+      <c r="E941" s="2" t="n">
+        <v>1500</v>
+      </c>
       <c r="F941" s="2" t="n"/>
       <c r="G941" s="2" t="inlineStr"/>
       <c r="H941" s="2" t="n"/>
@@ -52871,12 +52893,12 @@
       </c>
       <c r="C942" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D942" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E942" s="2" t="n"/>
@@ -52897,12 +52919,12 @@
       </c>
       <c r="C943" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D943" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>REDACCION PROYECTO</t>
         </is>
       </c>
       <c r="E943" s="2" t="n"/>
@@ -52923,49 +52945,41 @@
       </c>
       <c r="C944" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D944" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E944" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E944" s="2" t="n"/>
       <c r="F944" s="2" t="n"/>
       <c r="G944" s="2" t="inlineStr"/>
-      <c r="H944" s="2" t="inlineStr">
-        <is>
-          <t>100% a la firma del Plan de Seguridad y Salud</t>
-        </is>
-      </c>
+      <c r="H944" s="2" t="n"/>
     </row>
     <row r="945">
       <c r="A945" s="2" t="inlineStr">
         <is>
-          <t>F240</t>
+          <t>F239</t>
         </is>
       </c>
       <c r="B945" s="2" t="inlineStr">
         <is>
-          <t>VILLAMANIN 37 MADRID</t>
+          <t>BRAVO MURILLO 177 MADRID</t>
         </is>
       </c>
       <c r="C945" s="2" t="inlineStr">
         <is>
-          <t>Modificación de proyecto: modificado de proyecto visado para licencia y Next Generation</t>
+          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
         </is>
       </c>
       <c r="D945" s="2" t="inlineStr">
         <is>
-          <t>MODIFICACION DE PROYECTO</t>
-        </is>
-      </c>
-      <c r="E945" s="2" t="n">
-        <v>2500</v>
-      </c>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
+        </is>
+      </c>
+      <c r="E945" s="2" t="n"/>
       <c r="F945" s="2" t="n"/>
       <c r="G945" s="2" t="inlineStr"/>
       <c r="H945" s="2" t="n"/>
@@ -52973,180 +52987,164 @@
     <row r="946">
       <c r="A946" s="2" t="inlineStr">
         <is>
-          <t>F241</t>
+          <t>F239</t>
         </is>
       </c>
       <c r="B946" s="2" t="inlineStr">
         <is>
-          <t>FELIPE ALVAREZ 28 MADRID</t>
+          <t>BRAVO MURILLO 177 MADRID</t>
         </is>
       </c>
       <c r="C946" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D946" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E946" s="2" t="n"/>
       <c r="F946" s="2" t="n"/>
-      <c r="G946" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G946" s="2" t="inlineStr"/>
       <c r="H946" s="2" t="n"/>
     </row>
     <row r="947">
       <c r="A947" s="2" t="inlineStr">
         <is>
-          <t>F241</t>
+          <t>F239</t>
         </is>
       </c>
       <c r="B947" s="2" t="inlineStr">
         <is>
-          <t>FELIPE ALVAREZ 28 MADRID</t>
+          <t>BRAVO MURILLO 177 MADRID</t>
         </is>
       </c>
       <c r="C947" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D947" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E947" s="2" t="n"/>
       <c r="F947" s="2" t="n"/>
-      <c r="G947" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G947" s="2" t="inlineStr"/>
       <c r="H947" s="2" t="n"/>
     </row>
     <row r="948">
       <c r="A948" s="2" t="inlineStr">
         <is>
-          <t>F241</t>
+          <t>F239</t>
         </is>
       </c>
       <c r="B948" s="2" t="inlineStr">
         <is>
-          <t>FELIPE ALVAREZ 28 MADRID</t>
+          <t>BRAVO MURILLO 177 MADRID</t>
         </is>
       </c>
       <c r="C948" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D948" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
-        </is>
-      </c>
-      <c r="E948" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E948" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F948" s="2" t="n"/>
-      <c r="G948" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H948" s="2" t="n"/>
+      <c r="G948" s="2" t="inlineStr"/>
+      <c r="H948" s="2" t="inlineStr">
+        <is>
+          <t>100% a la firma del Plan de Seguridad y Salud</t>
+        </is>
+      </c>
     </row>
     <row r="949">
       <c r="A949" s="2" t="inlineStr">
         <is>
-          <t>F241</t>
+          <t>F240</t>
         </is>
       </c>
       <c r="B949" s="2" t="inlineStr">
         <is>
-          <t>FELIPE ALVAREZ 28 MADRID</t>
+          <t>VILLAMANIN 37 MADRID</t>
         </is>
       </c>
       <c r="C949" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Subvenciones (Gestión de Subvenciones Accesibilidad)</t>
+          <t>Modificación de proyecto: modificado de proyecto visado para licencia y Next Generation</t>
         </is>
       </c>
       <c r="D949" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
+          <t>MODIFICACION DE PROYECTO</t>
         </is>
       </c>
       <c r="E949" s="2" t="n">
-        <v>2225</v>
-      </c>
-      <c r="F949" s="2" t="n">
-        <v>3.5</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="F949" s="2" t="n"/>
       <c r="G949" s="2" t="inlineStr"/>
-      <c r="H949" s="2" t="inlineStr">
-        <is>
-          <t>A la concesión de cada subvención, 3.5% del importe concedido tras su ingreso</t>
-        </is>
-      </c>
+      <c r="H949" s="2" t="n"/>
     </row>
     <row r="950">
       <c r="A950" s="2" t="inlineStr">
         <is>
-          <t>F242</t>
+          <t>F241</t>
         </is>
       </c>
       <c r="B950" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO FATOU 24 MADRID</t>
+          <t>FELIPE ALVAREZ 28 MADRID</t>
         </is>
       </c>
       <c r="C950" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="D950" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E950" s="2" t="n">
-        <v>2225</v>
-      </c>
-      <c r="F950" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G950" s="2" t="inlineStr"/>
-      <c r="H950" s="2" t="inlineStr">
-        <is>
-          <t>Doc. técnica: 50% a la contratación (junio 2026), 50% un mes después (julio 2026); 3,5% a la concesión de cada subvención</t>
-        </is>
-      </c>
+          <t>IEE</t>
+        </is>
+      </c>
+      <c r="E950" s="2" t="n"/>
+      <c r="F950" s="2" t="n"/>
+      <c r="G950" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H950" s="2" t="n"/>
     </row>
     <row r="951">
       <c r="A951" s="2" t="inlineStr">
         <is>
-          <t>F242</t>
+          <t>F241</t>
         </is>
       </c>
       <c r="B951" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO FATOU 24 MADRID</t>
+          <t>FELIPE ALVAREZ 28 MADRID</t>
         </is>
       </c>
       <c r="C951" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="D951" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E951" s="2" t="n"/>
@@ -53161,22 +53159,22 @@
     <row r="952">
       <c r="A952" s="2" t="inlineStr">
         <is>
-          <t>F242</t>
+          <t>F241</t>
         </is>
       </c>
       <c r="B952" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO FATOU 24 MADRID</t>
+          <t>FELIPE ALVAREZ 28 MADRID</t>
         </is>
       </c>
       <c r="C952" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D952" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E952" s="2" t="n"/>
@@ -53191,168 +53189,192 @@
     <row r="953">
       <c r="A953" s="2" t="inlineStr">
         <is>
-          <t>F242</t>
+          <t>F241</t>
         </is>
       </c>
       <c r="B953" s="2" t="inlineStr">
         <is>
-          <t>FRANCISCO FATOU 24 MADRID</t>
+          <t>FELIPE ALVAREZ 28 MADRID</t>
         </is>
       </c>
       <c r="C953" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>Tramitación de Subvenciones (Gestión de Subvenciones Accesibilidad)</t>
         </is>
       </c>
       <c r="D953" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
-        </is>
-      </c>
-      <c r="E953" s="2" t="n"/>
-      <c r="F953" s="2" t="n"/>
-      <c r="G953" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H953" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E953" s="2" t="n">
+        <v>2225</v>
+      </c>
+      <c r="F953" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G953" s="2" t="inlineStr"/>
+      <c r="H953" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión de cada subvención, 3.5% del importe concedido tras su ingreso</t>
+        </is>
+      </c>
     </row>
     <row r="954">
       <c r="A954" s="2" t="inlineStr">
         <is>
-          <t>F243</t>
+          <t>F242</t>
         </is>
       </c>
       <c r="B954" s="2" t="inlineStr">
         <is>
-          <t>AV CASTILLA 2-4-6 ALCALA DE HENARES</t>
+          <t>FRANCISCO FATOU 24 MADRID</t>
         </is>
       </c>
       <c r="C954" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
         </is>
       </c>
       <c r="D954" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E954" s="2" t="n">
-        <v>920</v>
-      </c>
-      <c r="F954" s="2" t="n"/>
+        <v>2225</v>
+      </c>
+      <c r="F954" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G954" s="2" t="inlineStr"/>
       <c r="H954" s="2" t="inlineStr">
         <is>
-          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
+          <t>Doc. técnica: 50% a la contratación (junio 2026), 50% un mes después (julio 2026); 3,5% a la concesión de cada subvención</t>
         </is>
       </c>
     </row>
     <row r="955">
       <c r="A955" s="2" t="inlineStr">
         <is>
-          <t>F244</t>
+          <t>F242</t>
         </is>
       </c>
       <c r="B955" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>FRANCISCO FATOU 24 MADRID</t>
         </is>
       </c>
       <c r="C955" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
         </is>
       </c>
       <c r="D955" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="E955" s="2" t="n"/>
       <c r="F955" s="2" t="n"/>
-      <c r="G955" s="2" t="inlineStr"/>
+      <c r="G955" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H955" s="2" t="n"/>
     </row>
     <row r="956">
       <c r="A956" s="2" t="inlineStr">
         <is>
-          <t>F244</t>
+          <t>F242</t>
         </is>
       </c>
       <c r="B956" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>FRANCISCO FATOU 24 MADRID</t>
         </is>
       </c>
       <c r="C956" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
         </is>
       </c>
       <c r="D956" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E956" s="2" t="n"/>
       <c r="F956" s="2" t="n"/>
-      <c r="G956" s="2" t="inlineStr"/>
+      <c r="G956" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H956" s="2" t="n"/>
     </row>
     <row r="957">
       <c r="A957" s="2" t="inlineStr">
         <is>
-          <t>F244</t>
+          <t>F242</t>
         </is>
       </c>
       <c r="B957" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>FRANCISCO FATOU 24 MADRID</t>
         </is>
       </c>
       <c r="C957" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D957" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E957" s="2" t="n"/>
       <c r="F957" s="2" t="n"/>
-      <c r="G957" s="2" t="inlineStr"/>
+      <c r="G957" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H957" s="2" t="n"/>
     </row>
     <row r="958">
       <c r="A958" s="2" t="inlineStr">
         <is>
-          <t>F244</t>
+          <t>F243</t>
         </is>
       </c>
       <c r="B958" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>AV CASTILLA 2-4-6 ALCALA DE HENARES</t>
         </is>
       </c>
       <c r="C958" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D958" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
-        </is>
-      </c>
-      <c r="E958" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E958" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F958" s="2" t="n"/>
       <c r="G958" s="2" t="inlineStr"/>
-      <c r="H958" s="2" t="n"/>
+      <c r="H958" s="2" t="inlineStr">
+        <is>
+          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
+        </is>
+      </c>
     </row>
     <row r="959">
       <c r="A959" s="2" t="inlineStr">
@@ -53367,24 +53389,18 @@
       </c>
       <c r="C959" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D959" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E959" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
+        </is>
+      </c>
+      <c r="E959" s="2" t="n"/>
       <c r="F959" s="2" t="n"/>
       <c r="G959" s="2" t="inlineStr"/>
-      <c r="H959" s="2" t="inlineStr">
-        <is>
-          <t>100% a la firma del Plan de Seguridad y Salud</t>
-        </is>
-      </c>
+      <c r="H959" s="2" t="n"/>
     </row>
     <row r="960">
       <c r="A960" s="2" t="inlineStr">
@@ -53399,12 +53415,12 @@
       </c>
       <c r="C960" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D960" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>REDACCION PROYECTO</t>
         </is>
       </c>
       <c r="E960" s="2" t="n"/>
@@ -53415,123 +53431,111 @@
     <row r="961">
       <c r="A961" s="2" t="inlineStr">
         <is>
-          <t>F245</t>
+          <t>F244</t>
         </is>
       </c>
       <c r="B961" s="2" t="inlineStr">
         <is>
-          <t>MAGDALENA 3 GETAFE</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C961" s="2" t="inlineStr">
         <is>
-          <t>Toma de datos y modelado 3D</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D961" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>TRAMITACION LICENCIAS</t>
         </is>
       </c>
       <c r="E961" s="2" t="n"/>
       <c r="F961" s="2" t="n"/>
-      <c r="G961" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G961" s="2" t="inlineStr"/>
       <c r="H961" s="2" t="n"/>
     </row>
     <row r="962">
       <c r="A962" s="2" t="inlineStr">
         <is>
-          <t>F245</t>
+          <t>F244</t>
         </is>
       </c>
       <c r="B962" s="2" t="inlineStr">
         <is>
-          <t>MAGDALENA 3 GETAFE</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C962" s="2" t="inlineStr">
         <is>
-          <t>Proyecto (Redacción del Proyecto Básico y de Ejecución)</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D962" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
-        </is>
-      </c>
-      <c r="E962" s="2" t="n">
-        <v>3500</v>
-      </c>
+          <t>CERTIFICADO FIN DE OBRA</t>
+        </is>
+      </c>
+      <c r="E962" s="2" t="n"/>
       <c r="F962" s="2" t="n"/>
       <c r="G962" s="2" t="inlineStr"/>
-      <c r="H962" s="2" t="inlineStr">
-        <is>
-          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
-        </is>
-      </c>
+      <c r="H962" s="2" t="n"/>
     </row>
     <row r="963">
       <c r="A963" s="2" t="inlineStr">
         <is>
-          <t>F245</t>
+          <t>F244</t>
         </is>
       </c>
       <c r="B963" s="2" t="inlineStr">
         <is>
-          <t>MAGDALENA 3 GETAFE</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C963" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Licencia</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D963" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
-        </is>
-      </c>
-      <c r="E963" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E963" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F963" s="2" t="n"/>
-      <c r="G963" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H963" s="2" t="n"/>
+      <c r="G963" s="2" t="inlineStr"/>
+      <c r="H963" s="2" t="inlineStr">
+        <is>
+          <t>100% a la firma del Plan de Seguridad y Salud</t>
+        </is>
+      </c>
     </row>
     <row r="964">
       <c r="A964" s="2" t="inlineStr">
         <is>
-          <t>F245</t>
+          <t>F244</t>
         </is>
       </c>
       <c r="B964" s="2" t="inlineStr">
         <is>
-          <t>MAGDALENA 3 GETAFE</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C964" s="2" t="inlineStr">
         <is>
-          <t>Fin de obra</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D964" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E964" s="2" t="n"/>
       <c r="F964" s="2" t="n"/>
-      <c r="G964" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G964" s="2" t="inlineStr"/>
       <c r="H964" s="2" t="n"/>
     </row>
     <row r="965">
@@ -53547,12 +53551,12 @@
       </c>
       <c r="C965" s="2" t="inlineStr">
         <is>
-          <t>Dirección Facultativa</t>
+          <t>Toma de datos y modelado 3D</t>
         </is>
       </c>
       <c r="D965" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E965" s="2" t="n"/>
@@ -53567,142 +53571,156 @@
     <row r="966">
       <c r="A966" s="2" t="inlineStr">
         <is>
-          <t>F246</t>
+          <t>F245</t>
         </is>
       </c>
       <c r="B966" s="2" t="inlineStr">
         <is>
-          <t>NAZARET 32 BIS FUENLABRADA</t>
+          <t>MAGDALENA 3 GETAFE</t>
         </is>
       </c>
       <c r="C966" s="2" t="inlineStr">
         <is>
-          <t>Gestión de Subvenciones de Eficiencia Energética</t>
+          <t>Proyecto (Redacción del Proyecto Básico y de Ejecución)</t>
         </is>
       </c>
       <c r="D966" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E966" s="2" t="n"/>
-      <c r="F966" s="2" t="n">
-        <v>2</v>
-      </c>
+          <t>REDACCION PROYECTO</t>
+        </is>
+      </c>
+      <c r="E966" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="F966" s="2" t="n"/>
       <c r="G966" s="2" t="inlineStr"/>
       <c r="H966" s="2" t="inlineStr">
         <is>
-          <t>A la concesión, 2% del importe total concedido tras su ingreso en la cuenta de la comunidad</t>
+          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
         </is>
       </c>
     </row>
     <row r="967">
       <c r="A967" s="2" t="inlineStr">
         <is>
-          <t>F247</t>
+          <t>F245</t>
         </is>
       </c>
       <c r="B967" s="2" t="inlineStr">
         <is>
-          <t>PUERTO DE COTOS 11 MADRID</t>
+          <t>MAGDALENA 3 GETAFE</t>
         </is>
       </c>
       <c r="C967" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>Tramitación de Licencia</t>
         </is>
       </c>
       <c r="D967" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>TRAMITACION LICENCIAS</t>
         </is>
       </c>
       <c r="E967" s="2" t="n"/>
       <c r="F967" s="2" t="n"/>
-      <c r="G967" s="2" t="inlineStr"/>
+      <c r="G967" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H967" s="2" t="n"/>
     </row>
     <row r="968">
       <c r="A968" s="2" t="inlineStr">
         <is>
-          <t>F247</t>
+          <t>F245</t>
         </is>
       </c>
       <c r="B968" s="2" t="inlineStr">
         <is>
-          <t>PUERTO DE COTOS 11 MADRID</t>
+          <t>MAGDALENA 3 GETAFE</t>
         </is>
       </c>
       <c r="C968" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>Fin de obra</t>
         </is>
       </c>
       <c r="D968" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E968" s="2" t="n"/>
       <c r="F968" s="2" t="n"/>
-      <c r="G968" s="2" t="inlineStr"/>
+      <c r="G968" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H968" s="2" t="n"/>
     </row>
     <row r="969">
       <c r="A969" s="2" t="inlineStr">
         <is>
-          <t>F247</t>
+          <t>F245</t>
         </is>
       </c>
       <c r="B969" s="2" t="inlineStr">
         <is>
-          <t>PUERTO DE COTOS 11 MADRID</t>
+          <t>MAGDALENA 3 GETAFE</t>
         </is>
       </c>
       <c r="C969" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>Dirección Facultativa</t>
         </is>
       </c>
       <c r="D969" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E969" s="2" t="n"/>
       <c r="F969" s="2" t="n"/>
-      <c r="G969" s="2" t="inlineStr"/>
+      <c r="G969" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H969" s="2" t="n"/>
     </row>
     <row r="970">
       <c r="A970" s="2" t="inlineStr">
         <is>
-          <t>F247</t>
+          <t>F246</t>
         </is>
       </c>
       <c r="B970" s="2" t="inlineStr">
         <is>
-          <t>PUERTO DE COTOS 11 MADRID</t>
+          <t>NAZARET 32 BIS FUENLABRADA</t>
         </is>
       </c>
       <c r="C970" s="2" t="inlineStr">
         <is>
-          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
+          <t>Gestión de Subvenciones de Eficiencia Energética</t>
         </is>
       </c>
       <c r="D970" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E970" s="2" t="n"/>
-      <c r="F970" s="2" t="n"/>
-      <c r="G970" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H970" s="2" t="n"/>
+      <c r="F970" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G970" s="2" t="inlineStr"/>
+      <c r="H970" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión, 2% del importe total concedido tras su ingreso en la cuenta de la comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="971">
       <c r="A971" s="2" t="inlineStr">
@@ -53717,12 +53735,12 @@
       </c>
       <c r="C971" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D971" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E971" s="2" t="n"/>
@@ -53743,24 +53761,18 @@
       </c>
       <c r="C972" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D972" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E972" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>REDACCION PROYECTO</t>
+        </is>
+      </c>
+      <c r="E972" s="2" t="n"/>
       <c r="F972" s="2" t="n"/>
       <c r="G972" s="2" t="inlineStr"/>
-      <c r="H972" s="2" t="inlineStr">
-        <is>
-          <t>100% a la firma del Plan de Seguridad y Salud</t>
-        </is>
-      </c>
+      <c r="H972" s="2" t="n"/>
     </row>
     <row r="973">
       <c r="A973" s="2" t="inlineStr">
@@ -53775,26 +53787,18 @@
       </c>
       <c r="C973" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D973" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E973" s="2" t="n">
-        <v>1980</v>
-      </c>
-      <c r="F973" s="2" t="n">
-        <v>3.5</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E973" s="2" t="n"/>
+      <c r="F973" s="2" t="n"/>
       <c r="G973" s="2" t="inlineStr"/>
-      <c r="H973" s="2" t="inlineStr">
-        <is>
-          <t>Doc. técnica: 50% a la contratación, 50% a la entrega del Proyecto; 3,5% a la concesión de cada subvención</t>
-        </is>
-      </c>
+      <c r="H973" s="2" t="n"/>
     </row>
     <row r="974">
       <c r="A974" s="2" t="inlineStr">
@@ -53809,12 +53813,12 @@
       </c>
       <c r="C974" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
         </is>
       </c>
       <c r="D974" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E974" s="2" t="n"/>
@@ -53839,21 +53843,17 @@
       </c>
       <c r="C975" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D975" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E975" s="2" t="n"/>
       <c r="F975" s="2" t="n"/>
-      <c r="G975" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G975" s="2" t="inlineStr"/>
       <c r="H975" s="2" t="n"/>
     </row>
     <row r="976">
@@ -53869,33 +53869,39 @@
       </c>
       <c r="C976" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D976" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E976" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E976" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F976" s="2" t="n"/>
       <c r="G976" s="2" t="inlineStr"/>
-      <c r="H976" s="2" t="n"/>
+      <c r="H976" s="2" t="inlineStr">
+        <is>
+          <t>100% a la firma del Plan de Seguridad y Salud</t>
+        </is>
+      </c>
     </row>
     <row r="977">
       <c r="A977" s="2" t="inlineStr">
         <is>
-          <t>F248</t>
+          <t>F247</t>
         </is>
       </c>
       <c r="B977" s="2" t="inlineStr">
         <is>
-          <t>NURIA 28-32 MADRID</t>
+          <t>PUERTO DE COTOS 11 MADRID</t>
         </is>
       </c>
       <c r="C977" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD</t>
+          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
         </is>
       </c>
       <c r="D977" s="2" t="inlineStr">
@@ -53912,24 +53918,24 @@
       <c r="G977" s="2" t="inlineStr"/>
       <c r="H977" s="2" t="inlineStr">
         <is>
-          <t>Tramo fijo 100% a la contratación; 3,5% a la concesión de cada subvención</t>
+          <t>Doc. técnica: 50% a la contratación, 50% a la entrega del Proyecto; 3,5% a la concesión de cada subvención</t>
         </is>
       </c>
     </row>
     <row r="978">
       <c r="A978" s="2" t="inlineStr">
         <is>
-          <t>F248</t>
+          <t>F247</t>
         </is>
       </c>
       <c r="B978" s="2" t="inlineStr">
         <is>
-          <t>NURIA 28-32 MADRID</t>
+          <t>PUERTO DE COTOS 11 MADRID</t>
         </is>
       </c>
       <c r="C978" s="2" t="inlineStr">
         <is>
-          <t>Elaboración de Informe de Evaluación del Edificio</t>
+          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
         </is>
       </c>
       <c r="D978" s="2" t="inlineStr">
@@ -53949,17 +53955,17 @@
     <row r="979">
       <c r="A979" s="2" t="inlineStr">
         <is>
-          <t>F248</t>
+          <t>F247</t>
         </is>
       </c>
       <c r="B979" s="2" t="inlineStr">
         <is>
-          <t>NURIA 28-32 MADRID</t>
+          <t>PUERTO DE COTOS 11 MADRID</t>
         </is>
       </c>
       <c r="C979" s="2" t="inlineStr">
         <is>
-          <t>Certificado Energético</t>
+          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
         </is>
       </c>
       <c r="D979" s="2" t="inlineStr">
@@ -53979,86 +53985,82 @@
     <row r="980">
       <c r="A980" s="2" t="inlineStr">
         <is>
-          <t>F249</t>
+          <t>F247</t>
         </is>
       </c>
       <c r="B980" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>PUERTO DE COTOS 11 MADRID</t>
         </is>
       </c>
       <c r="C980" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D980" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E980" s="2" t="n">
-        <v>1980</v>
-      </c>
-      <c r="F980" s="2" t="n">
-        <v>3.5</v>
-      </c>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E980" s="2" t="n"/>
+      <c r="F980" s="2" t="n"/>
       <c r="G980" s="2" t="inlineStr"/>
-      <c r="H980" s="2" t="inlineStr">
-        <is>
-          <t>Documentación técnica: 100% a la contratación. Subvención: 3,5% a la concesión de cada subvención</t>
-        </is>
-      </c>
+      <c r="H980" s="2" t="n"/>
     </row>
     <row r="981">
       <c r="A981" s="2" t="inlineStr">
         <is>
-          <t>F249</t>
+          <t>F248</t>
         </is>
       </c>
       <c r="B981" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>NURIA 28-32 MADRID</t>
         </is>
       </c>
       <c r="C981" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD</t>
         </is>
       </c>
       <c r="D981" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
-        </is>
-      </c>
-      <c r="E981" s="2" t="n"/>
-      <c r="F981" s="2" t="n"/>
-      <c r="G981" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H981" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E981" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F981" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G981" s="2" t="inlineStr"/>
+      <c r="H981" s="2" t="inlineStr">
+        <is>
+          <t>Tramo fijo 100% a la contratación; 3,5% a la concesión de cada subvención</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" s="2" t="inlineStr">
         <is>
-          <t>F249</t>
+          <t>F248</t>
         </is>
       </c>
       <c r="B982" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>NURIA 28-32 MADRID</t>
         </is>
       </c>
       <c r="C982" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>Elaboración de Informe de Evaluación del Edificio</t>
         </is>
       </c>
       <c r="D982" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="E982" s="2" t="n"/>
@@ -54073,22 +54075,22 @@
     <row r="983">
       <c r="A983" s="2" t="inlineStr">
         <is>
-          <t>F249</t>
+          <t>F248</t>
         </is>
       </c>
       <c r="B983" s="2" t="inlineStr">
         <is>
-          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
+          <t>NURIA 28-32 MADRID</t>
         </is>
       </c>
       <c r="C983" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>Certificado Energético</t>
         </is>
       </c>
       <c r="D983" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E983" s="2" t="n"/>
@@ -54103,105 +54105,125 @@
     <row r="984">
       <c r="A984" s="2" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>F249</t>
         </is>
       </c>
       <c r="B984" s="2" t="inlineStr">
         <is>
-          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C984" s="2" t="inlineStr">
         <is>
-          <t>Toma de datos y modelado 3D</t>
+          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
         </is>
       </c>
       <c r="D984" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
-        </is>
-      </c>
-      <c r="E984" s="2" t="n"/>
-      <c r="F984" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E984" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F984" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G984" s="2" t="inlineStr"/>
-      <c r="H984" s="2" t="n"/>
+      <c r="H984" s="2" t="inlineStr">
+        <is>
+          <t>Documentación técnica: 100% a la contratación. Subvención: 3,5% a la concesión de cada subvención</t>
+        </is>
+      </c>
     </row>
     <row r="985">
       <c r="A985" s="2" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>F249</t>
         </is>
       </c>
       <c r="B985" s="2" t="inlineStr">
         <is>
-          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C985" s="2" t="inlineStr">
         <is>
-          <t>Redacción del Proyecto Básico y de Ejecución</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="D985" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="E985" s="2" t="n"/>
       <c r="F985" s="2" t="n"/>
-      <c r="G985" s="2" t="inlineStr"/>
+      <c r="G985" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H985" s="2" t="n"/>
     </row>
     <row r="986">
       <c r="A986" s="2" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>F249</t>
         </is>
       </c>
       <c r="B986" s="2" t="inlineStr">
         <is>
-          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C986" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Licencias y Permisos</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="D986" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E986" s="2" t="n"/>
       <c r="F986" s="2" t="n"/>
-      <c r="G986" s="2" t="inlineStr"/>
+      <c r="G986" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H986" s="2" t="n"/>
     </row>
     <row r="987">
       <c r="A987" s="2" t="inlineStr">
         <is>
-          <t>F250</t>
+          <t>F249</t>
         </is>
       </c>
       <c r="B987" s="2" t="inlineStr">
         <is>
-          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
+          <t>AV COLMENAR VIEJO 8 SAN SEBASTIAN DE LOS REYES</t>
         </is>
       </c>
       <c r="C987" s="2" t="inlineStr">
         <is>
-          <t>Fin de obra</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D987" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E987" s="2" t="n"/>
       <c r="F987" s="2" t="n"/>
-      <c r="G987" s="2" t="inlineStr"/>
+      <c r="G987" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H987" s="2" t="n"/>
     </row>
     <row r="988">
@@ -54217,12 +54239,12 @@
       </c>
       <c r="C988" s="2" t="inlineStr">
         <is>
-          <t>Coordinación de Seguridad y Salud</t>
+          <t>Toma de datos y modelado 3D</t>
         </is>
       </c>
       <c r="D988" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E988" s="2" t="n"/>
@@ -54243,26 +54265,18 @@
       </c>
       <c r="C989" s="2" t="inlineStr">
         <is>
-          <t>Gestión de Subvenciones Accesibilidad</t>
+          <t>Redacción del Proyecto Básico y de Ejecución</t>
         </is>
       </c>
       <c r="D989" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E989" s="2" t="n">
-        <v>1980</v>
-      </c>
-      <c r="F989" s="2" t="n">
-        <v>3.5</v>
-      </c>
+          <t>REDACCION PROYECTO</t>
+        </is>
+      </c>
+      <c r="E989" s="2" t="n"/>
+      <c r="F989" s="2" t="n"/>
       <c r="G989" s="2" t="inlineStr"/>
-      <c r="H989" s="2" t="inlineStr">
-        <is>
-          <t>A la contratación 100% tramo fijo; a la concesión de cada subvención tramo variable 3.5%</t>
-        </is>
-      </c>
+      <c r="H989" s="2" t="n"/>
     </row>
     <row r="990">
       <c r="A990" s="2" t="inlineStr">
@@ -54277,12 +54291,12 @@
       </c>
       <c r="C990" s="2" t="inlineStr">
         <is>
-          <t>Dirección Facultativa</t>
+          <t>Tramitación de Licencias y Permisos</t>
         </is>
       </c>
       <c r="D990" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>TRAMITACION LICENCIAS</t>
         </is>
       </c>
       <c r="E990" s="2" t="n"/>
@@ -54293,125 +54307,113 @@
     <row r="991">
       <c r="A991" s="2" t="inlineStr">
         <is>
-          <t>F251</t>
+          <t>F250</t>
         </is>
       </c>
       <c r="B991" s="2" t="inlineStr">
         <is>
-          <t>SAN IGNACIO 6 ALCORCÓN</t>
+          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
         </is>
       </c>
       <c r="C991" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Subvenciones (A éxito)</t>
+          <t>Fin de obra</t>
         </is>
       </c>
       <c r="D991" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E991" s="2" t="n"/>
-      <c r="F991" s="2" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="F991" s="2" t="n"/>
       <c r="G991" s="2" t="inlineStr"/>
-      <c r="H991" s="2" t="inlineStr">
-        <is>
-          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
-        </is>
-      </c>
+      <c r="H991" s="2" t="n"/>
     </row>
     <row r="992">
       <c r="A992" s="2" t="inlineStr">
         <is>
-          <t>F251</t>
+          <t>F250</t>
         </is>
       </c>
       <c r="B992" s="2" t="inlineStr">
         <is>
-          <t>SAN IGNACIO 6 ALCORCÓN</t>
+          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
         </is>
       </c>
       <c r="C992" s="2" t="inlineStr">
         <is>
-          <t>Documentación Técnica Anexa</t>
+          <t>Coordinación de Seguridad y Salud</t>
         </is>
       </c>
       <c r="D992" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E992" s="2" t="n">
-        <v>1980</v>
-      </c>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E992" s="2" t="n"/>
       <c r="F992" s="2" t="n"/>
       <c r="G992" s="2" t="inlineStr"/>
-      <c r="H992" s="2" t="inlineStr">
-        <is>
-          <t>A la contratación: 100%</t>
-        </is>
-      </c>
+      <c r="H992" s="2" t="n"/>
     </row>
     <row r="993">
       <c r="A993" s="2" t="inlineStr">
         <is>
-          <t>F251</t>
+          <t>F250</t>
         </is>
       </c>
       <c r="B993" s="2" t="inlineStr">
         <is>
-          <t>SAN IGNACIO 6 ALCORCÓN</t>
+          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
         </is>
       </c>
       <c r="C993" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+          <t>Gestión de Subvenciones Accesibilidad</t>
         </is>
       </c>
       <c r="D993" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
-        </is>
-      </c>
-      <c r="E993" s="2" t="n"/>
-      <c r="F993" s="2" t="n"/>
-      <c r="G993" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H993" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E993" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F993" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G993" s="2" t="inlineStr"/>
+      <c r="H993" s="2" t="inlineStr">
+        <is>
+          <t>A la contratación 100% tramo fijo; a la concesión de cada subvención tramo variable 3.5%</t>
+        </is>
+      </c>
     </row>
     <row r="994">
       <c r="A994" s="2" t="inlineStr">
         <is>
-          <t>F251</t>
+          <t>F250</t>
         </is>
       </c>
       <c r="B994" s="2" t="inlineStr">
         <is>
-          <t>SAN IGNACIO 6 ALCORCÓN</t>
+          <t>RAMON GOMEZ DE LA SERNA 45 MADRID</t>
         </is>
       </c>
       <c r="C994" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+          <t>Dirección Facultativa</t>
         </is>
       </c>
       <c r="D994" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E994" s="2" t="n"/>
       <c r="F994" s="2" t="n"/>
-      <c r="G994" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G994" s="2" t="inlineStr"/>
       <c r="H994" s="2" t="n"/>
     </row>
     <row r="995">
@@ -54427,37 +54429,39 @@
       </c>
       <c r="C995" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>Tramitación de Subvenciones (A éxito)</t>
         </is>
       </c>
       <c r="D995" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E995" s="2" t="n"/>
-      <c r="F995" s="2" t="n"/>
-      <c r="G995" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H995" s="2" t="n"/>
+      <c r="F995" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G995" s="2" t="inlineStr"/>
+      <c r="H995" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="996">
       <c r="A996" s="2" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>F251</t>
         </is>
       </c>
       <c r="B996" s="2" t="inlineStr">
         <is>
-          <t>MONTES DE TOLEDO 3 MADRID</t>
+          <t>SAN IGNACIO 6 ALCORCÓN</t>
         </is>
       </c>
       <c r="C996" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Subvenciones (Gestión de Subvenciones Accesibilidad)</t>
+          <t>Documentación Técnica Anexa</t>
         </is>
       </c>
       <c r="D996" s="2" t="inlineStr">
@@ -54468,30 +54472,28 @@
       <c r="E996" s="2" t="n">
         <v>1980</v>
       </c>
-      <c r="F996" s="2" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="F996" s="2" t="n"/>
       <c r="G996" s="2" t="inlineStr"/>
       <c r="H996" s="2" t="inlineStr">
         <is>
-          <t>A la concesión de cada subvención, 3.5% del importe concedido tras su ingreso</t>
+          <t>A la contratación: 100%</t>
         </is>
       </c>
     </row>
     <row r="997">
       <c r="A997" s="2" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>F251</t>
         </is>
       </c>
       <c r="B997" s="2" t="inlineStr">
         <is>
-          <t>MONTES DE TOLEDO 3 MADRID</t>
+          <t>SAN IGNACIO 6 ALCORCÓN</t>
         </is>
       </c>
       <c r="C997" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
         </is>
       </c>
       <c r="D997" s="2" t="inlineStr">
@@ -54511,17 +54513,17 @@
     <row r="998">
       <c r="A998" s="2" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>F251</t>
         </is>
       </c>
       <c r="B998" s="2" t="inlineStr">
         <is>
-          <t>MONTES DE TOLEDO 3 MADRID</t>
+          <t>SAN IGNACIO 6 ALCORCÓN</t>
         </is>
       </c>
       <c r="C998" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
         </is>
       </c>
       <c r="D998" s="2" t="inlineStr">
@@ -54541,12 +54543,12 @@
     <row r="999">
       <c r="A999" s="2" t="inlineStr">
         <is>
-          <t>F252</t>
+          <t>F251</t>
         </is>
       </c>
       <c r="B999" s="2" t="inlineStr">
         <is>
-          <t>MONTES DE TOLEDO 3 MADRID</t>
+          <t>SAN IGNACIO 6 ALCORCÓN</t>
         </is>
       </c>
       <c r="C999" s="2" t="inlineStr">
@@ -54571,7 +54573,7 @@
     <row r="1000">
       <c r="A1000" s="2" t="inlineStr">
         <is>
-          <t>F253</t>
+          <t>F252</t>
         </is>
       </c>
       <c r="B1000" s="2" t="inlineStr">
@@ -54581,27 +54583,31 @@
       </c>
       <c r="C1000" s="2" t="inlineStr">
         <is>
-          <t>Toma de datos y modelado 3D</t>
+          <t>Tramitación de Subvenciones (Gestión de Subvenciones Accesibilidad)</t>
         </is>
       </c>
       <c r="D1000" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
-        </is>
-      </c>
-      <c r="E1000" s="2" t="n"/>
-      <c r="F1000" s="2" t="n"/>
-      <c r="G1000" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1000" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E1000" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F1000" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1000" s="2" t="inlineStr"/>
+      <c r="H1000" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión de cada subvención, 3.5% del importe concedido tras su ingreso</t>
+        </is>
+      </c>
     </row>
     <row r="1001">
       <c r="A1001" s="2" t="inlineStr">
         <is>
-          <t>F253</t>
+          <t>F252</t>
         </is>
       </c>
       <c r="B1001" s="2" t="inlineStr">
@@ -54611,29 +54617,27 @@
       </c>
       <c r="C1001" s="2" t="inlineStr">
         <is>
-          <t>Proyecto (Redacción del Proyecto Básico y de Ejecución)</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="D1001" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
-        </is>
-      </c>
-      <c r="E1001" s="2" t="n">
-        <v>6580</v>
-      </c>
+          <t>IEE</t>
+        </is>
+      </c>
+      <c r="E1001" s="2" t="n"/>
       <c r="F1001" s="2" t="n"/>
-      <c r="G1001" s="2" t="inlineStr"/>
-      <c r="H1001" s="2" t="inlineStr">
-        <is>
-          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
-        </is>
-      </c>
+      <c r="G1001" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1001" s="2" t="n"/>
     </row>
     <row r="1002">
       <c r="A1002" s="2" t="inlineStr">
         <is>
-          <t>F253</t>
+          <t>F252</t>
         </is>
       </c>
       <c r="B1002" s="2" t="inlineStr">
@@ -54643,12 +54647,12 @@
       </c>
       <c r="C1002" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Licencias y Permisos</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="D1002" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E1002" s="2" t="n"/>
@@ -54663,7 +54667,7 @@
     <row r="1003">
       <c r="A1003" s="2" t="inlineStr">
         <is>
-          <t>F253</t>
+          <t>F252</t>
         </is>
       </c>
       <c r="B1003" s="2" t="inlineStr">
@@ -54673,7 +54677,7 @@
       </c>
       <c r="C1003" s="2" t="inlineStr">
         <is>
-          <t>Solicitud y análisis de presupuestos</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D1003" s="2" t="inlineStr">
@@ -54703,12 +54707,12 @@
       </c>
       <c r="C1004" s="2" t="inlineStr">
         <is>
-          <t>Fin de obra</t>
+          <t>Toma de datos y modelado 3D</t>
         </is>
       </c>
       <c r="D1004" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E1004" s="2" t="n"/>
@@ -54733,22 +54737,24 @@
       </c>
       <c r="C1005" s="2" t="inlineStr">
         <is>
-          <t>Dirección Facultativa</t>
+          <t>Proyecto (Redacción del Proyecto Básico y de Ejecución)</t>
         </is>
       </c>
       <c r="D1005" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E1005" s="2" t="n"/>
+          <t>REDACCION PROYECTO</t>
+        </is>
+      </c>
+      <c r="E1005" s="2" t="n">
+        <v>6580</v>
+      </c>
       <c r="F1005" s="2" t="n"/>
-      <c r="G1005" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1005" s="2" t="n"/>
+      <c r="G1005" s="2" t="inlineStr"/>
+      <c r="H1005" s="2" t="inlineStr">
+        <is>
+          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
+        </is>
+      </c>
     </row>
     <row r="1006">
       <c r="A1006" s="2" t="inlineStr">
@@ -54763,175 +54769,171 @@
       </c>
       <c r="C1006" s="2" t="inlineStr">
         <is>
-          <t>Coordinación de Seguridad y Salud</t>
+          <t>Tramitación de Licencias y Permisos</t>
         </is>
       </c>
       <c r="D1006" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E1006" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E1006" s="2" t="n"/>
       <c r="F1006" s="2" t="n"/>
-      <c r="G1006" s="2" t="inlineStr"/>
-      <c r="H1006" s="2" t="inlineStr">
-        <is>
-          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
-        </is>
-      </c>
+      <c r="G1006" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1006" s="2" t="n"/>
     </row>
     <row r="1007">
       <c r="A1007" s="2" t="inlineStr">
         <is>
-          <t>F254</t>
+          <t>F253</t>
         </is>
       </c>
       <c r="B1007" s="2" t="inlineStr">
         <is>
-          <t>CASTILLA 3 TORRE 5 AZUQUECA DE HENARES</t>
+          <t>MONTES DE TOLEDO 3 MADRID</t>
         </is>
       </c>
       <c r="C1007" s="2" t="inlineStr">
         <is>
-          <t>INFORME</t>
+          <t>Solicitud y análisis de presupuestos</t>
         </is>
       </c>
       <c r="D1007" s="2" t="inlineStr">
         <is>
-          <t>INFORME PERICIAL</t>
-        </is>
-      </c>
-      <c r="E1007" s="2" t="n">
-        <v>2000</v>
-      </c>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
+        </is>
+      </c>
+      <c r="E1007" s="2" t="n"/>
       <c r="F1007" s="2" t="n"/>
-      <c r="G1007" s="2" t="inlineStr"/>
+      <c r="G1007" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1007" s="2" t="n"/>
     </row>
     <row r="1008">
       <c r="A1008" s="2" t="inlineStr">
         <is>
-          <t>F255</t>
+          <t>F253</t>
         </is>
       </c>
       <c r="B1008" s="2" t="inlineStr">
         <is>
-          <t>PRINCIPE 18 MADRID</t>
+          <t>MONTES DE TOLEDO 3 MADRID</t>
         </is>
       </c>
       <c r="C1008" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Subvenciones (A éxito)</t>
+          <t>Fin de obra</t>
         </is>
       </c>
       <c r="D1008" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E1008" s="2" t="n"/>
-      <c r="F1008" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G1008" s="2" t="inlineStr"/>
-      <c r="H1008" s="2" t="inlineStr">
-        <is>
-          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
-        </is>
-      </c>
+      <c r="F1008" s="2" t="n"/>
+      <c r="G1008" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1008" s="2" t="n"/>
     </row>
     <row r="1009">
       <c r="A1009" s="2" t="inlineStr">
         <is>
-          <t>F255</t>
+          <t>F253</t>
         </is>
       </c>
       <c r="B1009" s="2" t="inlineStr">
         <is>
-          <t>PRINCIPE 18 MADRID</t>
+          <t>MONTES DE TOLEDO 3 MADRID</t>
         </is>
       </c>
       <c r="C1009" s="2" t="inlineStr">
         <is>
-          <t>Documentación Técnica Anexa</t>
+          <t>Dirección Facultativa</t>
         </is>
       </c>
       <c r="D1009" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E1009" s="2" t="n">
-        <v>1980</v>
-      </c>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E1009" s="2" t="n"/>
       <c r="F1009" s="2" t="n"/>
-      <c r="G1009" s="2" t="inlineStr"/>
-      <c r="H1009" s="2" t="inlineStr">
-        <is>
-          <t>A la contratación: 100%</t>
-        </is>
-      </c>
+      <c r="G1009" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1009" s="2" t="n"/>
     </row>
     <row r="1010">
       <c r="A1010" s="2" t="inlineStr">
         <is>
-          <t>F255</t>
+          <t>F253</t>
         </is>
       </c>
       <c r="B1010" s="2" t="inlineStr">
         <is>
-          <t>PRINCIPE 18 MADRID</t>
+          <t>MONTES DE TOLEDO 3 MADRID</t>
         </is>
       </c>
       <c r="C1010" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+          <t>Coordinación de Seguridad y Salud</t>
         </is>
       </c>
       <c r="D1010" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
-        </is>
-      </c>
-      <c r="E1010" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E1010" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F1010" s="2" t="n"/>
-      <c r="G1010" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1010" s="2" t="n"/>
+      <c r="G1010" s="2" t="inlineStr"/>
+      <c r="H1010" s="2" t="inlineStr">
+        <is>
+          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
+        </is>
+      </c>
     </row>
     <row r="1011">
       <c r="A1011" s="2" t="inlineStr">
         <is>
-          <t>F255</t>
+          <t>F254</t>
         </is>
       </c>
       <c r="B1011" s="2" t="inlineStr">
         <is>
-          <t>PRINCIPE 18 MADRID</t>
+          <t>CASTILLA 3 TORRE 5 AZUQUECA DE HENARES</t>
         </is>
       </c>
       <c r="C1011" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+          <t>INFORME</t>
         </is>
       </c>
       <c r="D1011" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
-        </is>
-      </c>
-      <c r="E1011" s="2" t="n"/>
+          <t>INFORME PERICIAL</t>
+        </is>
+      </c>
+      <c r="E1011" s="2" t="n">
+        <v>2000</v>
+      </c>
       <c r="F1011" s="2" t="n"/>
-      <c r="G1011" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1011" s="2" t="inlineStr"/>
       <c r="H1011" s="2" t="n"/>
     </row>
     <row r="1012">
@@ -54947,158 +54949,178 @@
       </c>
       <c r="C1012" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>Tramitación de Subvenciones (A éxito)</t>
         </is>
       </c>
       <c r="D1012" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E1012" s="2" t="n"/>
-      <c r="F1012" s="2" t="n"/>
-      <c r="G1012" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1012" s="2" t="n"/>
+      <c r="F1012" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1012" s="2" t="inlineStr"/>
+      <c r="H1012" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="1013">
       <c r="A1013" s="2" t="inlineStr">
         <is>
-          <t>F256</t>
+          <t>F255</t>
         </is>
       </c>
       <c r="B1013" s="2" t="inlineStr">
         <is>
-          <t>CASTILLA 13 PINTO</t>
+          <t>PRINCIPE 18 MADRID</t>
         </is>
       </c>
       <c r="C1013" s="2" t="inlineStr">
         <is>
-          <t>Coordinación de Seguridad y Salud</t>
+          <t>Documentación Técnica Anexa</t>
         </is>
       </c>
       <c r="D1013" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E1013" s="2" t="n">
-        <v>920</v>
+        <v>1980</v>
       </c>
       <c r="F1013" s="2" t="n"/>
       <c r="G1013" s="2" t="inlineStr"/>
       <c r="H1013" s="2" t="inlineStr">
         <is>
-          <t>100% a la firma del Plan de Seguridad y Salud</t>
+          <t>A la contratación: 100%</t>
         </is>
       </c>
     </row>
     <row r="1014">
       <c r="A1014" s="2" t="inlineStr">
         <is>
-          <t>F257</t>
+          <t>F255</t>
         </is>
       </c>
       <c r="B1014" s="2" t="inlineStr">
         <is>
-          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
+          <t>PRINCIPE 18 MADRID</t>
         </is>
       </c>
       <c r="C1014" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
         </is>
       </c>
       <c r="D1014" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="E1014" s="2" t="n"/>
       <c r="F1014" s="2" t="n"/>
-      <c r="G1014" s="2" t="inlineStr"/>
+      <c r="G1014" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1014" s="2" t="n"/>
     </row>
     <row r="1015">
       <c r="A1015" s="2" t="inlineStr">
         <is>
-          <t>F257</t>
+          <t>F255</t>
         </is>
       </c>
       <c r="B1015" s="2" t="inlineStr">
         <is>
-          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
+          <t>PRINCIPE 18 MADRID</t>
         </is>
       </c>
       <c r="C1015" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
         </is>
       </c>
       <c r="D1015" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E1015" s="2" t="n"/>
       <c r="F1015" s="2" t="n"/>
-      <c r="G1015" s="2" t="inlineStr"/>
+      <c r="G1015" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1015" s="2" t="n"/>
     </row>
     <row r="1016">
       <c r="A1016" s="2" t="inlineStr">
         <is>
-          <t>F257</t>
+          <t>F255</t>
         </is>
       </c>
       <c r="B1016" s="2" t="inlineStr">
         <is>
-          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
+          <t>PRINCIPE 18 MADRID</t>
         </is>
       </c>
       <c r="C1016" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D1016" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E1016" s="2" t="n"/>
       <c r="F1016" s="2" t="n"/>
-      <c r="G1016" s="2" t="inlineStr"/>
+      <c r="G1016" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1016" s="2" t="n"/>
     </row>
     <row r="1017">
       <c r="A1017" s="2" t="inlineStr">
         <is>
-          <t>F257</t>
+          <t>F256</t>
         </is>
       </c>
       <c r="B1017" s="2" t="inlineStr">
         <is>
-          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
+          <t>CASTILLA 13 PINTO</t>
         </is>
       </c>
       <c r="C1017" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>Coordinación de Seguridad y Salud</t>
         </is>
       </c>
       <c r="D1017" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
-        </is>
-      </c>
-      <c r="E1017" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E1017" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F1017" s="2" t="n"/>
       <c r="G1017" s="2" t="inlineStr"/>
-      <c r="H1017" s="2" t="n"/>
+      <c r="H1017" s="2" t="inlineStr">
+        <is>
+          <t>100% a la firma del Plan de Seguridad y Salud</t>
+        </is>
+      </c>
     </row>
     <row r="1018">
       <c r="A1018" s="2" t="inlineStr">
@@ -55113,12 +55135,12 @@
       </c>
       <c r="C1018" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D1018" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E1018" s="2" t="n"/>
@@ -55139,12 +55161,12 @@
       </c>
       <c r="C1019" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D1019" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>REDACCION PROYECTO</t>
         </is>
       </c>
       <c r="E1019" s="2" t="n"/>
@@ -55155,127 +55177,105 @@
     <row r="1020">
       <c r="A1020" s="2" t="inlineStr">
         <is>
-          <t>F258</t>
+          <t>F257</t>
         </is>
       </c>
       <c r="B1020" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE LA HABANA 80 MADRID</t>
+          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
         </is>
       </c>
       <c r="C1020" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D1020" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E1020" s="2" t="n">
-        <v>1980</v>
-      </c>
-      <c r="F1020" s="2" t="n">
-        <v>3.5</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E1020" s="2" t="n"/>
+      <c r="F1020" s="2" t="n"/>
       <c r="G1020" s="2" t="inlineStr"/>
-      <c r="H1020" s="2" t="inlineStr">
-        <is>
-          <t>Documentación técnica: 100% a la contratación. Subvención: 3,5% a la concesión de cada subvención</t>
-        </is>
-      </c>
+      <c r="H1020" s="2" t="n"/>
     </row>
     <row r="1021">
       <c r="A1021" s="2" t="inlineStr">
         <is>
-          <t>F258</t>
+          <t>F257</t>
         </is>
       </c>
       <c r="B1021" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE LA HABANA 80 MADRID</t>
+          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
         </is>
       </c>
       <c r="C1021" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES DE EFICIENCIA ENERGÉTICA</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D1021" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E1021" s="2" t="n"/>
-      <c r="F1021" s="2" t="n">
-        <v>3.5</v>
-      </c>
+      <c r="F1021" s="2" t="n"/>
       <c r="G1021" s="2" t="inlineStr"/>
-      <c r="H1021" s="2" t="inlineStr">
-        <is>
-          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
-        </is>
-      </c>
+      <c r="H1021" s="2" t="n"/>
     </row>
     <row r="1022">
       <c r="A1022" s="2" t="inlineStr">
         <is>
-          <t>F258</t>
+          <t>F257</t>
         </is>
       </c>
       <c r="B1022" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE LA HABANA 80 MADRID</t>
+          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
         </is>
       </c>
       <c r="C1022" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D1022" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="E1022" s="2" t="n"/>
       <c r="F1022" s="2" t="n"/>
-      <c r="G1022" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1022" s="2" t="inlineStr"/>
       <c r="H1022" s="2" t="n"/>
     </row>
     <row r="1023">
       <c r="A1023" s="2" t="inlineStr">
         <is>
-          <t>F258</t>
+          <t>F257</t>
         </is>
       </c>
       <c r="B1023" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE LA HABANA 80 MADRID</t>
+          <t>AV LOS PRINCIPES DE ESPAÑA 17 Y 19 COSLADA</t>
         </is>
       </c>
       <c r="C1023" s="2" t="inlineStr">
         <is>
-          <t>LIBRO DEL EDIFICIO</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D1023" s="2" t="inlineStr">
         <is>
-          <t>LEE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E1023" s="2" t="n"/>
       <c r="F1023" s="2" t="n"/>
-      <c r="G1023" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1023" s="2" t="inlineStr"/>
       <c r="H1023" s="2" t="n"/>
     </row>
     <row r="1024">
@@ -55291,22 +55291,26 @@
       </c>
       <c r="C1024" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
         </is>
       </c>
       <c r="D1024" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
-        </is>
-      </c>
-      <c r="E1024" s="2" t="n"/>
-      <c r="F1024" s="2" t="n"/>
-      <c r="G1024" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1024" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E1024" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F1024" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1024" s="2" t="inlineStr"/>
+      <c r="H1024" s="2" t="inlineStr">
+        <is>
+          <t>Documentación técnica: 100% a la contratación. Subvención: 3,5% a la concesión de cada subvención</t>
+        </is>
+      </c>
     </row>
     <row r="1025">
       <c r="A1025" s="2" t="inlineStr">
@@ -55321,27 +55325,29 @@
       </c>
       <c r="C1025" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>GESTIÓN DE SUBVENCIONES DE EFICIENCIA ENERGÉTICA</t>
         </is>
       </c>
       <c r="D1025" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E1025" s="2" t="n"/>
-      <c r="F1025" s="2" t="n"/>
-      <c r="G1025" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1025" s="2" t="n"/>
+      <c r="F1025" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1025" s="2" t="inlineStr"/>
+      <c r="H1025" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="1026">
       <c r="A1026" s="2" t="inlineStr">
         <is>
-          <t>F259</t>
+          <t>F258</t>
         </is>
       </c>
       <c r="B1026" s="2" t="inlineStr">
@@ -55351,23 +55357,27 @@
       </c>
       <c r="C1026" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
         </is>
       </c>
       <c r="D1026" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="E1026" s="2" t="n"/>
       <c r="F1026" s="2" t="n"/>
-      <c r="G1026" s="2" t="inlineStr"/>
+      <c r="G1026" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1026" s="2" t="n"/>
     </row>
     <row r="1027">
       <c r="A1027" s="2" t="inlineStr">
         <is>
-          <t>F259</t>
+          <t>F258</t>
         </is>
       </c>
       <c r="B1027" s="2" t="inlineStr">
@@ -55377,23 +55387,27 @@
       </c>
       <c r="C1027" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>LIBRO DEL EDIFICIO</t>
         </is>
       </c>
       <c r="D1027" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>LEE</t>
         </is>
       </c>
       <c r="E1027" s="2" t="n"/>
       <c r="F1027" s="2" t="n"/>
-      <c r="G1027" s="2" t="inlineStr"/>
+      <c r="G1027" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1027" s="2" t="n"/>
     </row>
     <row r="1028">
       <c r="A1028" s="2" t="inlineStr">
         <is>
-          <t>F259</t>
+          <t>F258</t>
         </is>
       </c>
       <c r="B1028" s="2" t="inlineStr">
@@ -55403,23 +55417,27 @@
       </c>
       <c r="C1028" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
         </is>
       </c>
       <c r="D1028" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E1028" s="2" t="n"/>
       <c r="F1028" s="2" t="n"/>
-      <c r="G1028" s="2" t="inlineStr"/>
+      <c r="G1028" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1028" s="2" t="n"/>
     </row>
     <row r="1029">
       <c r="A1029" s="2" t="inlineStr">
         <is>
-          <t>F259</t>
+          <t>F258</t>
         </is>
       </c>
       <c r="B1029" s="2" t="inlineStr">
@@ -55429,7 +55447,7 @@
       </c>
       <c r="C1029" s="2" t="inlineStr">
         <is>
-          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D1029" s="2" t="inlineStr">
@@ -55439,7 +55457,11 @@
       </c>
       <c r="E1029" s="2" t="n"/>
       <c r="F1029" s="2" t="n"/>
-      <c r="G1029" s="2" t="inlineStr"/>
+      <c r="G1029" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1029" s="2" t="n"/>
     </row>
     <row r="1030">
@@ -55455,12 +55477,12 @@
       </c>
       <c r="C1030" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D1030" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E1030" s="2" t="n"/>
@@ -55481,12 +55503,12 @@
       </c>
       <c r="C1031" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D1031" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>REDACCION PROYECTO</t>
         </is>
       </c>
       <c r="E1031" s="2" t="n"/>
@@ -55507,180 +55529,162 @@
       </c>
       <c r="C1032" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D1032" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E1032" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E1032" s="2" t="n"/>
       <c r="F1032" s="2" t="n"/>
       <c r="G1032" s="2" t="inlineStr"/>
-      <c r="H1032" s="2" t="inlineStr">
-        <is>
-          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
-        </is>
-      </c>
+      <c r="H1032" s="2" t="n"/>
     </row>
     <row r="1033">
       <c r="A1033" s="2" t="inlineStr">
         <is>
-          <t>F260</t>
+          <t>F259</t>
         </is>
       </c>
       <c r="B1033" s="2" t="inlineStr">
         <is>
-          <t>ALCALA DE GUADAIRA 41 MADRID</t>
+          <t>PASEO DE LA HABANA 80 MADRID</t>
         </is>
       </c>
       <c r="C1033" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES</t>
+          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
         </is>
       </c>
       <c r="D1033" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E1033" s="2" t="n">
-        <v>2225</v>
-      </c>
-      <c r="F1033" s="2" t="n">
-        <v>3.5</v>
-      </c>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
+        </is>
+      </c>
+      <c r="E1033" s="2" t="n"/>
+      <c r="F1033" s="2" t="n"/>
       <c r="G1033" s="2" t="inlineStr"/>
-      <c r="H1033" s="2" t="inlineStr">
-        <is>
-          <t>Tramo fijo 100% a la contratación; tramo variable 3,5% a la concesión de cada subvención</t>
-        </is>
-      </c>
+      <c r="H1033" s="2" t="n"/>
     </row>
     <row r="1034">
       <c r="A1034" s="2" t="inlineStr">
         <is>
-          <t>F261</t>
+          <t>F259</t>
         </is>
       </c>
       <c r="B1034" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE SAN ILLAN 3 MADRID</t>
+          <t>PASEO DE LA HABANA 80 MADRID</t>
         </is>
       </c>
       <c r="C1034" s="2" t="inlineStr">
         <is>
-          <t>Toma de datos y modelado 3D</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D1034" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E1034" s="2" t="n"/>
       <c r="F1034" s="2" t="n"/>
-      <c r="G1034" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1034" s="2" t="inlineStr"/>
       <c r="H1034" s="2" t="n"/>
     </row>
     <row r="1035">
       <c r="A1035" s="2" t="inlineStr">
         <is>
-          <t>F261</t>
+          <t>F259</t>
         </is>
       </c>
       <c r="B1035" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE SAN ILLAN 3 MADRID</t>
+          <t>PASEO DE LA HABANA 80 MADRID</t>
         </is>
       </c>
       <c r="C1035" s="2" t="inlineStr">
         <is>
-          <t>Proyecto (Redacción del Proyecto Básico y de Ejecución)</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D1035" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
-        </is>
-      </c>
-      <c r="E1035" s="2" t="n">
-        <v>6980</v>
-      </c>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="E1035" s="2" t="n"/>
       <c r="F1035" s="2" t="n"/>
       <c r="G1035" s="2" t="inlineStr"/>
-      <c r="H1035" s="2" t="inlineStr">
-        <is>
-          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
-        </is>
-      </c>
+      <c r="H1035" s="2" t="n"/>
     </row>
     <row r="1036">
       <c r="A1036" s="2" t="inlineStr">
         <is>
-          <t>F261</t>
+          <t>F259</t>
         </is>
       </c>
       <c r="B1036" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE SAN ILLAN 3 MADRID</t>
+          <t>PASEO DE LA HABANA 80 MADRID</t>
         </is>
       </c>
       <c r="C1036" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Licencia</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D1036" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
-        </is>
-      </c>
-      <c r="E1036" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E1036" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F1036" s="2" t="n"/>
-      <c r="G1036" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1036" s="2" t="n"/>
+      <c r="G1036" s="2" t="inlineStr"/>
+      <c r="H1036" s="2" t="inlineStr">
+        <is>
+          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
+        </is>
+      </c>
     </row>
     <row r="1037">
       <c r="A1037" s="2" t="inlineStr">
         <is>
-          <t>F261</t>
+          <t>F260</t>
         </is>
       </c>
       <c r="B1037" s="2" t="inlineStr">
         <is>
-          <t>PASEO DE SAN ILLAN 3 MADRID</t>
+          <t>ALCALA DE GUADAIRA 41 MADRID</t>
         </is>
       </c>
       <c r="C1037" s="2" t="inlineStr">
         <is>
-          <t>Solicitud y análisis de presupuestos</t>
+          <t>GESTIÓN DE SUBVENCIONES</t>
         </is>
       </c>
       <c r="D1037" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
-        </is>
-      </c>
-      <c r="E1037" s="2" t="n"/>
-      <c r="F1037" s="2" t="n"/>
-      <c r="G1037" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1037" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E1037" s="2" t="n">
+        <v>2225</v>
+      </c>
+      <c r="F1037" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1037" s="2" t="inlineStr"/>
+      <c r="H1037" s="2" t="inlineStr">
+        <is>
+          <t>Tramo fijo 100% a la contratación; tramo variable 3,5% a la concesión de cada subvención</t>
+        </is>
+      </c>
     </row>
     <row r="1038">
       <c r="A1038" s="2" t="inlineStr">
@@ -55695,12 +55699,12 @@
       </c>
       <c r="C1038" s="2" t="inlineStr">
         <is>
-          <t>Fin de obra</t>
+          <t>Toma de datos y modelado 3D</t>
         </is>
       </c>
       <c r="D1038" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E1038" s="2" t="n"/>
@@ -55725,22 +55729,24 @@
       </c>
       <c r="C1039" s="2" t="inlineStr">
         <is>
-          <t>Dirección Facultativa</t>
+          <t>Proyecto (Redacción del Proyecto Básico y de Ejecución)</t>
         </is>
       </c>
       <c r="D1039" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E1039" s="2" t="n"/>
+          <t>REDACCION PROYECTO</t>
+        </is>
+      </c>
+      <c r="E1039" s="2" t="n">
+        <v>6980</v>
+      </c>
       <c r="F1039" s="2" t="n"/>
-      <c r="G1039" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1039" s="2" t="n"/>
+      <c r="G1039" s="2" t="inlineStr"/>
+      <c r="H1039" s="2" t="inlineStr">
+        <is>
+          <t>50% a la contratación (provisión de fondos), 50% a la entrega del proyecto</t>
+        </is>
+      </c>
     </row>
     <row r="1040">
       <c r="A1040" s="2" t="inlineStr">
@@ -55755,29 +55761,27 @@
       </c>
       <c r="C1040" s="2" t="inlineStr">
         <is>
-          <t>Coordinación de Seguridad y Salud</t>
+          <t>Tramitación de Licencia</t>
         </is>
       </c>
       <c r="D1040" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E1040" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E1040" s="2" t="n"/>
       <c r="F1040" s="2" t="n"/>
-      <c r="G1040" s="2" t="inlineStr"/>
-      <c r="H1040" s="2" t="inlineStr">
-        <is>
-          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
-        </is>
-      </c>
+      <c r="G1040" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1040" s="2" t="n"/>
     </row>
     <row r="1041">
       <c r="A1041" s="2" t="inlineStr">
         <is>
-          <t>F262</t>
+          <t>F261</t>
         </is>
       </c>
       <c r="B1041" s="2" t="inlineStr">
@@ -55787,29 +55791,27 @@
       </c>
       <c r="C1041" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Subvenciones (A éxito)</t>
+          <t>Solicitud y análisis de presupuestos</t>
         </is>
       </c>
       <c r="D1041" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E1041" s="2" t="n"/>
-      <c r="F1041" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G1041" s="2" t="inlineStr"/>
-      <c r="H1041" s="2" t="inlineStr">
-        <is>
-          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
-        </is>
-      </c>
+      <c r="F1041" s="2" t="n"/>
+      <c r="G1041" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1041" s="2" t="n"/>
     </row>
     <row r="1042">
       <c r="A1042" s="2" t="inlineStr">
         <is>
-          <t>F262</t>
+          <t>F261</t>
         </is>
       </c>
       <c r="B1042" s="2" t="inlineStr">
@@ -55819,29 +55821,27 @@
       </c>
       <c r="C1042" s="2" t="inlineStr">
         <is>
-          <t>Documentación Técnica Anexa</t>
+          <t>Fin de obra</t>
         </is>
       </c>
       <c r="D1042" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E1042" s="2" t="n">
-        <v>1980</v>
-      </c>
+          <t>CERTIFICADO FIN DE OBRA</t>
+        </is>
+      </c>
+      <c r="E1042" s="2" t="n"/>
       <c r="F1042" s="2" t="n"/>
-      <c r="G1042" s="2" t="inlineStr"/>
-      <c r="H1042" s="2" t="inlineStr">
-        <is>
-          <t>A la contratación: 100%</t>
-        </is>
-      </c>
+      <c r="G1042" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1042" s="2" t="n"/>
     </row>
     <row r="1043">
       <c r="A1043" s="2" t="inlineStr">
         <is>
-          <t>F262</t>
+          <t>F261</t>
         </is>
       </c>
       <c r="B1043" s="2" t="inlineStr">
@@ -55851,12 +55851,12 @@
       </c>
       <c r="C1043" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+          <t>Dirección Facultativa</t>
         </is>
       </c>
       <c r="D1043" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E1043" s="2" t="n"/>
@@ -55871,7 +55871,7 @@
     <row r="1044">
       <c r="A1044" s="2" t="inlineStr">
         <is>
-          <t>F262</t>
+          <t>F261</t>
         </is>
       </c>
       <c r="B1044" s="2" t="inlineStr">
@@ -55881,22 +55881,24 @@
       </c>
       <c r="C1044" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+          <t>Coordinación de Seguridad y Salud</t>
         </is>
       </c>
       <c r="D1044" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
-        </is>
-      </c>
-      <c r="E1044" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E1044" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F1044" s="2" t="n"/>
-      <c r="G1044" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1044" s="2" t="n"/>
+      <c r="G1044" s="2" t="inlineStr"/>
+      <c r="H1044" s="2" t="inlineStr">
+        <is>
+          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
+        </is>
+      </c>
     </row>
     <row r="1045">
       <c r="A1045" s="2" t="inlineStr">
@@ -55911,115 +55913,131 @@
       </c>
       <c r="C1045" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>Tramitación de Subvenciones (A éxito)</t>
         </is>
       </c>
       <c r="D1045" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E1045" s="2" t="n"/>
-      <c r="F1045" s="2" t="n"/>
-      <c r="G1045" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1045" s="2" t="n"/>
+      <c r="F1045" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1045" s="2" t="inlineStr"/>
+      <c r="H1045" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
+        </is>
+      </c>
     </row>
     <row r="1046">
       <c r="A1046" s="2" t="inlineStr">
         <is>
-          <t>F263</t>
+          <t>F262</t>
         </is>
       </c>
       <c r="B1046" s="2" t="inlineStr">
         <is>
-          <t>GENIL 5 MADRID</t>
+          <t>PASEO DE SAN ILLAN 3 MADRID</t>
         </is>
       </c>
       <c r="C1046" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>Documentación Técnica Anexa</t>
         </is>
       </c>
       <c r="D1046" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
-        </is>
-      </c>
-      <c r="E1046" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E1046" s="2" t="n">
+        <v>1980</v>
+      </c>
       <c r="F1046" s="2" t="n"/>
       <c r="G1046" s="2" t="inlineStr"/>
-      <c r="H1046" s="2" t="n"/>
+      <c r="H1046" s="2" t="inlineStr">
+        <is>
+          <t>A la contratación: 100%</t>
+        </is>
+      </c>
     </row>
     <row r="1047">
       <c r="A1047" s="2" t="inlineStr">
         <is>
-          <t>F263</t>
+          <t>F262</t>
         </is>
       </c>
       <c r="B1047" s="2" t="inlineStr">
         <is>
-          <t>GENIL 5 MADRID</t>
+          <t>PASEO DE SAN ILLAN 3 MADRID</t>
         </is>
       </c>
       <c r="C1047" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
         </is>
       </c>
       <c r="D1047" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="E1047" s="2" t="n"/>
       <c r="F1047" s="2" t="n"/>
-      <c r="G1047" s="2" t="inlineStr"/>
+      <c r="G1047" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1047" s="2" t="n"/>
     </row>
     <row r="1048">
       <c r="A1048" s="2" t="inlineStr">
         <is>
-          <t>F263</t>
+          <t>F262</t>
         </is>
       </c>
       <c r="B1048" s="2" t="inlineStr">
         <is>
-          <t>GENIL 5 MADRID</t>
+          <t>PASEO DE SAN ILLAN 3 MADRID</t>
         </is>
       </c>
       <c r="C1048" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
         </is>
       </c>
       <c r="D1048" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E1048" s="2" t="n"/>
       <c r="F1048" s="2" t="n"/>
-      <c r="G1048" s="2" t="inlineStr"/>
+      <c r="G1048" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1048" s="2" t="n"/>
     </row>
     <row r="1049">
       <c r="A1049" s="2" t="inlineStr">
         <is>
-          <t>F263</t>
+          <t>F262</t>
         </is>
       </c>
       <c r="B1049" s="2" t="inlineStr">
         <is>
-          <t>GENIL 5 MADRID</t>
+          <t>PASEO DE SAN ILLAN 3 MADRID</t>
         </is>
       </c>
       <c r="C1049" s="2" t="inlineStr">
         <is>
-          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D1049" s="2" t="inlineStr">
@@ -56029,7 +56047,11 @@
       </c>
       <c r="E1049" s="2" t="n"/>
       <c r="F1049" s="2" t="n"/>
-      <c r="G1049" s="2" t="inlineStr"/>
+      <c r="G1049" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1049" s="2" t="n"/>
     </row>
     <row r="1050">
@@ -56045,12 +56067,12 @@
       </c>
       <c r="C1050" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D1050" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E1050" s="2" t="n"/>
@@ -56071,24 +56093,18 @@
       </c>
       <c r="C1051" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D1051" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
-        </is>
-      </c>
-      <c r="E1051" s="2" t="n">
-        <v>1000</v>
-      </c>
+          <t>REDACCION PROYECTO</t>
+        </is>
+      </c>
+      <c r="E1051" s="2" t="n"/>
       <c r="F1051" s="2" t="n"/>
       <c r="G1051" s="2" t="inlineStr"/>
-      <c r="H1051" s="2" t="inlineStr">
-        <is>
-          <t>100% al comienzo de obra</t>
-        </is>
-      </c>
+      <c r="H1051" s="2" t="n"/>
     </row>
     <row r="1052">
       <c r="A1052" s="2" t="inlineStr">
@@ -56103,44 +56119,38 @@
       </c>
       <c r="C1052" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D1052" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E1052" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E1052" s="2" t="n"/>
       <c r="F1052" s="2" t="n"/>
       <c r="G1052" s="2" t="inlineStr"/>
-      <c r="H1052" s="2" t="inlineStr">
-        <is>
-          <t>100% a la firma del Plan de Seguridad y Salud</t>
-        </is>
-      </c>
+      <c r="H1052" s="2" t="n"/>
     </row>
     <row r="1053">
       <c r="A1053" s="2" t="inlineStr">
         <is>
-          <t>F264</t>
+          <t>F263</t>
         </is>
       </c>
       <c r="B1053" s="2" t="inlineStr">
         <is>
-          <t>PADILLA 4 MOSTOLES</t>
+          <t>GENIL 5 MADRID</t>
         </is>
       </c>
       <c r="C1053" s="2" t="inlineStr">
         <is>
-          <t>Coordinación de Seguridad y Salud</t>
+          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
         </is>
       </c>
       <c r="D1053" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E1053" s="2" t="n"/>
@@ -56151,22 +56161,22 @@
     <row r="1054">
       <c r="A1054" s="2" t="inlineStr">
         <is>
-          <t>F264</t>
+          <t>F263</t>
         </is>
       </c>
       <c r="B1054" s="2" t="inlineStr">
         <is>
-          <t>PADILLA 4 MOSTOLES</t>
+          <t>GENIL 5 MADRID</t>
         </is>
       </c>
       <c r="C1054" s="2" t="inlineStr">
         <is>
-          <t>Dirección Facultativa</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D1054" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E1054" s="2" t="n"/>
@@ -56177,131 +56187,123 @@
     <row r="1055">
       <c r="A1055" s="2" t="inlineStr">
         <is>
-          <t>F265</t>
+          <t>F263</t>
         </is>
       </c>
       <c r="B1055" s="2" t="inlineStr">
         <is>
-          <t>BOLSA 3 MADRID</t>
+          <t>GENIL 5 MADRID</t>
         </is>
       </c>
       <c r="C1055" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D1055" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E1055" s="2" t="n">
-        <v>1980</v>
-      </c>
-      <c r="F1055" s="2" t="n">
-        <v>3.5</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="F1055" s="2" t="n"/>
       <c r="G1055" s="2" t="inlineStr"/>
       <c r="H1055" s="2" t="inlineStr">
         <is>
-          <t>Documentación técnica: 100% a la contratación. Subvención: 3,5% a la concesión de cada subvención</t>
+          <t>100% al comienzo de obra</t>
         </is>
       </c>
     </row>
     <row r="1056">
       <c r="A1056" s="2" t="inlineStr">
         <is>
-          <t>F265</t>
+          <t>F263</t>
         </is>
       </c>
       <c r="B1056" s="2" t="inlineStr">
         <is>
-          <t>BOLSA 3 MADRID</t>
+          <t>GENIL 5 MADRID</t>
         </is>
       </c>
       <c r="C1056" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D1056" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
-        </is>
-      </c>
-      <c r="E1056" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E1056" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F1056" s="2" t="n"/>
-      <c r="G1056" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1056" s="2" t="n"/>
+      <c r="G1056" s="2" t="inlineStr"/>
+      <c r="H1056" s="2" t="inlineStr">
+        <is>
+          <t>100% a la firma del Plan de Seguridad y Salud</t>
+        </is>
+      </c>
     </row>
     <row r="1057">
       <c r="A1057" s="2" t="inlineStr">
         <is>
-          <t>F265</t>
+          <t>F264</t>
         </is>
       </c>
       <c r="B1057" s="2" t="inlineStr">
         <is>
-          <t>BOLSA 3 MADRID</t>
+          <t>PADILLA 4 MOSTOLES</t>
         </is>
       </c>
       <c r="C1057" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>Coordinación de Seguridad y Salud</t>
         </is>
       </c>
       <c r="D1057" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="E1057" s="2" t="n"/>
       <c r="F1057" s="2" t="n"/>
-      <c r="G1057" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1057" s="2" t="inlineStr"/>
       <c r="H1057" s="2" t="n"/>
     </row>
     <row r="1058">
       <c r="A1058" s="2" t="inlineStr">
         <is>
-          <t>F265</t>
+          <t>F264</t>
         </is>
       </c>
       <c r="B1058" s="2" t="inlineStr">
         <is>
-          <t>BOLSA 3 MADRID</t>
+          <t>PADILLA 4 MOSTOLES</t>
         </is>
       </c>
       <c r="C1058" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>Dirección Facultativa</t>
         </is>
       </c>
       <c r="D1058" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E1058" s="2" t="n"/>
       <c r="F1058" s="2" t="n"/>
-      <c r="G1058" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1058" s="2" t="inlineStr"/>
       <c r="H1058" s="2" t="n"/>
     </row>
     <row r="1059">
       <c r="A1059" s="2" t="inlineStr">
         <is>
-          <t>F266</t>
+          <t>F265</t>
         </is>
       </c>
       <c r="B1059" s="2" t="inlineStr">
@@ -56311,23 +56313,31 @@
       </c>
       <c r="C1059" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
+          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD (Documentación Técnica Anexa + tramo a éxito)</t>
         </is>
       </c>
       <c r="D1059" s="2" t="inlineStr">
         <is>
-          <t>TOMA DE DATOS Y MODELADO 3D</t>
-        </is>
-      </c>
-      <c r="E1059" s="2" t="n"/>
-      <c r="F1059" s="2" t="n"/>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E1059" s="2" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F1059" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G1059" s="2" t="inlineStr"/>
-      <c r="H1059" s="2" t="n"/>
+      <c r="H1059" s="2" t="inlineStr">
+        <is>
+          <t>Documentación técnica: 100% a la contratación. Subvención: 3,5% a la concesión de cada subvención</t>
+        </is>
+      </c>
     </row>
     <row r="1060">
       <c r="A1060" s="2" t="inlineStr">
         <is>
-          <t>F266</t>
+          <t>F265</t>
         </is>
       </c>
       <c r="B1060" s="2" t="inlineStr">
@@ -56337,23 +56347,27 @@
       </c>
       <c r="C1060" s="2" t="inlineStr">
         <is>
-          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="D1060" s="2" t="inlineStr">
         <is>
-          <t>REDACCION PROYECTO</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="E1060" s="2" t="n"/>
       <c r="F1060" s="2" t="n"/>
-      <c r="G1060" s="2" t="inlineStr"/>
+      <c r="G1060" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1060" s="2" t="n"/>
     </row>
     <row r="1061">
       <c r="A1061" s="2" t="inlineStr">
         <is>
-          <t>F266</t>
+          <t>F265</t>
         </is>
       </c>
       <c r="B1061" s="2" t="inlineStr">
@@ -56363,23 +56377,27 @@
       </c>
       <c r="C1061" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="D1061" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION LICENCIAS</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E1061" s="2" t="n"/>
       <c r="F1061" s="2" t="n"/>
-      <c r="G1061" s="2" t="inlineStr"/>
+      <c r="G1061" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1061" s="2" t="n"/>
     </row>
     <row r="1062">
       <c r="A1062" s="2" t="inlineStr">
         <is>
-          <t>F266</t>
+          <t>F265</t>
         </is>
       </c>
       <c r="B1062" s="2" t="inlineStr">
@@ -56389,7 +56407,7 @@
       </c>
       <c r="C1062" s="2" t="inlineStr">
         <is>
-          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D1062" s="2" t="inlineStr">
@@ -56399,7 +56417,11 @@
       </c>
       <c r="E1062" s="2" t="n"/>
       <c r="F1062" s="2" t="n"/>
-      <c r="G1062" s="2" t="inlineStr"/>
+      <c r="G1062" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
       <c r="H1062" s="2" t="n"/>
     </row>
     <row r="1063">
@@ -56415,12 +56437,12 @@
       </c>
       <c r="C1063" s="2" t="inlineStr">
         <is>
-          <t>FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="D1063" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO FIN DE OBRA</t>
+          <t>TOMA DE DATOS Y MODELADO 3D</t>
         </is>
       </c>
       <c r="E1063" s="2" t="n"/>
@@ -56441,12 +56463,12 @@
       </c>
       <c r="C1064" s="2" t="inlineStr">
         <is>
-          <t>DIRECCIÓN FACULTATIVA</t>
+          <t>REDACCIÓN DEL PROYECTO BÁSICO Y DE EJECUCIÓN</t>
         </is>
       </c>
       <c r="D1064" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>REDACCION PROYECTO</t>
         </is>
       </c>
       <c r="E1064" s="2" t="n"/>
@@ -56467,234 +56489,212 @@
       </c>
       <c r="C1065" s="2" t="inlineStr">
         <is>
-          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
+          <t>TRAMITACIÓN DE LICENCIAS Y PERMISOS</t>
         </is>
       </c>
       <c r="D1065" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
-        </is>
-      </c>
-      <c r="E1065" s="2" t="n">
-        <v>920</v>
-      </c>
+          <t>TRAMITACION LICENCIAS</t>
+        </is>
+      </c>
+      <c r="E1065" s="2" t="n"/>
       <c r="F1065" s="2" t="n"/>
       <c r="G1065" s="2" t="inlineStr"/>
-      <c r="H1065" s="2" t="inlineStr">
-        <is>
-          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
-        </is>
-      </c>
+      <c r="H1065" s="2" t="n"/>
     </row>
     <row r="1066">
       <c r="A1066" s="2" t="inlineStr">
         <is>
-          <t>F267</t>
+          <t>F266</t>
         </is>
       </c>
       <c r="B1066" s="2" t="inlineStr">
         <is>
-          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
+          <t>BOLSA 3 MADRID</t>
         </is>
       </c>
       <c r="C1066" s="2" t="inlineStr">
         <is>
-          <t>Tramitación de Subvenciones (Gestión de Subvenciones Accesibilidad)</t>
+          <t>SOLICITUD Y ANÁLISIS DE PRESUPUESTOS</t>
         </is>
       </c>
       <c r="D1066" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E1066" s="2" t="n">
-        <v>2625</v>
-      </c>
-      <c r="F1066" s="2" t="n">
-        <v>3.5</v>
-      </c>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
+        </is>
+      </c>
+      <c r="E1066" s="2" t="n"/>
+      <c r="F1066" s="2" t="n"/>
       <c r="G1066" s="2" t="inlineStr"/>
-      <c r="H1066" s="2" t="inlineStr">
-        <is>
-          <t>A la concesión de cada subvención, 3.5% del importe concedido tras su ingreso</t>
-        </is>
-      </c>
+      <c r="H1066" s="2" t="n"/>
     </row>
     <row r="1067">
       <c r="A1067" s="2" t="inlineStr">
         <is>
-          <t>F267</t>
+          <t>F266</t>
         </is>
       </c>
       <c r="B1067" s="2" t="inlineStr">
         <is>
-          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
+          <t>BOLSA 3 MADRID</t>
         </is>
       </c>
       <c r="C1067" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>FIN DE OBRA</t>
         </is>
       </c>
       <c r="D1067" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>CERTIFICADO FIN DE OBRA</t>
         </is>
       </c>
       <c r="E1067" s="2" t="n"/>
       <c r="F1067" s="2" t="n"/>
-      <c r="G1067" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1067" s="2" t="inlineStr"/>
       <c r="H1067" s="2" t="n"/>
     </row>
     <row r="1068">
       <c r="A1068" s="2" t="inlineStr">
         <is>
-          <t>F267</t>
+          <t>F266</t>
         </is>
       </c>
       <c r="B1068" s="2" t="inlineStr">
         <is>
-          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
+          <t>BOLSA 3 MADRID</t>
         </is>
       </c>
       <c r="C1068" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>DIRECCIÓN FACULTATIVA</t>
         </is>
       </c>
       <c r="D1068" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E1068" s="2" t="n"/>
       <c r="F1068" s="2" t="n"/>
-      <c r="G1068" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
+      <c r="G1068" s="2" t="inlineStr"/>
       <c r="H1068" s="2" t="n"/>
     </row>
     <row r="1069">
       <c r="A1069" s="2" t="inlineStr">
         <is>
-          <t>F267</t>
+          <t>F266</t>
         </is>
       </c>
       <c r="B1069" s="2" t="inlineStr">
         <is>
-          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
+          <t>BOLSA 3 MADRID</t>
         </is>
       </c>
       <c r="C1069" s="2" t="inlineStr">
         <is>
-          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
+          <t>COORDINACIÓN DE SEGURIDAD Y SALUD</t>
         </is>
       </c>
       <c r="D1069" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION 3 PRESUPUESTOS</t>
-        </is>
-      </c>
-      <c r="E1069" s="2" t="n"/>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E1069" s="2" t="n">
+        <v>920</v>
+      </c>
       <c r="F1069" s="2" t="n"/>
-      <c r="G1069" s="2" t="inlineStr">
-        <is>
-          <t>sí</t>
-        </is>
-      </c>
-      <c r="H1069" s="2" t="n"/>
+      <c r="G1069" s="2" t="inlineStr"/>
+      <c r="H1069" s="2" t="inlineStr">
+        <is>
+          <t>A la firma del Plan de Seguridad y Salud: 100% de los honorarios</t>
+        </is>
+      </c>
     </row>
     <row r="1070">
       <c r="A1070" s="2" t="inlineStr">
         <is>
-          <t>F268</t>
+          <t>F267</t>
         </is>
       </c>
       <c r="B1070" s="2" t="inlineStr">
         <is>
-          <t>AV DR FLEMING 32 LEGANES</t>
+          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
         </is>
       </c>
       <c r="C1070" s="2" t="inlineStr">
         <is>
-          <t>Coordinación de Seguridad y Salud</t>
+          <t>Tramitación de Subvenciones (Gestión de Subvenciones Accesibilidad)</t>
         </is>
       </c>
       <c r="D1070" s="2" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>TRAMITACION SUBVENCIONES</t>
         </is>
       </c>
       <c r="E1070" s="2" t="n">
-        <v>990</v>
-      </c>
-      <c r="F1070" s="2" t="n"/>
+        <v>2625</v>
+      </c>
+      <c r="F1070" s="2" t="n">
+        <v>3.5</v>
+      </c>
       <c r="G1070" s="2" t="inlineStr"/>
       <c r="H1070" s="2" t="inlineStr">
         <is>
-          <t>100% a la firma del Plan de Seguridad y Salud</t>
+          <t>A la concesión de cada subvención, 3.5% del importe concedido tras su ingreso</t>
         </is>
       </c>
     </row>
     <row r="1071">
       <c r="A1071" s="2" t="inlineStr">
         <is>
-          <t>F269</t>
+          <t>F267</t>
         </is>
       </c>
       <c r="B1071" s="2" t="inlineStr">
         <is>
-          <t>FELIPE ALVAREZ 28 MADRID</t>
+          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
         </is>
       </c>
       <c r="C1071" s="2" t="inlineStr">
         <is>
-          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD</t>
+          <t>IEE</t>
         </is>
       </c>
       <c r="D1071" s="2" t="inlineStr">
         <is>
-          <t>TRAMITACION SUBVENCIONES</t>
-        </is>
-      </c>
-      <c r="E1071" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F1071" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="G1071" s="2" t="inlineStr"/>
-      <c r="H1071" s="2" t="inlineStr">
-        <is>
-          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
-        </is>
-      </c>
+          <t>IEE</t>
+        </is>
+      </c>
+      <c r="E1071" s="2" t="n"/>
+      <c r="F1071" s="2" t="n"/>
+      <c r="G1071" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1071" s="2" t="n"/>
     </row>
     <row r="1072">
       <c r="A1072" s="2" t="inlineStr">
         <is>
-          <t>F269</t>
+          <t>F267</t>
         </is>
       </c>
       <c r="B1072" s="2" t="inlineStr">
         <is>
-          <t>FELIPE ALVAREZ 28 MADRID</t>
+          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
         </is>
       </c>
       <c r="C1072" s="2" t="inlineStr">
         <is>
-          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="D1072" s="2" t="inlineStr">
         <is>
-          <t>IEE</t>
+          <t>CEE</t>
         </is>
       </c>
       <c r="E1072" s="2" t="n"/>
@@ -56709,22 +56709,22 @@
     <row r="1073">
       <c r="A1073" s="2" t="inlineStr">
         <is>
-          <t>F269</t>
+          <t>F267</t>
         </is>
       </c>
       <c r="B1073" s="2" t="inlineStr">
         <is>
-          <t>FELIPE ALVAREZ 28 MADRID</t>
+          <t>NÉCTAR 31 PORTAL 1 - 2 - 3 MADRID</t>
         </is>
       </c>
       <c r="C1073" s="2" t="inlineStr">
         <is>
-          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+          <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
       <c r="D1073" s="2" t="inlineStr">
         <is>
-          <t>CEE</t>
+          <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
       <c r="E1073" s="2" t="n"/>
@@ -56739,35 +56739,161 @@
     <row r="1074">
       <c r="A1074" s="2" t="inlineStr">
         <is>
+          <t>F268</t>
+        </is>
+      </c>
+      <c r="B1074" s="2" t="inlineStr">
+        <is>
+          <t>AV DR FLEMING 32 LEGANES</t>
+        </is>
+      </c>
+      <c r="C1074" s="2" t="inlineStr">
+        <is>
+          <t>Coordinación de Seguridad y Salud</t>
+        </is>
+      </c>
+      <c r="D1074" s="2" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
+      <c r="E1074" s="2" t="n">
+        <v>990</v>
+      </c>
+      <c r="F1074" s="2" t="n"/>
+      <c r="G1074" s="2" t="inlineStr"/>
+      <c r="H1074" s="2" t="inlineStr">
+        <is>
+          <t>100% a la firma del Plan de Seguridad y Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" s="2" t="inlineStr">
+        <is>
           <t>F269</t>
         </is>
       </c>
-      <c r="B1074" s="2" t="inlineStr">
+      <c r="B1075" s="2" t="inlineStr">
         <is>
           <t>FELIPE ALVAREZ 28 MADRID</t>
         </is>
       </c>
-      <c r="C1074" s="2" t="inlineStr">
+      <c r="C1075" s="2" t="inlineStr">
+        <is>
+          <t>GESTIÓN DE SUBVENCIONES ACCESIBILIDAD</t>
+        </is>
+      </c>
+      <c r="D1075" s="2" t="inlineStr">
+        <is>
+          <t>TRAMITACION SUBVENCIONES</t>
+        </is>
+      </c>
+      <c r="E1075" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F1075" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G1075" s="2" t="inlineStr"/>
+      <c r="H1075" s="2" t="inlineStr">
+        <is>
+          <t>A la concesión de cada subvención, 3,5% del importe concedido tras su ingreso en la cuenta de la comunidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" s="2" t="inlineStr">
+        <is>
+          <t>F269</t>
+        </is>
+      </c>
+      <c r="B1076" s="2" t="inlineStr">
+        <is>
+          <t>FELIPE ALVAREZ 28 MADRID</t>
+        </is>
+      </c>
+      <c r="C1076" s="2" t="inlineStr">
+        <is>
+          <t>INFORME DE EVALUACIÓN DEL EDIFICIO (IEE)</t>
+        </is>
+      </c>
+      <c r="D1076" s="2" t="inlineStr">
+        <is>
+          <t>IEE</t>
+        </is>
+      </c>
+      <c r="E1076" s="2" t="n"/>
+      <c r="F1076" s="2" t="n"/>
+      <c r="G1076" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1076" s="2" t="n"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" s="2" t="inlineStr">
+        <is>
+          <t>F269</t>
+        </is>
+      </c>
+      <c r="B1077" s="2" t="inlineStr">
+        <is>
+          <t>FELIPE ALVAREZ 28 MADRID</t>
+        </is>
+      </c>
+      <c r="C1077" s="2" t="inlineStr">
+        <is>
+          <t>CERTIFICADO DE EFICIENCIA ENERGÉTICA</t>
+        </is>
+      </c>
+      <c r="D1077" s="2" t="inlineStr">
+        <is>
+          <t>CEE</t>
+        </is>
+      </c>
+      <c r="E1077" s="2" t="n"/>
+      <c r="F1077" s="2" t="n"/>
+      <c r="G1077" s="2" t="inlineStr">
+        <is>
+          <t>sí</t>
+        </is>
+      </c>
+      <c r="H1077" s="2" t="n"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" s="2" t="inlineStr">
+        <is>
+          <t>F269</t>
+        </is>
+      </c>
+      <c r="B1078" s="2" t="inlineStr">
+        <is>
+          <t>FELIPE ALVAREZ 28 MADRID</t>
+        </is>
+      </c>
+      <c r="C1078" s="2" t="inlineStr">
         <is>
           <t>Estudio y Comparativa Técnica de Adecuación a Proyecto de 3 Presupuestos de Contrata</t>
         </is>
       </c>
-      <c r="D1074" s="2" t="inlineStr">
+      <c r="D1078" s="2" t="inlineStr">
         <is>
           <t>TRAMITACION 3 PRESUPUESTOS</t>
         </is>
       </c>
-      <c r="E1074" s="2" t="n"/>
-      <c r="F1074" s="2" t="n"/>
-      <c r="G1074" s="2" t="inlineStr">
+      <c r="E1078" s="2" t="n"/>
+      <c r="F1078" s="2" t="n"/>
+      <c r="G1078" s="2" t="inlineStr">
         <is>
           <t>sí</t>
         </is>
       </c>
-      <c r="H1074" s="2" t="n"/>
+      <c r="H1078" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1074"/>
+  <autoFilter ref="A1:H1078"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>